--- a/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$324</definedName>

--- a/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$324</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$319</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E324"/>
+  <dimension ref="A1:E319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AB1009</t>
+          <t>AB1019</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,19 +487,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`angelöw` (sv)</t>
+          <t>`arbetsträtt` (sv)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1019</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AB1014</t>
+          <t>AB1019</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,17 +509,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`energised` (en)</t>
+          <t>`förläsningar` (sv)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1019</t>
         </is>
       </c>
     </row>
@@ -536,12 +536,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`arbetsträtt` (sv)</t>
+          <t>`municpality` (en)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AB1019</t>
+          <t>AB1022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -568,19 +568,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`förläsningar` (sv)</t>
+          <t>`därmellen` (sv)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1022</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AB1019</t>
+          <t>AB1029</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`municpality` (en)</t>
+          <t>`abilith` (en)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1029</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AB1022</t>
+          <t>AB3001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -622,19 +622,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`därmellen` (sv)</t>
+          <t>`kommunförb` (sv)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB3001</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AB1022</t>
+          <t>AB3001</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`kravställan` (sv)</t>
+          <t>`sölvell` (sv)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB3001</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AB1029</t>
+          <t>ABQ2AM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`abilith` (en)</t>
+          <t>`inludes` (en)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AB1031</t>
+          <t>ABQ2AM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -703,100 +703,100 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`relationalism` (en)</t>
+          <t>`managment` (en)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AB1031</t>
+          <t>ABQ2B4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`summarised` (en)</t>
+          <t>`en` — …- formulera och muntligt framföra konstruktiv kritik på en en text av vetenskaplig karaktär    - vetenskapligt värdera oc…</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2B4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AB3001</t>
+          <t>BQ1079</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`kommunförb` (sv)</t>
+          <t>`devolop` (en)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ1079</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AB3001</t>
+          <t>BQ1079</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`sölvell` (sv)</t>
+          <t>`strucuring` (en)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ1079</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ABQ2AM</t>
+          <t>BQ2018</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -806,24 +806,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`inludes` (en)</t>
+          <t>`lärarare` (sv)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2018</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ABQ2AM</t>
+          <t>BQ2018</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -838,19 +838,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`managment` (en)</t>
+          <t>`filmic` (en)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2018</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ABQ2B4</t>
+          <t>BQ2057</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -860,24 +860,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`en` — …- formulera och muntligt framföra konstruktiv kritik på en en text av vetenskaplig karaktär    - vetenskapligt värdera oc…</t>
+          <t>`postproduction` (en)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2057</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>BQ1079</t>
+          <t>GBQ29D</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -892,19 +892,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`devolop` (en)</t>
+          <t>`undergradaute` (en)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ1079</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29D</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>BQ1079</t>
+          <t>GBQ29E</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -919,19 +919,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`strucuring` (en)</t>
+          <t>`undergradaute` (en)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ1079</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29E</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>BQ2018</t>
+          <t>GBQ2U6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -946,19 +946,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`lärarare` (sv)</t>
+          <t>`användar` (sv)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>BQ2018</t>
+          <t>GBQ2U6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -968,24 +968,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`filmic` (en)</t>
+          <t>`beställningsfilmsproduktion` (sv)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>BQ2057</t>
+          <t>GBQ2UB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -995,24 +995,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`postproduction` (en)</t>
+          <t>`berättandestruktur` (sv)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2057</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UB</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GBQ29D</t>
+          <t>GBQ2WH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`undergradaute` (en)</t>
+          <t>`tbt` (en)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WH</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GBQ29E</t>
+          <t>GBQ2WK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1049,24 +1049,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`undergradaute` (en)</t>
+          <t>`berätttarelement` (sv)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WK</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U6</t>
+          <t>GBQ36K</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1076,24 +1076,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`användar` (sv)</t>
+          <t>`praktical` (en)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36K</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U6</t>
+          <t>GBQ36K</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1103,24 +1103,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`beställningsfilmsproduktion` (sv)</t>
+          <t>`thery` (en)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36K</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GBQ2UB</t>
+          <t>GBQ38V</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`berättandestruktur` (sv)</t>
+          <t>`mediacomposer-miljö` (sv)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38V</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GBQ2WH</t>
+          <t>GBQ38W</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`tbt` (en)</t>
+          <t>`composer-miljö` (sv)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GBQ2WK</t>
+          <t>GBQ38W</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`berätttarelement` (sv)</t>
+          <t>`höguppupplöst` (sv)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GBQ36K</t>
+          <t>GBQ38W</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`praktical` (en)</t>
+          <t>`avanced` (en)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GBQ36K</t>
+          <t>GBQ38X</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`thery` (en)</t>
+          <t>`documetnary` (en)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GBQ38V</t>
+          <t>GBQ38X</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1265,24 +1265,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`mediacomposer-miljö` (sv)</t>
+          <t>`filmproject` (en)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GBQ38W</t>
+          <t>GBQ38X</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1292,24 +1292,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`composer-miljö` (sv)</t>
+          <t>`histrorical` (en)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GBQ38W</t>
+          <t>GBQ3A6</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`höguppupplöst` (sv)</t>
+          <t>`användar` (sv)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GBQ38W</t>
+          <t>GBQ3A7</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1346,24 +1346,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`avanced` (en)</t>
+          <t>`wars-berättelserna` (sv)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GBQ38X</t>
+          <t>GBQ3A7</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1373,24 +1373,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`documetnary` (en)</t>
+          <t>`wars-berättelsernas` (sv)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GBQ38X</t>
+          <t>GBQ3AA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1405,19 +1405,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`filmproject` (en)</t>
+          <t>`ideational` (en)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AA</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GBQ38X</t>
+          <t>GBQ3AV</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1432,19 +1432,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`histrorical` (en)</t>
+          <t>`multimodality` (en)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AV</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A6</t>
+          <t>GBQ3AW</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1454,24 +1454,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`användar` (sv)</t>
+          <t>`explainer` (en)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A7</t>
+          <t>GBQ3FG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1481,29 +1481,29 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`wars-berättelserna` (sv)</t>
+          <t>`excercises` (en)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A7</t>
+          <t>EU1027</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`wars-berättelsernas` (sv)</t>
+          <t>`grundäggande` (sv)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1027</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AA</t>
+          <t>EU1033</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1540,51 +1540,51 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`ideational` (en)</t>
+          <t>`itssocial` (en)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1033</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AV</t>
+          <t>EU1034</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`multimodality` (en)</t>
+          <t>`förhandlingprocesser` (sv)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1034</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AW</t>
+          <t>GEU2KV</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`explainer` (en)</t>
+          <t>`opportunties` (en)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GBQ3FG</t>
+          <t>GEU2KV</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1621,51 +1621,51 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`excercises` (en)</t>
+          <t>`willll` (en)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>EU1027</t>
+          <t>AFI273</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`grundäggande` (sv)</t>
+          <t>`contignency` (en)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFI273</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>EU1033</t>
+          <t>FI1023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1675,78 +1675,78 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`itssocial` (en)</t>
+          <t>`philosohical` (en)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>EU1034</t>
+          <t>FI1024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`förhandlingprocesser` (sv)</t>
+          <t>`etichs` (en)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GEU2KV</t>
+          <t>FI1039</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`opportunties` (en)</t>
+          <t>`have` — …urthermore, on completion of the course, the student should have have the ability to :       - be reflective in relation to probl…</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GEU2KV</t>
+          <t>FI1039</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`willll` (en)</t>
+          <t>`asessment` (en)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>AFI273</t>
+          <t>FI1039</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`contignency` (en)</t>
+          <t>`developement` (en)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFI273</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>FI1023</t>
+          <t>FI2003</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1810,19 +1810,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`philosohical` (en)</t>
+          <t>`avklarade` (en)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>FI1024</t>
+          <t>FI2003</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`etichs` (en)</t>
+          <t>`filosofi` (en)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>FI1039</t>
+          <t>FI2003</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1859,24 +1859,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`have` — …urthermore, on completion of the course, the student should have have the ability to :       - be reflective in relation to probl…</t>
+          <t>`uppsats` (en)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>FI1039</t>
+          <t>FI2003</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1891,19 +1891,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`asessment` (en)</t>
+          <t>`vara` (en)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>FI1039</t>
+          <t>FI2003</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1918,19 +1918,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`developement` (en)</t>
+          <t>`varav` (en)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>FI2003</t>
+          <t>GFI3BT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1945,19 +1945,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`avklarade` (en)</t>
+          <t>`introdcution` (en)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>FI2003</t>
+          <t>GFI3BT</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1972,19 +1972,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`filosofi` (en)</t>
+          <t>`througout` (en)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>FI2003</t>
+          <t>GFI3BU</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1999,51 +1999,51 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`uppsats` (en)</t>
+          <t>`througout` (en)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>FI2003</t>
+          <t>AHI272</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`vara` (en)</t>
+          <t>`europeiskspråkiga` (sv)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>FI2003</t>
+          <t>AHI272</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`varav` (en)</t>
+          <t>`poitical` (en)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GFI3BT</t>
+          <t>AHI29Q</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`introdcution` (en)</t>
+          <t>`consultaion` (en)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GFI3BT</t>
+          <t>AHI29Q</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`througout` (en)</t>
+          <t>`situatin` (en)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GFI3BU</t>
+          <t>AS2005</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`througout` (en)</t>
+          <t>`takenup` (en)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2005</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>AHI272</t>
+          <t>AS3017</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2161,19 +2161,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`europeiskspråkiga` (sv)</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>AHI272</t>
+          <t>AS3020</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2188,19 +2188,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`poitical` (en)</t>
+          <t>`outlineof` (en)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>AHI29Q</t>
+          <t>AS3022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2215,19 +2215,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`consultaion` (en)</t>
+          <t>`teh` (en)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>AHI29Q</t>
+          <t>GHI29Y</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2237,24 +2237,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`situatin` (en)</t>
+          <t>`innhållet` (sv)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>AS2005</t>
+          <t>GHI33T</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2264,24 +2264,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`takenup` (en)</t>
+          <t>`problemförmuleringsförmåga` (sv)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>AS3017</t>
+          <t>GHI33V</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2296,19 +2296,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`literära` (sv)</t>
+          <t>`delkurseninnehåller` (sv)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>AS3020</t>
+          <t>GHI33V</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2318,24 +2318,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`outlineof` (en)</t>
+          <t>`godkäng` (sv)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>AS3022</t>
+          <t>GHI35A</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2345,24 +2345,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`teh` (en)</t>
+          <t>`analyseratmänniskors` (sv)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GHI29Y</t>
+          <t>GHI35A</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2377,19 +2377,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`innhållet` (sv)</t>
+          <t>`medförintelsen` (sv)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GHI33T</t>
+          <t>GHI35A</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`problemförmuleringsförmåga` (sv)</t>
+          <t>`människorsagerande` (sv)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GHI33V</t>
+          <t>GHI362</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2431,19 +2431,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`delkurseninnehåller` (sv)</t>
+          <t>`självstänigt` (sv)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GHI33V</t>
+          <t>GHI362</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2453,24 +2453,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`godkäng` (sv)</t>
+          <t>`metod` (en)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GHI35A</t>
+          <t>HI1008</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2480,24 +2480,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`analyseratmänniskors` (sv)</t>
+          <t>`criterions` (en)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GHI35A</t>
+          <t>HI2011</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`medförintelsen` (sv)</t>
+          <t>`historiedidaktikområdet` (sv)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GHI35A</t>
+          <t>HI2012</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`människorsagerande` (sv)</t>
+          <t>`sjävvalt` (sv)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GHI362</t>
+          <t>HI2016</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`självstänigt` (sv)</t>
+          <t>`sjävvalt` (sv)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GHI362</t>
+          <t>HI3019</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2588,29 +2588,29 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`metod` (en)</t>
+          <t>`självständg` (sv)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3019</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>HI1008</t>
+          <t>AKG27R</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2620,78 +2620,78 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`criterions` (en)</t>
+          <t>`compulsotry` (en)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>HI2011</t>
+          <t>AKG27R</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`historiedidaktikområdet` (sv)</t>
+          <t>`curent` (en)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>HI2012</t>
+          <t>AKG27R</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`sjävvalt` (sv)</t>
+          <t>`theoretica` (en)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>HI2016</t>
+          <t>GKG3AT</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2701,46 +2701,46 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`sjävvalt` (sv)</t>
+          <t>`tilllämpas` (sv)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>HI3019</t>
+          <t>GKG3AT</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`självständg` (sv)</t>
+          <t>`writtten` (en)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>AKG27R</t>
+          <t>KG1005</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2750,24 +2750,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`compulsotry` (en)</t>
+          <t>`nyström` (sv)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1005</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>AKG27R</t>
+          <t>KG1016</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2782,19 +2782,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`curent` (en)</t>
+          <t>`datalaborations` (en)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>AKG27R</t>
+          <t>KG1020</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2809,19 +2809,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`theoretica` (en)</t>
+          <t>`assignements` (en)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1020</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GKG3AT</t>
+          <t>KG1022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2831,24 +2831,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`tilllämpas` (sv)</t>
+          <t>`attractivity` (en)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1022</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GKG3AT</t>
+          <t>KG1024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2858,24 +2858,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`writtten` (en)</t>
+          <t>`beräklningstung` (sv)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>KG1005</t>
+          <t>KG1024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2885,24 +2885,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`nyström` (sv)</t>
+          <t>`chorological` (en)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>KG1016</t>
+          <t>KG1024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2917,19 +2917,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`datalaborations` (en)</t>
+          <t>`demographical` (en)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>KG1020</t>
+          <t>KG1024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2944,19 +2944,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`assignements` (en)</t>
+          <t>`quantitativ` (en)</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>KG1022</t>
+          <t>KG1025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2971,19 +2971,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`attractivity` (en)</t>
+          <t>`evolvement` (en)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>KG1024</t>
+          <t>KG1025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2993,24 +2993,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`beräklningstung` (sv)</t>
+          <t>`thise` (en)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>KG1024</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3025,19 +3025,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`chorological` (en)</t>
+          <t>`obser` (en)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>KG1024</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3052,19 +3052,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>`demographical` (en)</t>
+          <t>`perspetives` (en)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>KG1024</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>`quantitativ` (en)</t>
+          <t>`standarized` (en)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>KG1025</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3106,19 +3106,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>`evolvement` (en)</t>
+          <t>`vations` (en)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>KG1025</t>
+          <t>KG2005</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3133,19 +3133,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>`thise` (en)</t>
+          <t>`qualititative` (en)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>KG3010</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3155,24 +3155,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>`obser` (en)</t>
+          <t>`bjälesjö` (sv)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>KG3010</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3187,19 +3187,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>`perspetives` (en)</t>
+          <t>`recognises` (en)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>KG3011</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3209,24 +3209,24 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>`standarized` (en)</t>
+          <t>`kartöverlägg` (sv)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>KG3011</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3236,24 +3236,24 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>`vations` (en)</t>
+          <t>`skalnivå` (sv)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>KG2005</t>
+          <t>KG3014</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3268,19 +3268,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>`qualititative` (en)</t>
+          <t>`eaxaminer` (en)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>KG3010</t>
+          <t>KG3015</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3290,24 +3290,24 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>`bjälesjö` (sv)</t>
+          <t>`eaxaminer` (en)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>KG3010</t>
+          <t>KG3016</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3317,24 +3317,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>`recognises` (en)</t>
+          <t>`gällade` (sv)</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>KG3011</t>
+          <t>KG3016</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3344,29 +3344,29 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>`kartöverlägg` (sv)</t>
+          <t>`aggregative` (en)</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>KG3011</t>
+          <t>GLP236</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3376,105 +3376,105 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>`skalnivå` (sv)</t>
+          <t>`framträdandeform` (sv)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>KG3014</t>
+          <t>GLP29R</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>`eaxaminer` (en)</t>
+          <t>`flerspårsmaterial` (sv)</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29R</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>KG3015</t>
+          <t>GLP2JZ</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>`eaxaminer` (en)</t>
+          <t>`flerspårsmaterial` (sv)</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2JZ</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>KG3016</t>
+          <t>GLP359</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>`gällade` (sv)</t>
+          <t>`digitalization` (en)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>KG3016</t>
+          <t>GLP359</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3484,19 +3484,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>`aggregative` (en)</t>
+          <t>`djing` (en)</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GLP236</t>
+          <t>GLP3AH</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>`framträdandeform` (sv)</t>
+          <t>`ande` (en)</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GLP29R</t>
+          <t>GLP3AH</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3533,24 +3533,24 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>`flerspårsmaterial` (sv)</t>
+          <t>`excercises` (en)</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GLP2JZ</t>
+          <t>GLP3AR</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3565,19 +3565,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>`flerspårsmaterial` (sv)</t>
+          <t>`tools-miljö` (sv)</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2JZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GLP359</t>
+          <t>GLP3AR</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3592,19 +3592,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>`digitalization` (en)</t>
+          <t>`prouction` (en)</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GLP359</t>
+          <t>LP1032</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3614,24 +3614,24 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>`djing` (en)</t>
+          <t>`fördjupningskod` (sv)</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GLP3AH</t>
+          <t>LP1032</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3646,19 +3646,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>`ande` (en)</t>
+          <t>`scholary` (en)</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GLP3AH</t>
+          <t>LP1032</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3673,19 +3673,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>`excercises` (en)</t>
+          <t>`sumarise` (en)</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GLP3AR</t>
+          <t>LP1054</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3695,24 +3695,24 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>`tools-miljö` (sv)</t>
+          <t>`audiovisuell` (en)</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GLP3AR</t>
+          <t>LP1071</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3722,24 +3722,24 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>`prouction` (en)</t>
+          <t>`erätter` (sv)</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>LP1032</t>
+          <t>LP1071</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3749,24 +3749,24 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>`fördjupningskod` (sv)</t>
+          <t>`evaulates` (en)</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>LP1032</t>
+          <t>LP2012</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3781,19 +3781,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>`scholary` (en)</t>
+          <t>`intiate` (en)</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>LP1032</t>
+          <t>LP2013</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3808,19 +3808,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>`sumarise` (en)</t>
+          <t>`learnings` (en)</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>LP1054</t>
+          <t>LP2013</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3835,78 +3835,78 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>`audiovisuell` (en)</t>
+          <t>`litterature` (en)</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>LP1071</t>
+          <t>GMN3E3</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>`erätter` (sv)</t>
+          <t>`rethoric` (en)</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3E3</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>LP1071</t>
+          <t>GMN3EA</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>`evaulates` (en)</t>
+          <t>`användar` (sv)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EA</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>LP2012</t>
+          <t>GMN3EX</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3916,24 +3916,24 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>`intiate` (en)</t>
+          <t>`desgin` (en)</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EX</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>LP2013</t>
+          <t>GNA2NT</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3943,51 +3943,51 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>`learnings` (en)</t>
+          <t>`assignement` (en)</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2NT</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>LP2013</t>
+          <t>GNA3DA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>`litterature` (en)</t>
+          <t>`tillgångspristeorier` (sv)</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3DA</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GMN3E3</t>
+          <t>GNA3FN</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3997,51 +3997,51 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>`rethoric` (en)</t>
+          <t>`receiva` (en)</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3E3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3FN</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GMN3EA</t>
+          <t>NA1003</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>`användar` (sv)</t>
+          <t>`modigliani` (en)</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1003</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GMN3EX</t>
+          <t>NA1003</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4051,19 +4051,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>`desgin` (en)</t>
+          <t>`scholes` (en)</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1003</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GNA2NT</t>
+          <t>NA1024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4073,24 +4073,24 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>`assignement` (en)</t>
+          <t>`efterfråge` (sv)</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2NT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GNA3DA</t>
+          <t>NA1024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4100,24 +4100,24 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>`tillgångspristeorier` (sv)</t>
+          <t>`distancelectures` (en)</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3DA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GNA3FN</t>
+          <t>NA1025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4132,19 +4132,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>`receiva` (en)</t>
+          <t>`konjunkturinstitutet` (en)</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3FN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1025</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>NA1003</t>
+          <t>NA1026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4154,24 +4154,24 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>`modigliani` (en)</t>
+          <t>`hässel` (sv)</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>NA1003</t>
+          <t>NA1026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4181,24 +4181,24 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>`scholes` (en)</t>
+          <t>`ränteparitetsvillkor` (sv)</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>NA1024</t>
+          <t>NA1026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4213,19 +4213,19 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>`efterfråge` (sv)</t>
+          <t>`studieförb` (sv)</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>NA1024</t>
+          <t>NA1027</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4235,24 +4235,24 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>`distancelectures` (en)</t>
+          <t>`förläsningar` (sv)</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>NA1025</t>
+          <t>NA1027</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4267,19 +4267,19 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>`konjunkturinstitutet` (en)</t>
+          <t>`internetbased` (en)</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>NA1026</t>
+          <t>NA1028</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4294,19 +4294,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>`hässel` (sv)</t>
+          <t>`efterfråge` (sv)</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1028</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>NA1026</t>
+          <t>NA1029</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4316,24 +4316,24 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>`ränteparitetsvillkor` (sv)</t>
+          <t>`differentiat` (en)</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>NA1026</t>
+          <t>NA1030</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4343,24 +4343,24 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>`studieförb` (sv)</t>
+          <t>`excercises` (en)</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>NA1027</t>
+          <t>NA1032</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4370,24 +4370,24 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>`förläsningar` (sv)</t>
+          <t>`descirbe` (en)</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>NA1027</t>
+          <t>NA1035</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4397,24 +4397,24 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>`internetbased` (en)</t>
+          <t>`efterfråge` (sv)</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1035</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>NA1028</t>
+          <t>NA1036</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4424,24 +4424,24 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>`efterfråge` (sv)</t>
+          <t>`longterm` (en)</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>NA1029</t>
+          <t>NA1036</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4456,19 +4456,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>`differentiat` (en)</t>
+          <t>`shortterm` (en)</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>NA1030</t>
+          <t>NA1039</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4483,19 +4483,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>`excercises` (en)</t>
+          <t>`assingments` (en)</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>NA1032</t>
+          <t>NA1039</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4510,19 +4510,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>`descirbe` (en)</t>
+          <t>`externalities` (en)</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>NA1035</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4537,19 +4537,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>`efterfråge` (sv)</t>
+          <t>`kalandermånader` (sv)</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>NA1036</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4564,19 +4564,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>`longterm` (en)</t>
+          <t>`calender` (en)</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>NA1036</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4591,19 +4591,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>`shortterm` (en)</t>
+          <t>`oppobet` (en)</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>NA1039</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4618,19 +4618,19 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>`assingments` (en)</t>
+          <t>`opposnent` (en)</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>NA1039</t>
+          <t>NA2009</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4645,19 +4645,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>`externalities` (en)</t>
+          <t>`resultas` (en)</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>NA3001</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4672,19 +4672,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>`kalandermånader` (sv)</t>
+          <t>`länderjämförelser` (sv)</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>NA3010</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4694,24 +4694,24 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>`calender` (en)</t>
+          <t>`kalandermånader` (sv)</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>NA3011</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4726,78 +4726,78 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>`oppobet` (en)</t>
+          <t>`tobbit` (en)</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>GPE3AJ</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>`opposnent` (en)</t>
+          <t>`kollegialtlärande` (sv)</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>NA2009</t>
+          <t>PE1010</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>`resultas` (en)</t>
+          <t>`elfström` (sv)</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>NA3001</t>
+          <t>PE1010</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4807,24 +4807,24 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>`länderjämförelser` (sv)</t>
+          <t>`göteborg` (sv)</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>NA3010</t>
+          <t>PE1010</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4834,46 +4834,46 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>`kalandermånader` (sv)</t>
+          <t>`linköpings` (sv)</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>NA3011</t>
+          <t>PE1010</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>`tobbit` (en)</t>
+          <t>`lpfö` (sv)</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>GPE3AJ</t>
+          <t>PE1010</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>`kollegialtlärande` (sv)</t>
+          <t>`löfdahl` (sv)</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
         </is>
       </c>
     </row>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>`elfström` (sv)</t>
+          <t>`norrköping` (sv)</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>`göteborg` (sv)</t>
+          <t>`åberg` (sv)</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -4954,7 +4954,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>PE1010</t>
+          <t>PE1011</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4969,19 +4969,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>`linköpings` (sv)</t>
+          <t>`hög-skolepoäng` (sv)</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1011</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>PE1010</t>
+          <t>PE1020</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4991,24 +4991,24 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>`lpfö` (sv)</t>
+          <t>`gryndsyn` (en)</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>PE1010</t>
+          <t>PE1021</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5018,24 +5018,24 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>`löfdahl` (sv)</t>
+          <t>`centrum` (en)</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1021</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>PE1010</t>
+          <t>PE1021</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5045,24 +5045,24 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>`norrköping` (sv)</t>
+          <t>`grund` (en)</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1021</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>PE1010</t>
+          <t>PE1023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5077,19 +5077,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>`åberg` (sv)</t>
+          <t>`lärarlagsarbete` (sv)</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>PE1011</t>
+          <t>PE1023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5104,19 +5104,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>`hög-skolepoäng` (sv)</t>
+          <t>`rättsäkerhet` (sv)</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>PE1020</t>
+          <t>PE1054</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5126,24 +5126,24 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>`gryndsyn` (en)</t>
+          <t>`lärstrategier` (sv)</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>PE1021</t>
+          <t>PE1064</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5153,24 +5153,24 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>`centrum` (en)</t>
+          <t>`rättsäkerhetsproblematiken` (sv)</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1064</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>PE1021</t>
+          <t>PE1067</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5180,24 +5180,24 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>`grund` (en)</t>
+          <t>`att` — ….m. 2013-11-13.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>PE1023</t>
+          <t>PE1068</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5212,19 +5212,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>`lärarlagsarbete` (sv)</t>
+          <t>`känndom` (sv)</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>PE1023</t>
+          <t>PE2005</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5234,24 +5234,24 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>`rättsäkerhet` (sv)</t>
+          <t>`gryndsyn` (en)</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>PE1054</t>
+          <t>PE3004</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5266,19 +5266,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>`lärstrategier` (sv)</t>
+          <t>`högskole-mässighet` (sv)</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>PE1064</t>
+          <t>PE3004</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5293,19 +5293,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>`rättsäkerhetsproblematiken` (sv)</t>
+          <t>`lärarlagsarbete` (sv)</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>PE1067</t>
+          <t>PE3004</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5315,110 +5315,110 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>`att` — ….m. 2013-11-13.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
+          <t>`rättsäkerhet` (sv)</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>PE1068</t>
+          <t>GPA2FW</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>`känndom` (sv)</t>
+          <t>`managemet` (en)</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>PE2005</t>
+          <t>GPA2R6</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>`gryndsyn` (en)</t>
+          <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>PE3004</t>
+          <t>GPA353</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>`högskole-mässighet` (sv)</t>
+          <t>`valuest` (en)</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA353</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>PE3004</t>
+          <t>APG24E</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5428,24 +5428,24 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>`lärarlagsarbete` (sv)</t>
+          <t>`inlämingsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>PE3004</t>
+          <t>APG25N</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5455,24 +5455,24 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>`rättsäkerhet` (sv)</t>
+          <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>GPA2FW</t>
+          <t>APG29G</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5482,24 +5482,24 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>`managemet` (en)</t>
+          <t>`asignments` (en)</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG29G</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>GPA2R6</t>
+          <t>APG2AA</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5509,24 +5509,24 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>`tillvägagångsätt` (sv)</t>
+          <t>`lärarskicklighetetens` (sv)</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GPA353</t>
+          <t>APG2AC</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5536,19 +5536,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>`valuest` (en)</t>
+          <t>`aanalyze` (en)</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA353</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>APG24E</t>
+          <t>APG2AC</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5558,24 +5558,24 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>`inlämingsuppgifter` (sv)</t>
+          <t>`nalyze` (en)</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>APG25N</t>
+          <t>APG2AC</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5585,24 +5585,24 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>`tillvägagångsätt` (sv)</t>
+          <t>`rincipal` (en)</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>APG29G</t>
+          <t>APG2C3</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5617,19 +5617,19 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>`asignments` (en)</t>
+          <t>`practies` (en)</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG29G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>APG2AA</t>
+          <t>APG2CC</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5644,19 +5644,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>`lärarskicklighetetens` (sv)</t>
+          <t>`lärar-elevrelationer` (sv)</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>APG2AC</t>
+          <t>APG2CD</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5666,24 +5666,24 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>`aanalyze` (en)</t>
+          <t>`lärarprofessionsspecifika` (sv)</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>APG2AC</t>
+          <t>APG2CD</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5698,19 +5698,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>`nalyze` (en)</t>
+          <t>`practicies` (en)</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>APG2AC</t>
+          <t>APG2CM</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5720,24 +5720,24 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>`rincipal` (en)</t>
+          <t>`undervisningensmål` (sv)</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>APG2C3</t>
+          <t>APG2CM</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5752,19 +5752,19 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>`practies` (en)</t>
+          <t>`pratice` (en)</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>APG2CC</t>
+          <t>GPG22K</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5774,24 +5774,24 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>`lärar-elevrelationer` (sv)</t>
+          <t>`conciderations` (en)</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>APG2CD</t>
+          <t>GPG27X</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5806,19 +5806,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>`lärarprofessionsspecifika` (sv)</t>
+          <t>`lärar` (sv)</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>APG2CD</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5828,24 +5828,24 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>`practicies` (en)</t>
+          <t>`samhällorienterande` (sv)</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>APG2CM</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5855,24 +5855,24 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>`undervisningensmål` (sv)</t>
+          <t>`hinduism` (en)</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>APG2CM</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5887,19 +5887,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>`pratice` (en)</t>
+          <t>`judaism` (en)</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>GPG22K</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5914,19 +5914,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>`conciderations` (en)</t>
+          <t>`sociaty` (en)</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>GPG27X</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5936,24 +5936,24 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>`lärar` (sv)</t>
+          <t>`understandingn` (en)</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5963,24 +5963,24 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>`samhällorienterande` (sv)</t>
+          <t>`systematising` (en)</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GPG328</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5990,24 +5990,24 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>`hinduism` (en)</t>
+          <t>`andraämne` (sv)</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GPG329</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6017,24 +6017,24 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>`judaism` (en)</t>
+          <t>`andraämne` (sv)</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GPG3AD</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6044,24 +6044,24 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>`sociaty` (en)</t>
+          <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GPG3CG</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6076,19 +6076,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>`understandingn` (en)</t>
+          <t>`perspecitves` (en)</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>GPG3CK</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6098,24 +6098,24 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>`systematising` (en)</t>
+          <t>`inlämninguppgift` (sv)</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>GPG328</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6130,19 +6130,19 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>`andraämne` (sv)</t>
+          <t>`samhällorienterande` (sv)</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>GPG329</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6152,24 +6152,24 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>`andraämne` (sv)</t>
+          <t>`sociaty` (en)</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>GPG3AD</t>
+          <t>GPG3FR</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6179,24 +6179,24 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
+          <t>`progamme` (en)</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>GPG3CG</t>
+          <t>GPG3FU</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6211,19 +6211,19 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>`perspecitves` (en)</t>
+          <t>`developement` (en)</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>GPG3CK</t>
+          <t>GPG3FU</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6233,24 +6233,24 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>`inlämninguppgift` (sv)</t>
+          <t>`evalution` (en)</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6260,24 +6260,24 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>`samhällorienterande` (sv)</t>
+          <t>`antagna` (en)</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6292,19 +6292,19 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>`sociaty` (en)</t>
+          <t>`att` (en)</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>GPG3FR</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6319,19 +6319,19 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>`progamme` (en)</t>
+          <t>`dessutom` (en)</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>GPG3FU</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6346,19 +6346,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>`developement` (en)</t>
+          <t>`fritidshem` (en)</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>GPG3FU</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>`evalution` (en)</t>
+          <t>`hela` (en)</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>`antagna` (en)</t>
+          <t>`inriktningen` (en)</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>`att` (en)</t>
+          <t>`specialiseringar` (en)</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>`dessutom` (en)</t>
+          <t>`studenten` (en)</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>`fritidshem` (en)</t>
+          <t>`studerande` (en)</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>`hela` (en)</t>
+          <t>`tidigare` (en)</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -6520,7 +6520,7 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>PG3024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6535,19 +6535,19 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>`inriktningen` (en)</t>
+          <t>`inklusive` (en)</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>PG3024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -6562,19 +6562,19 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>`specialiseringar` (en)</t>
+          <t>`kurs` (en)</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>PG3024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -6589,19 +6589,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>`studenten` (en)</t>
+          <t>`tematisk` (en)</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>PG3024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6616,24 +6616,24 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>`studerande` (en)</t>
+          <t>`utveckling` (en)</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>ARK26T</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6643,24 +6643,24 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>`tidigare` (en)</t>
+          <t>`chassidism` (en)</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>ARK26T</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -6670,24 +6670,24 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>`inklusive` (en)</t>
+          <t>`esotericism` (en)</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>ARK26T</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6697,24 +6697,24 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>`kurs` (en)</t>
+          <t>`jewish` (en)</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>ARK26T</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6724,24 +6724,24 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>`tematisk` (en)</t>
+          <t>`kabbalistic` (en)</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>ARK27Q</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -6751,19 +6751,19 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>`utveckling` (en)</t>
+          <t>`canaan` (en)</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>ARK26T</t>
+          <t>ARK27Q</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6778,19 +6778,19 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>`chassidism` (en)</t>
+          <t>`civilising` (en)</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>ARK26T</t>
+          <t>ARK27Q</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6805,19 +6805,19 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>`esotericism` (en)</t>
+          <t>`mesopotamia` (en)</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>ARK26T</t>
+          <t>ARK27Q</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6832,19 +6832,19 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>`jewish` (en)</t>
+          <t>`tha` (en)</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>ARK26T</t>
+          <t>ARK29K</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6859,19 +6859,19 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>`kabbalistic` (en)</t>
+          <t>`cpecialisation` (en)</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29K</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>ARK29L</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6881,24 +6881,24 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>`canaan` (en)</t>
+          <t>`markonivå` (sv)</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29L</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>GRK323</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6913,19 +6913,19 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>`civilising` (en)</t>
+          <t>`jerusalem` (en)</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK323</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>GRK366</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6940,19 +6940,19 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>`mesopotamia` (en)</t>
+          <t>`enivronments` (en)</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK366</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>GRK3B4</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6962,24 +6962,24 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>`tha` (en)</t>
+          <t>`ämesteoretiska` (sv)</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>ARK29K</t>
+          <t>RK3043</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6989,29 +6989,29 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>`cpecialisation` (en)</t>
+          <t>`vernakulär` (sv)</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>ARK29L</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7021,78 +7021,78 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>`markonivå` (sv)</t>
+          <t>`mervärdskatt` (sv)</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>GRK323</t>
+          <t>GRV2MK</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>`jerusalem` (en)</t>
+          <t>`innhåller` (sv)</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK323</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>GRK366</t>
+          <t>RV1001</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>`enivronments` (en)</t>
+          <t>`glavå` (sv)</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK366</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>GRK3B4</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -7102,46 +7102,46 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>`ämesteoretiska` (sv)</t>
+          <t>`mervärdskatt` (sv)</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>RK3043</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>`vernakulär` (sv)</t>
+          <t>`taxat` (en)</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>RV1004</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7156,19 +7156,19 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>`mervärdskatt` (sv)</t>
+          <t>`åke` (sv)</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>GRV2MK</t>
+          <t>RV1009</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7183,19 +7183,19 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>`innhåller` (sv)</t>
+          <t>`eg-rättslig` (sv)</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>RV1001</t>
+          <t>RV1009</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7210,19 +7210,19 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>`glavå` (sv)</t>
+          <t>`eg-rättsliga` (sv)</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7237,19 +7237,19 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>`mervärdskatt` (sv)</t>
+          <t>`glavå` (sv)</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7264,19 +7264,19 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>`taxat` (en)</t>
+          <t>`bargening` (en)</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>RV1004</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7291,19 +7291,19 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>`åke` (sv)</t>
+          <t>`obestånds` (sv)</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>RV1009</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7313,24 +7313,24 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>`eg-rättslig` (sv)</t>
+          <t>`pratices` (en)</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>RV1009</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -7340,24 +7340,24 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>`eg-rättsliga` (sv)</t>
+          <t>`securites` (en)</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -7372,19 +7372,19 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>`glavå` (sv)</t>
+          <t>`clevesköld` (sv)</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -7394,24 +7394,24 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>`bargening` (en)</t>
+          <t>`förvaltningsrättliga` (sv)</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -7426,19 +7426,19 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>`obestånds` (sv)</t>
+          <t>`rättsäkerheten` (sv)</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -7453,19 +7453,19 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>`pratices` (en)</t>
+          <t>`xxxxxxxxxxx` (en)</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -7480,19 +7480,19 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>`securites` (en)</t>
+          <t>`xxxxxxxxxxxxx` (en)</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>RV1045</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -7507,19 +7507,19 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>`clevesköld` (sv)</t>
+          <t>`åtgärdscheman` (sv)</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>RV1050</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -7534,19 +7534,19 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>`förvaltningsrättliga` (sv)</t>
+          <t>`eu-rätten` (sv)</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>RV1055</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -7556,29 +7556,29 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>`rättsäkerheten` (sv)</t>
+          <t>`samt` — …aminationsformer  En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,…</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>ASK22L</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -7588,24 +7588,24 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>`xxxxxxxxxxx` (en)</t>
+          <t>`formes` (en)</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>ASK22L</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -7615,100 +7615,100 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>`xxxxxxxxxxxxx` (en)</t>
+          <t>`modus` (en)</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>RV1045</t>
+          <t>ASK22L</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>`åtgärdscheman` (sv)</t>
+          <t>`operandi` (en)</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>RV1050</t>
+          <t>ASK22M</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>`eu-rätten` (sv)</t>
+          <t>`reviewscrutiny` (en)</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>RV1055</t>
+          <t>ASK289</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>`samt` — …aminationsformer  En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,…</t>
+          <t>`adress` (en)</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>ASK22L</t>
+          <t>ASK289</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -7723,19 +7723,19 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>`formes` (en)</t>
+          <t>`compative` (en)</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>ASK22L</t>
+          <t>SK1050</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -7745,24 +7745,24 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>`modus` (en)</t>
+          <t>`europarådet` (sv)</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>ASK22L</t>
+          <t>SK1054</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -7777,19 +7777,19 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>`operandi` (en)</t>
+          <t>`problematique` (en)</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1054</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>ASK22M</t>
+          <t>SK1055</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -7804,51 +7804,51 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>`reviewscrutiny` (en)</t>
+          <t>`interconnectedness` (en)</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1055</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>ASK289</t>
+          <t>GSO2PL</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>`adress` (en)</t>
+          <t>`credits` — …7.5 credits, Psychological Perspectives on Social Work 7.5 credits credits and Welfare Measures and User Perspective 15 credits…</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>ASK289</t>
+          <t>SO1027</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -7858,51 +7858,51 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>`compative` (en)</t>
+          <t>`abilty` (en)</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>SK1050</t>
+          <t>SO1027</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>`europarådet` (sv)</t>
+          <t>`constructivism` (en)</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>SK1054</t>
+          <t>SO1027</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -7912,78 +7912,78 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>`problematique` (en)</t>
+          <t>`interactionism` (en)</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>SK1055</t>
+          <t>ATR26B</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>`interconnectedness` (en)</t>
+          <t>`hållbarbetsmål` (sv)</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>GSO2PL</t>
+          <t>ATR2BJ</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>`credits` — …7.5 credits, Psychological Perspectives on Social Work 7.5 credits credits and Welfare Measures and User Perspective 15 credits…</t>
+          <t>`leaisure` (en)</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>SO1027</t>
+          <t>ATR2BJ</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -7993,73 +7993,73 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>`abilty` (en)</t>
+          <t>`uns` (en)</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>SO1027</t>
+          <t>GTR22D</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>`constructivism` (en)</t>
+          <t>`samhållsvetenskap` (sv)</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>SO1027</t>
+          <t>GTR22D</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>`interactionism` (en)</t>
+          <t>`värderigsförmåga` (sv)</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>ATR26B</t>
+          <t>GTR265</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8074,19 +8074,19 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>`hållbarbetsmål` (sv)</t>
+          <t>`fömåga` (sv)</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>ATR2BJ</t>
+          <t>GTR265</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8101,19 +8101,19 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>`leaisure` (en)</t>
+          <t>`afte` (en)</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>ATR2BJ</t>
+          <t>GTR26E</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8123,24 +8123,24 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>`uns` (en)</t>
+          <t>`erätter` (sv)</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>GTR22D</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8155,19 +8155,19 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>`samhållsvetenskap` (sv)</t>
+          <t>`förhållningssät` (sv)</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>GTR22D</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8177,24 +8177,24 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>`värderigsförmåga` (sv)</t>
+          <t>`assignement` (en)</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>GTR265</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8204,24 +8204,24 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>`fömåga` (sv)</t>
+          <t>`implmented` (en)</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>GTR265</t>
+          <t>GTR2DG</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -8231,24 +8231,24 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>`afte` (en)</t>
+          <t>`the` — …earch. The course is organised into two parts. In part one, the The course introduces students to quantitative research. The co…</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>GTR26E</t>
+          <t>GTR2DG</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -8263,19 +8263,19 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>`erätter` (sv)</t>
+          <t>`enkätsstudie` (sv)</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>GTR2DP</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -8290,19 +8290,19 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>`förhållningssät` (sv)</t>
+          <t>`värderingsfömåga` (sv)</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>GTR3B6</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -8312,24 +8312,24 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>`assignement` (en)</t>
+          <t>`sälenfjällen` (sv)</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3B6</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>GTR3D7</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -8344,19 +8344,19 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>`implmented` (en)</t>
+          <t>`kungliga` (en)</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3D7</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -8366,24 +8366,24 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>`the` — …earch. The course is organised into two parts. In part one, the The course introduces students to quantitative research. The co…</t>
+          <t>`recourses` (en)</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -8398,19 +8398,19 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>`enkätsstudie` (sv)</t>
+          <t>`använding` (sv)</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>GTR2DP</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -8420,24 +8420,24 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>`värderingsfömåga` (sv)</t>
+          <t>`lerning` (en)</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>GTR3B6</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -8447,24 +8447,24 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>`sälenfjällen` (sv)</t>
+          <t>`powerpoint` (en)</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3B6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>GTR3D7</t>
+          <t>TR1018</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -8479,19 +8479,19 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>`kungliga` (en)</t>
+          <t>`geodemographic` (en)</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3D7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>TR1024</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -8501,24 +8501,24 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>`recourses` (en)</t>
+          <t>`fömåga` (sv)</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>TR1013</t>
+          <t>TR1024</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -8528,24 +8528,24 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>`använding` (sv)</t>
+          <t>`afte` (en)</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>TR1013</t>
+          <t>TR1025</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -8560,19 +8560,19 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>`lerning` (en)</t>
+          <t>`studiesand` (en)</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>TR1013</t>
+          <t>TR1027</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -8582,24 +8582,24 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>`powerpoint` (en)</t>
+          <t>`fömåga` (sv)</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>TR1018</t>
+          <t>TR1027</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -8614,19 +8614,19 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>`geodemographic` (en)</t>
+          <t>`afte` (en)</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>TR1024</t>
+          <t>TR1028</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -8641,19 +8641,19 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>`fömåga` (sv)</t>
+          <t>`förhållningssät` (sv)</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>TR1024</t>
+          <t>TR1028</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -8668,19 +8668,19 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>`afte` (en)</t>
+          <t>`ansd` (en)</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>TR1025</t>
+          <t>TR1029</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -8700,14 +8700,14 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>TR1027</t>
+          <t>TR1030</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -8722,19 +8722,19 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>`fömåga` (sv)</t>
+          <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>TR1027</t>
+          <t>TR1031</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -8744,24 +8744,24 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>`afte` (en)</t>
+          <t>`kulturellafördomar` (sv)</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>TR1028</t>
+          <t>TR1034</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -8776,19 +8776,19 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>`förhållningssät` (sv)</t>
+          <t>`förvärvda` (sv)</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>TR1028</t>
+          <t>TR1034</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -8803,19 +8803,19 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>`ansd` (en)</t>
+          <t>`organisaton` (en)</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>TR1029</t>
+          <t>TR2004</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -8830,19 +8830,19 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>`studiesand` (en)</t>
+          <t>`stuides` (en)</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>TR1030</t>
+          <t>TR3006</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -8852,24 +8852,24 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>`tillvägagångsätt` (sv)</t>
+          <t>`the` — …- Independently identify and analyze scientific problems in the the relevant field of knowledge and conduct and report on a pro…</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>TR1031</t>
+          <t>TR3006</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -8884,51 +8884,51 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>`kulturellafördomar` (sv)</t>
+          <t>`ocskå` (sv)</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>TR1034</t>
+          <t>AS2002</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>`förvärvda` (sv)</t>
+          <t>`takenup` (en)</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>TR1034</t>
+          <t>AS3002</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -8938,78 +8938,78 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>`organisaton` (en)</t>
+          <t>`teh` (en)</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>TR2004</t>
+          <t>AS3009</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>`stuides` (en)</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>TR3006</t>
+          <t>AS3012</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>`the` — …- Independently identify and analyze scientific problems in the the relevant field of knowledge and conduct and report on a pro…</t>
+          <t>`outlineof` (en)</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>TR3006</t>
+          <t>AS4001</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -9019,19 +9019,19 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>`ocskå` (sv)</t>
+          <t>`mastersnivå` (sv)</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>AS2002</t>
+          <t>AS4003</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -9041,157 +9041,22 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>`takenup` (en)</t>
+          <t>`angrepssätt` (sv)</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="2" t="inlineStr">
-        <is>
-          <t>AS3002</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>`teh` (en)</t>
-        </is>
-      </c>
-      <c r="E320" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" s="2" t="inlineStr">
-        <is>
-          <t>AS3009</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>`literära` (sv)</t>
-        </is>
-      </c>
-      <c r="E321" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" s="2" t="inlineStr">
-        <is>
-          <t>AS3012</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>`outlineof` (en)</t>
-        </is>
-      </c>
-      <c r="E322" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="2" t="inlineStr">
-        <is>
-          <t>AS4001</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>`mastersnivå` (sv)</t>
-        </is>
-      </c>
-      <c r="E323" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" s="2" t="inlineStr">
-        <is>
-          <t>AS4003</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>`angrepssätt` (sv)</t>
-        </is>
-      </c>
-      <c r="E324" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E324"/>
+  <autoFilter ref="A1:E319"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -9829,16 +9694,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E318" r:id="rId634"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A319" r:id="rId635"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E319" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A320" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E320" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A321" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E321" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A322" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E322" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A323" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E323" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A324" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E324" r:id="rId646"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$319</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$250</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E319"/>
+  <dimension ref="A1:E250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -634,27 +634,27 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AB3001</t>
+          <t>ABQ2AM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`sölvell` (sv)</t>
+          <t>`inludes` (en)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`inludes` (en)</t>
+          <t>`managment` (en)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ABQ2AM</t>
+          <t>ABQ2B4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -698,24 +698,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`managment` (en)</t>
+          <t>`en` — …- formulera och muntligt framföra konstruktiv kritik på en en text av vetenskaplig karaktär    - vetenskapligt värdera oc…</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2B4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ABQ2B4</t>
+          <t>BQ1079</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -725,17 +725,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`en` — …- formulera och muntligt framföra konstruktiv kritik på en en text av vetenskaplig karaktär    - vetenskapligt värdera oc…</t>
+          <t>`devolop` (en)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ1079</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`devolop` (en)</t>
+          <t>`strucuring` (en)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>BQ1079</t>
+          <t>BQ2018</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -779,24 +779,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`strucuring` (en)</t>
+          <t>`lärarare` (sv)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ1079</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2018</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>BQ2018</t>
+          <t>BQ2057</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -806,24 +806,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`lärarare` (sv)</t>
+          <t>`postproduction` (en)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2057</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>BQ2018</t>
+          <t>GBQ29D</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -838,19 +838,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`filmic` (en)</t>
+          <t>`undergradaute` (en)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29D</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>BQ2057</t>
+          <t>GBQ29E</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -865,19 +865,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`postproduction` (en)</t>
+          <t>`undergradaute` (en)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2057</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29E</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GBQ29D</t>
+          <t>GBQ2U6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -887,24 +887,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`undergradaute` (en)</t>
+          <t>`användar` (sv)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GBQ29E</t>
+          <t>GBQ2U6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -914,24 +914,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`undergradaute` (en)</t>
+          <t>`beställningsfilmsproduktion` (sv)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U6</t>
+          <t>GBQ2UB</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -946,19 +946,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`användar` (sv)</t>
+          <t>`berättandestruktur` (sv)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UB</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U6</t>
+          <t>GBQ2WH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -968,24 +968,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`beställningsfilmsproduktion` (sv)</t>
+          <t>`tbt` (en)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WH</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GBQ2UB</t>
+          <t>GBQ2WK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1000,19 +1000,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`berättandestruktur` (sv)</t>
+          <t>`berätttarelement` (sv)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WK</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GBQ2WH</t>
+          <t>GBQ36K</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`tbt` (en)</t>
+          <t>`praktical` (en)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36K</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GBQ2WK</t>
+          <t>GBQ36K</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1049,24 +1049,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`berätttarelement` (sv)</t>
+          <t>`thery` (en)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36K</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GBQ36K</t>
+          <t>GBQ38V</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1076,24 +1076,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`praktical` (en)</t>
+          <t>`mediacomposer-miljö` (sv)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38V</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GBQ36K</t>
+          <t>GBQ38W</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1103,24 +1103,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`thery` (en)</t>
+          <t>`composer-miljö` (sv)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GBQ38V</t>
+          <t>GBQ38W</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`mediacomposer-miljö` (sv)</t>
+          <t>`höguppupplöst` (sv)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`composer-miljö` (sv)</t>
+          <t>`avanced` (en)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1174,7 +1174,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GBQ38W</t>
+          <t>GBQ38X</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`höguppupplöst` (sv)</t>
+          <t>`documetnary` (en)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GBQ38W</t>
+          <t>GBQ38X</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,12 +1216,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`avanced` (en)</t>
+          <t>`filmproject` (en)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`documetnary` (en)</t>
+          <t>`histrorical` (en)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GBQ38X</t>
+          <t>GBQ3A6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1265,24 +1265,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`filmproject` (en)</t>
+          <t>`användar` (sv)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GBQ38X</t>
+          <t>GBQ3A7</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1292,24 +1292,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`histrorical` (en)</t>
+          <t>`wars-berättelserna` (sv)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A6</t>
+          <t>GBQ3A7</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`användar` (sv)</t>
+          <t>`wars-berättelsernas` (sv)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A7</t>
+          <t>GBQ3AW</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1346,24 +1346,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`wars-berättelserna` (sv)</t>
+          <t>`explainer` (en)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A7</t>
+          <t>GBQ3FG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1373,56 +1373,56 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`wars-berättelsernas` (sv)</t>
+          <t>`excercises` (en)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AA</t>
+          <t>EU1027</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`ideational` (en)</t>
+          <t>`grundäggande` (sv)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1027</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AV</t>
+          <t>EU1033</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`multimodality` (en)</t>
+          <t>`itssocial` (en)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1033</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AW</t>
+          <t>EU1034</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`explainer` (en)</t>
+          <t>`förhandlingprocesser` (sv)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1034</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GBQ3FG</t>
+          <t>GEU2KV</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1486,19 +1486,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`excercises` (en)</t>
+          <t>`opportunties` (en)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>EU1027</t>
+          <t>GEU2KV</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1508,29 +1508,29 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`grundäggande` (sv)</t>
+          <t>`willll` (en)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>EU1033</t>
+          <t>AFI273</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1540,51 +1540,51 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`itssocial` (en)</t>
+          <t>`contignency` (en)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFI273</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>EU1034</t>
+          <t>FI1023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`förhandlingprocesser` (sv)</t>
+          <t>`philosohical` (en)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GEU2KV</t>
+          <t>FI1024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1594,46 +1594,46 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`opportunties` (en)</t>
+          <t>`etichs` (en)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GEU2KV</t>
+          <t>FI1039</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`willll` (en)</t>
+          <t>`have` — …urthermore, on completion of the course, the student should have have the ability to :       - be reflective in relation to probl…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>AFI273</t>
+          <t>FI1039</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1648,19 +1648,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`contignency` (en)</t>
+          <t>`asessment` (en)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFI273</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>FI1023</t>
+          <t>FI1039</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`philosohical` (en)</t>
+          <t>`developement` (en)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>FI1024</t>
+          <t>FI2003</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1702,19 +1702,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`etichs` (en)</t>
+          <t>`filosofi` (en)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>FI1039</t>
+          <t>GFI3BT</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1724,24 +1724,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`have` — …urthermore, on completion of the course, the student should have have the ability to :       - be reflective in relation to probl…</t>
+          <t>`introdcution` (en)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>FI1039</t>
+          <t>GFI3BT</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`asessment` (en)</t>
+          <t>`througout` (en)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>FI1039</t>
+          <t>GFI3BU</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1783,51 +1783,51 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`developement` (en)</t>
+          <t>`througout` (en)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>FI2003</t>
+          <t>AHI272</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`avklarade` (en)</t>
+          <t>`europeiskspråkiga` (sv)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>FI2003</t>
+          <t>AHI272</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1837,24 +1837,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`filosofi` (en)</t>
+          <t>`poitical` (en)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>FI2003</t>
+          <t>AHI29Q</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`uppsats` (en)</t>
+          <t>`consultaion` (en)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>FI2003</t>
+          <t>AHI29Q</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`vara` (en)</t>
+          <t>`situatin` (en)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>FI2003</t>
+          <t>AS2005</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1918,51 +1918,51 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`varav` (en)</t>
+          <t>`takenup` (en)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2005</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GFI3BT</t>
+          <t>AS3017</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`introdcution` (en)</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GFI3BT</t>
+          <t>AS3020</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`througout` (en)</t>
+          <t>`outlineof` (en)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GFI3BU</t>
+          <t>AS3022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1999,19 +1999,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`througout` (en)</t>
+          <t>`teh` (en)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>AHI272</t>
+          <t>GHI29Y</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2026,19 +2026,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`europeiskspråkiga` (sv)</t>
+          <t>`innhållet` (sv)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>AHI272</t>
+          <t>GHI33T</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2048,24 +2048,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`poitical` (en)</t>
+          <t>`problemförmuleringsförmåga` (sv)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>AHI29Q</t>
+          <t>GHI33V</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2075,24 +2075,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`consultaion` (en)</t>
+          <t>`delkurseninnehåller` (sv)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>AHI29Q</t>
+          <t>GHI33V</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2102,24 +2102,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`situatin` (en)</t>
+          <t>`godkäng` (sv)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>AS2005</t>
+          <t>GHI35A</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2129,24 +2129,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`takenup` (en)</t>
+          <t>`analyseratmänniskors` (sv)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>AS3017</t>
+          <t>GHI35A</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2161,19 +2161,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`literära` (sv)</t>
+          <t>`medförintelsen` (sv)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>AS3020</t>
+          <t>GHI35A</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2183,24 +2183,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`outlineof` (en)</t>
+          <t>`människorsagerande` (sv)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>AS3022</t>
+          <t>GHI362</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2210,24 +2210,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`teh` (en)</t>
+          <t>`självstänigt` (sv)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GHI29Y</t>
+          <t>HI1008</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2237,24 +2237,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`innhållet` (sv)</t>
+          <t>`criterions` (en)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GHI33T</t>
+          <t>HI2011</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2269,19 +2269,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`problemförmuleringsförmåga` (sv)</t>
+          <t>`historiedidaktikområdet` (sv)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GHI33V</t>
+          <t>HI2012</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2296,19 +2296,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`delkurseninnehåller` (sv)</t>
+          <t>`sjävvalt` (sv)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GHI33V</t>
+          <t>HI2016</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2323,19 +2323,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`godkäng` (sv)</t>
+          <t>`sjävvalt` (sv)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GHI35A</t>
+          <t>HI3019</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,132 +2350,132 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`analyseratmänniskors` (sv)</t>
+          <t>`självständg` (sv)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3019</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GHI35A</t>
+          <t>AKG27R</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`medförintelsen` (sv)</t>
+          <t>`compulsotry` (en)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GHI35A</t>
+          <t>AKG27R</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`människorsagerande` (sv)</t>
+          <t>`curent` (en)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GHI362</t>
+          <t>AKG27R</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`självstänigt` (sv)</t>
+          <t>`theoretica` (en)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GHI362</t>
+          <t>GKG3AT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`metod` (en)</t>
+          <t>`tilllämpas` (sv)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>HI1008</t>
+          <t>GKG3AT</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2485,78 +2485,78 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`criterions` (en)</t>
+          <t>`writtten` (en)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>HI2011</t>
+          <t>KG1016</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`historiedidaktikområdet` (sv)</t>
+          <t>`datalaborations` (en)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>HI2012</t>
+          <t>KG1020</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`sjävvalt` (sv)</t>
+          <t>`assignements` (en)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1020</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>HI2016</t>
+          <t>KG1024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2566,46 +2566,46 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`sjävvalt` (sv)</t>
+          <t>`beräklningstung` (sv)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>HI3019</t>
+          <t>KG1024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`självständg` (sv)</t>
+          <t>`quantitativ` (en)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>AKG27R</t>
+          <t>KG1025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2620,19 +2620,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`compulsotry` (en)</t>
+          <t>`evolvement` (en)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>AKG27R</t>
+          <t>KG1025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2647,19 +2647,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`curent` (en)</t>
+          <t>`thise` (en)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>AKG27R</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2674,19 +2674,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`theoretica` (en)</t>
+          <t>`obser` (en)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GKG3AT</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2696,24 +2696,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`tilllämpas` (sv)</t>
+          <t>`perspetives` (en)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GKG3AT</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2728,19 +2728,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`writtten` (en)</t>
+          <t>`standarized` (en)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>KG1005</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2750,24 +2750,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`nyström` (sv)</t>
+          <t>`vations` (en)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>KG1016</t>
+          <t>KG2005</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2782,19 +2782,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`datalaborations` (en)</t>
+          <t>`qualititative` (en)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>KG1020</t>
+          <t>KG3010</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2809,19 +2809,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`assignements` (en)</t>
+          <t>`recognises` (en)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>KG1022</t>
+          <t>KG3011</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2831,24 +2831,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`attractivity` (en)</t>
+          <t>`kartöverlägg` (sv)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>KG1024</t>
+          <t>KG3011</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2863,19 +2863,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`beräklningstung` (sv)</t>
+          <t>`skalnivå` (sv)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>KG1024</t>
+          <t>KG3014</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2890,19 +2890,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`chorological` (en)</t>
+          <t>`eaxaminer` (en)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>KG1024</t>
+          <t>KG3015</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2917,19 +2917,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`demographical` (en)</t>
+          <t>`eaxaminer` (en)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>KG1024</t>
+          <t>KG3016</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2939,110 +2939,110 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`quantitativ` (en)</t>
+          <t>`gällade` (sv)</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>KG1025</t>
+          <t>GLP236</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`evolvement` (en)</t>
+          <t>`framträdandeform` (sv)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>KG1025</t>
+          <t>GLP29R</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`thise` (en)</t>
+          <t>`flerspårsmaterial` (sv)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29R</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>GLP2JZ</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`obser` (en)</t>
+          <t>`flerspårsmaterial` (sv)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2JZ</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>GLP359</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>`perspetives` (en)</t>
+          <t>`djing` (en)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>GLP3AH</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>`standarized` (en)</t>
+          <t>`ande` (en)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>GLP3AH</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3106,186 +3106,186 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>`vations` (en)</t>
+          <t>`excercises` (en)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>KG2005</t>
+          <t>GLP3AR</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>`qualititative` (en)</t>
+          <t>`tools-miljö` (sv)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>KG3010</t>
+          <t>GLP3AR</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>`bjälesjö` (sv)</t>
+          <t>`prouction` (en)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>KG3010</t>
+          <t>LP1032</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>`recognises` (en)</t>
+          <t>`fördjupningskod` (sv)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>KG3011</t>
+          <t>LP1032</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>`kartöverlägg` (sv)</t>
+          <t>`scholary` (en)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>KG3011</t>
+          <t>LP1032</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>`skalnivå` (sv)</t>
+          <t>`sumarise` (en)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>KG3014</t>
+          <t>LP1071</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>`eaxaminer` (en)</t>
+          <t>`erätter` (sv)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>KG3015</t>
+          <t>LP1071</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3295,51 +3295,51 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>`eaxaminer` (en)</t>
+          <t>`evaulates` (en)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>KG3016</t>
+          <t>LP2012</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>`gällade` (sv)</t>
+          <t>`intiate` (en)</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>KG3016</t>
+          <t>LP2013</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3349,19 +3349,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>`aggregative` (en)</t>
+          <t>`learnings` (en)</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GLP236</t>
+          <t>LP2013</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3371,56 +3371,56 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>`framträdandeform` (sv)</t>
+          <t>`litterature` (en)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GLP29R</t>
+          <t>GMN3E3</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>`flerspårsmaterial` (sv)</t>
+          <t>`rethoric` (en)</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3E3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GLP2JZ</t>
+          <t>GMN3EA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>`flerspårsmaterial` (sv)</t>
+          <t>`användar` (sv)</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2JZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EA</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GLP359</t>
+          <t>GMN3EX</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>`digitalization` (en)</t>
+          <t>`desgin` (en)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EX</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GLP359</t>
+          <t>GNA2NT</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>`djing` (en)</t>
+          <t>`assignement` (en)</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2NT</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GLP3AH</t>
+          <t>GNA3FN</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3511,105 +3511,105 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>`ande` (en)</t>
+          <t>`receiva` (en)</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3FN</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GLP3AH</t>
+          <t>NA1024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>`excercises` (en)</t>
+          <t>`efterfråge` (sv)</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>GLP3AR</t>
+          <t>NA1024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>`tools-miljö` (sv)</t>
+          <t>`distancelectures` (en)</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GLP3AR</t>
+          <t>NA1026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>`prouction` (en)</t>
+          <t>`studieförb` (sv)</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>LP1032</t>
+          <t>NA1027</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3619,51 +3619,51 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>`fördjupningskod` (sv)</t>
+          <t>`förläsningar` (sv)</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>LP1032</t>
+          <t>NA1028</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>`scholary` (en)</t>
+          <t>`efterfråge` (sv)</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1028</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>LP1032</t>
+          <t>NA1029</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3673,24 +3673,24 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>`sumarise` (en)</t>
+          <t>`differentiat` (en)</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>LP1054</t>
+          <t>NA1030</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3700,78 +3700,78 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>`audiovisuell` (en)</t>
+          <t>`excercises` (en)</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>LP1071</t>
+          <t>NA1032</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>`erätter` (sv)</t>
+          <t>`descirbe` (en)</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>LP1071</t>
+          <t>NA1035</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>`evaulates` (en)</t>
+          <t>`efterfråge` (sv)</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1035</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>LP2012</t>
+          <t>NA1036</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3781,24 +3781,24 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>`intiate` (en)</t>
+          <t>`longterm` (en)</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>LP2013</t>
+          <t>NA1036</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3808,24 +3808,24 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>`learnings` (en)</t>
+          <t>`shortterm` (en)</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>LP2013</t>
+          <t>NA1039</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3835,78 +3835,78 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>`litterature` (en)</t>
+          <t>`assingments` (en)</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GMN3E3</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>`rethoric` (en)</t>
+          <t>`kalandermånader` (sv)</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3E3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GMN3EA</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>`användar` (sv)</t>
+          <t>`calender` (en)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GMN3EX</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3916,19 +3916,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>`desgin` (en)</t>
+          <t>`oppobet` (en)</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GNA2NT</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3943,19 +3943,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>`assignement` (en)</t>
+          <t>`opposnent` (en)</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2NT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GNA3DA</t>
+          <t>NA2009</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3965,24 +3965,24 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>`tillgångspristeorier` (sv)</t>
+          <t>`resultas` (en)</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3DA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GNA3FN</t>
+          <t>NA3001</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3992,24 +3992,24 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>`receiva` (en)</t>
+          <t>`länderjämförelser` (sv)</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3FN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>NA1003</t>
+          <t>NA3010</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4019,24 +4019,24 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>`modigliani` (en)</t>
+          <t>`kalandermånader` (sv)</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>NA1003</t>
+          <t>NA3011</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4051,24 +4051,24 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>`scholes` (en)</t>
+          <t>`tobbit` (en)</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>NA1024</t>
+          <t>GPE3AJ</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4078,51 +4078,51 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>`efterfråge` (sv)</t>
+          <t>`kollegialtlärande` (sv)</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>NA1024</t>
+          <t>PE1011</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>`distancelectures` (en)</t>
+          <t>`hög-skolepoäng` (sv)</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1011</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>NA1025</t>
+          <t>PE1020</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4132,51 +4132,51 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>`konjunkturinstitutet` (en)</t>
+          <t>`gryndsyn` (en)</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>NA1026</t>
+          <t>PE1021</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>`hässel` (sv)</t>
+          <t>`centrum` (en)</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1021</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>NA1026</t>
+          <t>PE1023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4186,24 +4186,24 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>`ränteparitetsvillkor` (sv)</t>
+          <t>`lärarlagsarbete` (sv)</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>NA1026</t>
+          <t>PE1023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4213,24 +4213,24 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>`studieförb` (sv)</t>
+          <t>`rättsäkerhet` (sv)</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>NA1027</t>
+          <t>PE1054</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4240,105 +4240,105 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>`förläsningar` (sv)</t>
+          <t>`lärstrategier` (sv)</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>NA1027</t>
+          <t>PE1064</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>`internetbased` (en)</t>
+          <t>`rättsäkerhetsproblematiken` (sv)</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1064</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>NA1028</t>
+          <t>PE1067</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>`efterfråge` (sv)</t>
+          <t>`att` — ….m. 2013-11-13.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>NA1029</t>
+          <t>PE1068</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>`differentiat` (en)</t>
+          <t>`känndom` (sv)</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>NA1030</t>
+          <t>PE2005</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4348,51 +4348,51 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>`excercises` (en)</t>
+          <t>`gryndsyn` (en)</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>NA1032</t>
+          <t>PE3004</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>`descirbe` (en)</t>
+          <t>`högskole-mässighet` (sv)</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>NA1035</t>
+          <t>PE3004</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4402,51 +4402,51 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>`efterfråge` (sv)</t>
+          <t>`lärarlagsarbete` (sv)</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>NA1036</t>
+          <t>PE3004</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>`longterm` (en)</t>
+          <t>`rättsäkerhet` (sv)</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>NA1036</t>
+          <t>GPA2FW</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4456,51 +4456,51 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>`shortterm` (en)</t>
+          <t>`managemet` (en)</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>NA1039</t>
+          <t>GPA2R6</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>`assingments` (en)</t>
+          <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>NA1039</t>
+          <t>GPA353</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4510,24 +4510,24 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>`externalities` (en)</t>
+          <t>`valuest` (en)</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA353</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>APG24E</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4537,51 +4537,51 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>`kalandermånader` (sv)</t>
+          <t>`inlämingsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>APG25N</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>`calender` (en)</t>
+          <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>APG29G</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4591,51 +4591,51 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>`oppobet` (en)</t>
+          <t>`asignments` (en)</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG29G</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>APG2AA</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>`opposnent` (en)</t>
+          <t>`lärarskicklighetetens` (sv)</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>NA2009</t>
+          <t>APG2AC</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4645,78 +4645,78 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>`resultas` (en)</t>
+          <t>`aanalyze` (en)</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>NA3001</t>
+          <t>APG2AC</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>`länderjämförelser` (sv)</t>
+          <t>`nalyze` (en)</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>NA3010</t>
+          <t>APG2AC</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>`kalandermånader` (sv)</t>
+          <t>`rincipal` (en)</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>NA3011</t>
+          <t>APG2C3</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4726,24 +4726,24 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>`tobbit` (en)</t>
+          <t>`practies` (en)</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>GPE3AJ</t>
+          <t>APG2CC</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4753,24 +4753,24 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>`kollegialtlärande` (sv)</t>
+          <t>`lärar-elevrelationer` (sv)</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>PE1010</t>
+          <t>APG2CD</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4780,51 +4780,51 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>`elfström` (sv)</t>
+          <t>`lärarprofessionsspecifika` (sv)</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>PE1010</t>
+          <t>APG2CD</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>`göteborg` (sv)</t>
+          <t>`practicies` (en)</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>PE1010</t>
+          <t>APG2CM</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4834,78 +4834,78 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>`linköpings` (sv)</t>
+          <t>`undervisningensmål` (sv)</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>PE1010</t>
+          <t>APG2CM</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>`lpfö` (sv)</t>
+          <t>`pratice` (en)</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>PE1010</t>
+          <t>GPG22K</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>`löfdahl` (sv)</t>
+          <t>`conciderations` (en)</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>PE1010</t>
+          <t>GPG27X</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4915,24 +4915,24 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>`norrköping` (sv)</t>
+          <t>`lärar` (sv)</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>PE1010</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4942,51 +4942,51 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>`åberg` (sv)</t>
+          <t>`samhällorienterande` (sv)</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>PE1011</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>`hög-skolepoäng` (sv)</t>
+          <t>`hinduism` (en)</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>PE1020</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4996,24 +4996,24 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>`gryndsyn` (en)</t>
+          <t>`sociaty` (en)</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>PE1021</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5023,51 +5023,51 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>`centrum` (en)</t>
+          <t>`understandingn` (en)</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>PE1021</t>
+          <t>GPG328</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>`grund` (en)</t>
+          <t>`andraämne` (sv)</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>PE1023</t>
+          <t>GPG329</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5077,78 +5077,78 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>`lärarlagsarbete` (sv)</t>
+          <t>`andraämne` (sv)</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>PE1023</t>
+          <t>GPG3AD</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>`rättsäkerhet` (sv)</t>
+          <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>PE1054</t>
+          <t>GPG3CG</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>`lärstrategier` (sv)</t>
+          <t>`perspecitves` (en)</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>PE1064</t>
+          <t>GPG3CK</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5158,78 +5158,78 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>`rättsäkerhetsproblematiken` (sv)</t>
+          <t>`inlämninguppgift` (sv)</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>PE1067</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>`att` — ….m. 2013-11-13.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
+          <t>`samhällorienterande` (sv)</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>PE1068</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>`känndom` (sv)</t>
+          <t>`sociaty` (en)</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>PE2005</t>
+          <t>GPG3FR</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5239,105 +5239,105 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>`gryndsyn` (en)</t>
+          <t>`progamme` (en)</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>PE3004</t>
+          <t>GPG3FU</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>`högskole-mässighet` (sv)</t>
+          <t>`developement` (en)</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>PE3004</t>
+          <t>GPG3FU</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>`lärarlagsarbete` (sv)</t>
+          <t>`evalution` (en)</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>PE3004</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>`rättsäkerhet` (sv)</t>
+          <t>`att` (en)</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GPA2FW</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5347,51 +5347,51 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>`managemet` (en)</t>
+          <t>`studenten` (en)</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GPA2R6</t>
+          <t>ARK27Q</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>`tillvägagångsätt` (sv)</t>
+          <t>`tha` (en)</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>GPA353</t>
+          <t>ARK29K</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5401,24 +5401,24 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>`valuest` (en)</t>
+          <t>`cpecialisation` (en)</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA353</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29K</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>APG24E</t>
+          <t>ARK29L</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5428,78 +5428,78 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>`inlämingsuppgifter` (sv)</t>
+          <t>`markonivå` (sv)</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29L</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>APG25N</t>
+          <t>GRK366</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>`tillvägagångsätt` (sv)</t>
+          <t>`enivronments` (en)</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK366</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>APG29G</t>
+          <t>GRK3B4</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>`asignments` (en)</t>
+          <t>`ämesteoretiska` (sv)</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG29G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>APG2AA</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5509,105 +5509,105 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>`lärarskicklighetetens` (sv)</t>
+          <t>`mervärdskatt` (sv)</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>APG2AC</t>
+          <t>GRV2MK</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>`aanalyze` (en)</t>
+          <t>`innhåller` (sv)</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>APG2AC</t>
+          <t>RV1001</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>`nalyze` (en)</t>
+          <t>`glavå` (sv)</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>APG2AC</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>`rincipal` (en)</t>
+          <t>`mervärdskatt` (sv)</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>APG2C3</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5617,24 +5617,24 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>`practies` (en)</t>
+          <t>`taxat` (en)</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>APG2CC</t>
+          <t>RV1009</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5644,24 +5644,24 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>`lärar-elevrelationer` (sv)</t>
+          <t>`eg-rättslig` (sv)</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>APG2CD</t>
+          <t>RV1009</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5671,105 +5671,105 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>`lärarprofessionsspecifika` (sv)</t>
+          <t>`eg-rättsliga` (sv)</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>APG2CD</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>`practicies` (en)</t>
+          <t>`glavå` (sv)</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>APG2CM</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>`undervisningensmål` (sv)</t>
+          <t>`bargening` (en)</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>APG2CM</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>`pratice` (en)</t>
+          <t>`obestånds` (sv)</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>GPG22K</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5779,51 +5779,51 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>`conciderations` (en)</t>
+          <t>`pratices` (en)</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>GPG27X</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>`lärar` (sv)</t>
+          <t>`securites` (en)</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5833,51 +5833,51 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>`samhällorienterande` (sv)</t>
+          <t>`förvaltningsrättliga` (sv)</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>`hinduism` (en)</t>
+          <t>`rättsäkerheten` (sv)</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5887,24 +5887,24 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>`judaism` (en)</t>
+          <t>`xxxxxxxxxxx` (en)</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5914,159 +5914,159 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>`sociaty` (en)</t>
+          <t>`xxxxxxxxxxxxx` (en)</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>RV1045</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>`understandingn` (en)</t>
+          <t>`åtgärdscheman` (sv)</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>RV1050</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>`systematising` (en)</t>
+          <t>`eu-rätten` (sv)</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>GPG328</t>
+          <t>RV1055</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>`andraämne` (sv)</t>
+          <t>`samt` — …aminationsformer  En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,…</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GPG329</t>
+          <t>ASK22L</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>`andraämne` (sv)</t>
+          <t>`formes` (en)</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>GPG3AD</t>
+          <t>ASK22M</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
+          <t>`reviewscrutiny` (en)</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GPG3CG</t>
+          <t>ASK289</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6076,78 +6076,78 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>`perspecitves` (en)</t>
+          <t>`adress` (en)</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>GPG3CK</t>
+          <t>ASK289</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>`inlämninguppgift` (sv)</t>
+          <t>`compative` (en)</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>GSO2PL</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>`samhällorienterande` (sv)</t>
+          <t>`credits` — …7.5 credits, Psychological Perspectives on Social Work 7.5 credits credits and Welfare Measures and User Perspective 15 credits…</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>SO1027</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6157,51 +6157,51 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>`sociaty` (en)</t>
+          <t>`abilty` (en)</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>GPG3FR</t>
+          <t>ATR26B</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>`progamme` (en)</t>
+          <t>`hållbarbetsmål` (sv)</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>GPG3FU</t>
+          <t>ATR2BJ</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6211,24 +6211,24 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>`developement` (en)</t>
+          <t>`leaisure` (en)</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>GPG3FU</t>
+          <t>ATR2BJ</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6238,105 +6238,105 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>`evalution` (en)</t>
+          <t>`uns` (en)</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>GTR22D</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>`antagna` (en)</t>
+          <t>`samhållsvetenskap` (sv)</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>GTR22D</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>`att` (en)</t>
+          <t>`värderigsförmåga` (sv)</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>GTR265</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>`dessutom` (en)</t>
+          <t>`fömåga` (sv)</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>GTR265</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6346,78 +6346,78 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>`fritidshem` (en)</t>
+          <t>`afte` (en)</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>GTR26E</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>`hela` (en)</t>
+          <t>`erätter` (sv)</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>`inriktningen` (en)</t>
+          <t>`förhållningssät` (sv)</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -6427,24 +6427,24 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>`specialiseringar` (en)</t>
+          <t>`assignement` (en)</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6454,105 +6454,105 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>`studenten` (en)</t>
+          <t>`implmented` (en)</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>GTR2DG</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>`studerande` (en)</t>
+          <t>`the` — …earch. The course is organised into two parts. In part one, the The course introduces students to quantitative research. The co…</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>GTR2DG</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>`tidigare` (en)</t>
+          <t>`enkätsstudie` (sv)</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>GTR2DP</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>`inklusive` (en)</t>
+          <t>`värderingsfömåga` (sv)</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -6562,51 +6562,51 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>`kurs` (en)</t>
+          <t>`recourses` (en)</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>`tematisk` (en)</t>
+          <t>`använding` (sv)</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -6616,24 +6616,24 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>`utveckling` (en)</t>
+          <t>`lerning` (en)</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>ARK26T</t>
+          <t>TR1018</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6643,51 +6643,51 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>`chassidism` (en)</t>
+          <t>`geodemographic` (en)</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>ARK26T</t>
+          <t>TR1024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>`esotericism` (en)</t>
+          <t>`fömåga` (sv)</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>ARK26T</t>
+          <t>TR1024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6697,24 +6697,24 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>`jewish` (en)</t>
+          <t>`afte` (en)</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>ARK26T</t>
+          <t>TR1025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6724,51 +6724,51 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>`kabbalistic` (en)</t>
+          <t>`studiesand` (en)</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK26T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>TR1027</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>`canaan` (en)</t>
+          <t>`fömåga` (sv)</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>TR1027</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -6778,51 +6778,51 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>`civilising` (en)</t>
+          <t>`afte` (en)</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>TR1028</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>`mesopotamia` (en)</t>
+          <t>`förhållningssät` (sv)</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>TR1028</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -6832,24 +6832,24 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>`tha` (en)</t>
+          <t>`ansd` (en)</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>ARK29K</t>
+          <t>TR1029</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -6859,24 +6859,24 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>`cpecialisation` (en)</t>
+          <t>`studiesand` (en)</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>ARK29L</t>
+          <t>TR1030</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -6886,159 +6886,159 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>`markonivå` (sv)</t>
+          <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>GRK323</t>
+          <t>TR1031</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>`jerusalem` (en)</t>
+          <t>`kulturellafördomar` (sv)</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK323</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>GRK366</t>
+          <t>TR1034</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>`enivronments` (en)</t>
+          <t>`förvärvda` (sv)</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK366</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>GRK3B4</t>
+          <t>TR1034</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>`ämesteoretiska` (sv)</t>
+          <t>`organisaton` (en)</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>RK3043</t>
+          <t>TR2004</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>`vernakulär` (sv)</t>
+          <t>`stuides` (en)</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>TR3006</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>`mervärdskatt` (sv)</t>
+          <t>`the` — …- Independently identify and analyze scientific problems in the the relevant field of knowledge and conduct and report on a pro…</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>GRV2MK</t>
+          <t>TR3006</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7048,132 +7048,132 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>`innhåller` (sv)</t>
+          <t>`ocskå` (sv)</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>RV1001</t>
+          <t>AS2002</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>`glavå` (sv)</t>
+          <t>`takenup` (en)</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>AS3002</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>`mervärdskatt` (sv)</t>
+          <t>`teh` (en)</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>AS3009</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>`taxat` (en)</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>RV1004</t>
+          <t>AS3012</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>`åke` (sv)</t>
+          <t>`outlineof` (en)</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>RV1009</t>
+          <t>AS4003</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7183,1880 +7183,17 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>`eg-rättslig` (sv)</t>
+          <t>`angrepssätt` (sv)</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
-        <is>
-          <t>RV1009</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>`eg-rättsliga` (sv)</t>
-        </is>
-      </c>
-      <c r="E251" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="2" t="inlineStr">
-        <is>
-          <t>RV1026</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>`glavå` (sv)</t>
-        </is>
-      </c>
-      <c r="E252" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="2" t="inlineStr">
-        <is>
-          <t>RV1026</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>`bargening` (en)</t>
-        </is>
-      </c>
-      <c r="E253" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="2" t="inlineStr">
-        <is>
-          <t>RV1038</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>`obestånds` (sv)</t>
-        </is>
-      </c>
-      <c r="E254" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="2" t="inlineStr">
-        <is>
-          <t>RV1038</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>`pratices` (en)</t>
-        </is>
-      </c>
-      <c r="E255" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="2" t="inlineStr">
-        <is>
-          <t>RV1038</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>`securites` (en)</t>
-        </is>
-      </c>
-      <c r="E256" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
-        <is>
-          <t>RV1043</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>`clevesköld` (sv)</t>
-        </is>
-      </c>
-      <c r="E257" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="2" t="inlineStr">
-        <is>
-          <t>RV1043</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>`förvaltningsrättliga` (sv)</t>
-        </is>
-      </c>
-      <c r="E258" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="2" t="inlineStr">
-        <is>
-          <t>RV1043</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>`rättsäkerheten` (sv)</t>
-        </is>
-      </c>
-      <c r="E259" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="2" t="inlineStr">
-        <is>
-          <t>RV1043</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>`xxxxxxxxxxx` (en)</t>
-        </is>
-      </c>
-      <c r="E260" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="2" t="inlineStr">
-        <is>
-          <t>RV1043</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>`xxxxxxxxxxxxx` (en)</t>
-        </is>
-      </c>
-      <c r="E261" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="2" t="inlineStr">
-        <is>
-          <t>RV1045</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>`åtgärdscheman` (sv)</t>
-        </is>
-      </c>
-      <c r="E262" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="2" t="inlineStr">
-        <is>
-          <t>RV1050</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>`eu-rätten` (sv)</t>
-        </is>
-      </c>
-      <c r="E263" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="2" t="inlineStr">
-        <is>
-          <t>RV1055</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>RVA</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>Dubblerat ord</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>`samt` — …aminationsformer  En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,…</t>
-        </is>
-      </c>
-      <c r="E264" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="2" t="inlineStr">
-        <is>
-          <t>ASK22L</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>SKA</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>`formes` (en)</t>
-        </is>
-      </c>
-      <c r="E265" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="2" t="inlineStr">
-        <is>
-          <t>ASK22L</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>SKA</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>`modus` (en)</t>
-        </is>
-      </c>
-      <c r="E266" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="2" t="inlineStr">
-        <is>
-          <t>ASK22L</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>SKA</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>`operandi` (en)</t>
-        </is>
-      </c>
-      <c r="E267" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="2" t="inlineStr">
-        <is>
-          <t>ASK22M</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>SKA</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>`reviewscrutiny` (en)</t>
-        </is>
-      </c>
-      <c r="E268" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="2" t="inlineStr">
-        <is>
-          <t>ASK289</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>SKA</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>`adress` (en)</t>
-        </is>
-      </c>
-      <c r="E269" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="2" t="inlineStr">
-        <is>
-          <t>ASK289</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>SKA</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>`compative` (en)</t>
-        </is>
-      </c>
-      <c r="E270" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="2" t="inlineStr">
-        <is>
-          <t>SK1050</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>SKA</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>`europarådet` (sv)</t>
-        </is>
-      </c>
-      <c r="E271" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="2" t="inlineStr">
-        <is>
-          <t>SK1054</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>SKA</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>`problematique` (en)</t>
-        </is>
-      </c>
-      <c r="E272" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1054</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="2" t="inlineStr">
-        <is>
-          <t>SK1055</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>SKA</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>`interconnectedness` (en)</t>
-        </is>
-      </c>
-      <c r="E273" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1055</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="2" t="inlineStr">
-        <is>
-          <t>GSO2PL</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>SOA</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>Dubblerat ord</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>`credits` — …7.5 credits, Psychological Perspectives on Social Work 7.5 credits credits and Welfare Measures and User Perspective 15 credits…</t>
-        </is>
-      </c>
-      <c r="E274" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="2" t="inlineStr">
-        <is>
-          <t>SO1027</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>SOA</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>`abilty` (en)</t>
-        </is>
-      </c>
-      <c r="E275" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="2" t="inlineStr">
-        <is>
-          <t>SO1027</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>SOA</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>`constructivism` (en)</t>
-        </is>
-      </c>
-      <c r="E276" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="2" t="inlineStr">
-        <is>
-          <t>SO1027</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>SOA</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>`interactionism` (en)</t>
-        </is>
-      </c>
-      <c r="E277" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="2" t="inlineStr">
-        <is>
-          <t>ATR26B</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>`hållbarbetsmål` (sv)</t>
-        </is>
-      </c>
-      <c r="E278" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="2" t="inlineStr">
-        <is>
-          <t>ATR2BJ</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>`leaisure` (en)</t>
-        </is>
-      </c>
-      <c r="E279" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="2" t="inlineStr">
-        <is>
-          <t>ATR2BJ</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>`uns` (en)</t>
-        </is>
-      </c>
-      <c r="E280" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="2" t="inlineStr">
-        <is>
-          <t>GTR22D</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>`samhållsvetenskap` (sv)</t>
-        </is>
-      </c>
-      <c r="E281" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="2" t="inlineStr">
-        <is>
-          <t>GTR22D</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>`värderigsförmåga` (sv)</t>
-        </is>
-      </c>
-      <c r="E282" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="2" t="inlineStr">
-        <is>
-          <t>GTR265</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>`fömåga` (sv)</t>
-        </is>
-      </c>
-      <c r="E283" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="2" t="inlineStr">
-        <is>
-          <t>GTR265</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>`afte` (en)</t>
-        </is>
-      </c>
-      <c r="E284" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="2" t="inlineStr">
-        <is>
-          <t>GTR26E</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>`erätter` (sv)</t>
-        </is>
-      </c>
-      <c r="E285" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="2" t="inlineStr">
-        <is>
-          <t>GTR29Q</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>`förhållningssät` (sv)</t>
-        </is>
-      </c>
-      <c r="E286" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="2" t="inlineStr">
-        <is>
-          <t>GTR29Q</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>`assignement` (en)</t>
-        </is>
-      </c>
-      <c r="E287" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="2" t="inlineStr">
-        <is>
-          <t>GTR29Q</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>`implmented` (en)</t>
-        </is>
-      </c>
-      <c r="E288" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="2" t="inlineStr">
-        <is>
-          <t>GTR2DG</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>Dubblerat ord</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>`the` — …earch. The course is organised into two parts. In part one, the The course introduces students to quantitative research. The co…</t>
-        </is>
-      </c>
-      <c r="E289" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="2" t="inlineStr">
-        <is>
-          <t>GTR2DG</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>`enkätsstudie` (sv)</t>
-        </is>
-      </c>
-      <c r="E290" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="2" t="inlineStr">
-        <is>
-          <t>GTR2DP</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>`värderingsfömåga` (sv)</t>
-        </is>
-      </c>
-      <c r="E291" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="2" t="inlineStr">
-        <is>
-          <t>GTR3B6</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>`sälenfjällen` (sv)</t>
-        </is>
-      </c>
-      <c r="E292" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3B6</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="2" t="inlineStr">
-        <is>
-          <t>GTR3D7</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>`kungliga` (en)</t>
-        </is>
-      </c>
-      <c r="E293" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3D7</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="2" t="inlineStr">
-        <is>
-          <t>TR1007</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>`recourses` (en)</t>
-        </is>
-      </c>
-      <c r="E294" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="2" t="inlineStr">
-        <is>
-          <t>TR1013</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>`använding` (sv)</t>
-        </is>
-      </c>
-      <c r="E295" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="2" t="inlineStr">
-        <is>
-          <t>TR1013</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>`lerning` (en)</t>
-        </is>
-      </c>
-      <c r="E296" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="2" t="inlineStr">
-        <is>
-          <t>TR1013</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>`powerpoint` (en)</t>
-        </is>
-      </c>
-      <c r="E297" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="2" t="inlineStr">
-        <is>
-          <t>TR1018</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>`geodemographic` (en)</t>
-        </is>
-      </c>
-      <c r="E298" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="2" t="inlineStr">
-        <is>
-          <t>TR1024</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>`fömåga` (sv)</t>
-        </is>
-      </c>
-      <c r="E299" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="2" t="inlineStr">
-        <is>
-          <t>TR1024</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>`afte` (en)</t>
-        </is>
-      </c>
-      <c r="E300" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="2" t="inlineStr">
-        <is>
-          <t>TR1025</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>`studiesand` (en)</t>
-        </is>
-      </c>
-      <c r="E301" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="2" t="inlineStr">
-        <is>
-          <t>TR1027</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>`fömåga` (sv)</t>
-        </is>
-      </c>
-      <c r="E302" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="2" t="inlineStr">
-        <is>
-          <t>TR1027</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>`afte` (en)</t>
-        </is>
-      </c>
-      <c r="E303" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="2" t="inlineStr">
-        <is>
-          <t>TR1028</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>`förhållningssät` (sv)</t>
-        </is>
-      </c>
-      <c r="E304" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="2" t="inlineStr">
-        <is>
-          <t>TR1028</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>`ansd` (en)</t>
-        </is>
-      </c>
-      <c r="E305" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="2" t="inlineStr">
-        <is>
-          <t>TR1029</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>`studiesand` (en)</t>
-        </is>
-      </c>
-      <c r="E306" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="2" t="inlineStr">
-        <is>
-          <t>TR1030</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>`tillvägagångsätt` (sv)</t>
-        </is>
-      </c>
-      <c r="E307" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="2" t="inlineStr">
-        <is>
-          <t>TR1031</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>`kulturellafördomar` (sv)</t>
-        </is>
-      </c>
-      <c r="E308" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="2" t="inlineStr">
-        <is>
-          <t>TR1034</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>`förvärvda` (sv)</t>
-        </is>
-      </c>
-      <c r="E309" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="2" t="inlineStr">
-        <is>
-          <t>TR1034</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>`organisaton` (en)</t>
-        </is>
-      </c>
-      <c r="E310" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="2" t="inlineStr">
-        <is>
-          <t>TR2004</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>`stuides` (en)</t>
-        </is>
-      </c>
-      <c r="E311" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="2" t="inlineStr">
-        <is>
-          <t>TR3006</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>Dubblerat ord</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>`the` — …- Independently identify and analyze scientific problems in the the relevant field of knowledge and conduct and report on a pro…</t>
-        </is>
-      </c>
-      <c r="E312" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="2" t="inlineStr">
-        <is>
-          <t>TR3006</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>`ocskå` (sv)</t>
-        </is>
-      </c>
-      <c r="E313" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="2" t="inlineStr">
-        <is>
-          <t>AS2002</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>`takenup` (en)</t>
-        </is>
-      </c>
-      <c r="E314" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="2" t="inlineStr">
-        <is>
-          <t>AS3002</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>`teh` (en)</t>
-        </is>
-      </c>
-      <c r="E315" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="2" t="inlineStr">
-        <is>
-          <t>AS3009</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>`literära` (sv)</t>
-        </is>
-      </c>
-      <c r="E316" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="2" t="inlineStr">
-        <is>
-          <t>AS3012</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>`outlineof` (en)</t>
-        </is>
-      </c>
-      <c r="E317" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" s="2" t="inlineStr">
-        <is>
-          <t>AS4001</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>`mastersnivå` (sv)</t>
-        </is>
-      </c>
-      <c r="E318" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4001</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="2" t="inlineStr">
-        <is>
-          <t>AS4003</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>`angrepssätt` (sv)</t>
-        </is>
-      </c>
-      <c r="E319" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E319"/>
+  <autoFilter ref="A1:E250"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -9556,144 +7693,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId496"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A250" r:id="rId497"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A251" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E251" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A252" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E252" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A253" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E253" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A254" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E254" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A255" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E255" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A256" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E256" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A257" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E257" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A258" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E258" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A259" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E259" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A260" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E260" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A261" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E261" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A262" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E262" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A263" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E263" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A264" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E264" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A265" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E265" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A266" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E266" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A267" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E267" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A268" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E268" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A269" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E269" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A270" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E270" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A271" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E271" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A272" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E272" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A273" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E273" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A274" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E274" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A275" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E275" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A276" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E276" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A277" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E277" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A278" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E278" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A279" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E279" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A280" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E280" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A281" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E281" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A282" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E282" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A283" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E283" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A284" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E284" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A285" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E285" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A286" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E286" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A287" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E287" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A288" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E288" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A289" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E289" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A290" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E290" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A291" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E291" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A292" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E292" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A293" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E293" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A294" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E294" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A295" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E295" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A296" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E296" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A297" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E297" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A298" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E298" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A299" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E299" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A300" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E300" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A301" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E301" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A302" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E302" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A303" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E303" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A304" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E304" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A305" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E305" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A306" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E306" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A307" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E307" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A308" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E308" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A309" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E309" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A310" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E310" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A311" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E311" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A312" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E312" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A313" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E313" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A314" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E314" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A315" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E315" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A316" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E316" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A317" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E317" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A318" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E318" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A319" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E319" r:id="rId636"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$250</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,221 +472,6728 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ABQ2B4</t>
+          <t>AB1019</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`en` — …- formulera och muntligt framföra konstruktiv kritik på en en text av vetenskaplig karaktär    - vetenskapligt värdera oc…</t>
+          <t>`arbetsträtt` (sv)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1019</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>FI1039</t>
+          <t>AB1019</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`have` — …urthermore, on completion of the course, the student should have have the ability to :       - be reflective in relation to probl…</t>
+          <t>`förläsningar` (sv)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1019</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>PE1067</t>
+          <t>AB1019</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`att` — ….m. 2013-11-13.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
+          <t>`municpality` (en)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1019</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GPG3AD</t>
+          <t>AB1022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
+          <t>`därmellen` (sv)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1022</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>RV1055</t>
+          <t>AB1029</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`samt` — …aminationsformer  En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,…</t>
+          <t>`abilith` (en)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1029</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GSO2PL</t>
+          <t>AB3001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`credits` — …7.5 credits, Psychological Perspectives on Social Work 7.5 credits credits and Welfare Measures and User Perspective 15 credits…</t>
+          <t>`kommunförb` (sv)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB3001</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>ABQ2AM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`the` — …earch. The course is organised into two parts. In part one, the The course introduces students to quantitative research. The co…</t>
+          <t>`inludes` (en)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>ABQ2AM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>`managment` (en)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ABQ2B4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>`en` — …- formulera och muntligt framföra konstruktiv kritik på en en text av vetenskaplig karaktär    - vetenskapligt värdera oc…</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>BQ1079</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>`devolop` (en)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ1079</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>BQ1079</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>`strucuring` (en)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ1079</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>BQ2018</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>`lärarare` (sv)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>BQ2057</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>`postproduction` (en)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2057</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>GBQ29D</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>`undergradaute` (en)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29D</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>GBQ29E</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>`undergradaute` (en)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29E</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>GBQ2U6</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>`användar` (sv)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>GBQ2U6</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>`beställningsfilmsproduktion` (sv)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>GBQ2UB</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>`berättandestruktur` (sv)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UB</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>GBQ2WH</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>`tbt` (en)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WH</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>GBQ2WK</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>`berätttarelement` (sv)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WK</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>GBQ36K</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>`praktical` (en)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36K</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>GBQ36K</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>`thery` (en)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36K</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>GBQ38V</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>`mediacomposer-miljö` (sv)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38V</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>GBQ38W</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>`composer-miljö` (sv)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>GBQ38W</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>`höguppupplöst` (sv)</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>GBQ38W</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>`avanced` (en)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>GBQ38X</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>`documetnary` (en)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>GBQ38X</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>`filmproject` (en)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>GBQ38X</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>`histrorical` (en)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>GBQ3A6</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>`användar` (sv)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>GBQ3A7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>`wars-berättelserna` (sv)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>GBQ3A7</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>`wars-berättelsernas` (sv)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>GBQ3AW</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>`explainer` (en)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>GBQ3FG</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>`excercises` (en)</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>EU1027</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>EUN</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>`grundäggande` (sv)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>EU1033</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>EUN</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>`itssocial` (en)</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1033</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>EU1034</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>EUN</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>`förhandlingprocesser` (sv)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1034</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>GEU2KV</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>EUN</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>`opportunties` (en)</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>GEU2KV</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>EUN</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>`willll` (en)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>AFI273</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>`contignency` (en)</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFI273</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>FI1023</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>`philosohical` (en)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>FI1024</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>`etichs` (en)</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>FI1039</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>`have` — …urthermore, on completion of the course, the student should have have the ability to :       - be reflective in relation to probl…</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>FI1039</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>`asessment` (en)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>FI1039</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>`developement` (en)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>FI2003</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>`filosofi` (en)</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>GFI3BT</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>`introdcution` (en)</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>GFI3BT</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>`througout` (en)</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>GFI3BU</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>`througout` (en)</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>AHI272</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>`europeiskspråkiga` (sv)</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>AHI272</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>`poitical` (en)</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>AHI29Q</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>`consultaion` (en)</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>AHI29Q</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>`situatin` (en)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>AS2005</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>`takenup` (en)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>AS3017</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>`literära` (sv)</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>AS3020</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>`outlineof` (en)</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>AS3022</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>`teh` (en)</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>GHI29Y</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>`innhållet` (sv)</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>GHI33T</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>`problemförmuleringsförmåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>GHI33V</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>`delkurseninnehåller` (sv)</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>GHI33V</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>`godkäng` (sv)</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>GHI35A</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>`analyseratmänniskors` (sv)</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>GHI35A</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>`medförintelsen` (sv)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>GHI35A</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>`människorsagerande` (sv)</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>GHI362</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>`självstänigt` (sv)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>HI1008</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>`criterions` (en)</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>HI2011</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>`historiedidaktikområdet` (sv)</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>HI2012</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>`sjävvalt` (sv)</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>HI2016</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>`sjävvalt` (sv)</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>HI3019</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>`självständg` (sv)</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3019</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>AKG27R</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>`compulsotry` (en)</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>AKG27R</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>`curent` (en)</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>AKG27R</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>`theoretica` (en)</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>GKG3AT</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>`tilllämpas` (sv)</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>GKG3AT</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>`writtten` (en)</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>KG1016</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>`datalaborations` (en)</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>KG1020</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>`assignements` (en)</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1020</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>KG1024</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>`beräklningstung` (sv)</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>KG1024</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>`quantitativ` (en)</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>KG1025</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>`evolvement` (en)</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>KG1025</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>`thise` (en)</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>KG2001</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>`obser` (en)</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>KG2001</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>`perspetives` (en)</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>KG2001</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>`standarized` (en)</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>KG2001</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>`vations` (en)</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>KG2005</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>`qualititative` (en)</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>KG3010</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>`recognises` (en)</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>KG3011</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>`kartöverlägg` (sv)</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>KG3011</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>`skalnivå` (sv)</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>KG3014</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>`eaxaminer` (en)</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>KG3015</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>`eaxaminer` (en)</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>KG3016</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>`gällade` (sv)</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>GLP236</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>`framträdandeform` (sv)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>GLP29R</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>`flerspårsmaterial` (sv)</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29R</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>GLP2JZ</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>`flerspårsmaterial` (sv)</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2JZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>GLP359</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>`djing` (en)</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>GLP3AH</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>`ande` (en)</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>GLP3AH</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>`excercises` (en)</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>GLP3AR</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>`tools-miljö` (sv)</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>GLP3AR</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>`prouction` (en)</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>LP1032</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>`fördjupningskod` (sv)</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>LP1032</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>`scholary` (en)</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>LP1032</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>`sumarise` (en)</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>LP1071</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>`erätter` (sv)</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>LP1071</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>`evaulates` (en)</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>LP2012</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>`intiate` (en)</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>LP2013</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>`learnings` (en)</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>LP2013</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>`litterature` (en)</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>GMN3E3</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>MPR</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>`rethoric` (en)</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3E3</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>GMN3EA</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>MPR</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>`användar` (sv)</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EA</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>GMN3EX</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>MPR</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>`desgin` (en)</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EX</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>GNA2NT</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>`assignement` (en)</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2NT</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>GNA3FN</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>`receiva` (en)</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3FN</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>NA1024</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>`efterfråge` (sv)</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>NA1024</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>`distancelectures` (en)</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>NA1026</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>`studieförb` (sv)</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>NA1027</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>`förläsningar` (sv)</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>NA1028</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>`efterfråge` (sv)</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>NA1029</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>`differentiat` (en)</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>NA1030</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>`excercises` (en)</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>NA1032</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>`descirbe` (en)</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>NA1035</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>`efterfråge` (sv)</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1035</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>NA1036</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>`longterm` (en)</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>NA1036</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>`shortterm` (en)</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>NA1039</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>`assingments` (en)</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>NA2008</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>`kalandermånader` (sv)</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>NA2008</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>`calender` (en)</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>NA2008</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>`oppobet` (en)</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>NA2008</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>`opposnent` (en)</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>NA2009</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>`resultas` (en)</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>NA3001</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>`länderjämförelser` (sv)</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>NA3010</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>`kalandermånader` (sv)</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>NA3011</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>`tobbit` (en)</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>GPE3AJ</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>`kollegialtlärande` (sv)</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>PE1011</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>`hög-skolepoäng` (sv)</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1011</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>PE1020</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>`gryndsyn` (en)</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>PE1021</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>`centrum` (en)</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1021</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>PE1023</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>`lärarlagsarbete` (sv)</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>PE1023</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>`rättsäkerhet` (sv)</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>PE1054</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>`lärstrategier` (sv)</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>PE1064</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>`rättsäkerhetsproblematiken` (sv)</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1064</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>PE1067</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>`att` — ….m. 2013-11-13.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>PE1068</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>`känndom` (sv)</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>PE2005</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>`gryndsyn` (en)</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>PE3004</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>`högskole-mässighet` (sv)</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>PE3004</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>`lärarlagsarbete` (sv)</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>PE3004</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>`rättsäkerhet` (sv)</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>GPA2FW</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>`managemet` (en)</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>GPA2R6</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>`tillvägagångsätt` (sv)</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>GPA353</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>`valuest` (en)</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA353</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>APG24E</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>`inlämingsuppgifter` (sv)</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>APG25N</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>`tillvägagångsätt` (sv)</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>APG29G</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>`asignments` (en)</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG29G</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>APG2AA</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>`lärarskicklighetetens` (sv)</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>APG2AC</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>`aanalyze` (en)</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>APG2AC</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>`nalyze` (en)</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>APG2AC</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>`rincipal` (en)</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>APG2C3</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>`practies` (en)</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>APG2CC</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>`lärar-elevrelationer` (sv)</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>APG2CD</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>`lärarprofessionsspecifika` (sv)</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>APG2CD</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>`practicies` (en)</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>APG2CM</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>`undervisningensmål` (sv)</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>APG2CM</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>`pratice` (en)</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>GPG22K</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>`conciderations` (en)</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>GPG27X</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>`lärar` (sv)</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>GPG2SC</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>`samhällorienterande` (sv)</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>GPG2SC</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>`hinduism` (en)</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>GPG2SC</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>`sociaty` (en)</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>GPG2SC</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>`understandingn` (en)</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>GPG328</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>`andraämne` (sv)</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>GPG329</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>`andraämne` (sv)</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>GPG3AD</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CG</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>`perspecitves` (en)</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CK</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>`inlämninguppgift` (sv)</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CL</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>`samhällorienterande` (sv)</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CL</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>`sociaty` (en)</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>GPG3FR</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>`progamme` (en)</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>GPG3FU</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>`developement` (en)</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>GPG3FU</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>`evalution` (en)</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>PG3023</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>`att` (en)</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>PG3023</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>`studenten` (en)</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>ARK27Q</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>`tha` (en)</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>ARK29K</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>`cpecialisation` (en)</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29K</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>ARK29L</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>`markonivå` (sv)</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29L</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>GRK366</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>`enivronments` (en)</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK366</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>GRK3B4</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>`ämesteoretiska` (sv)</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>GRV266</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>`mervärdskatt` (sv)</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>GRV2MK</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>`innhåller` (sv)</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>RV1001</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>`glavå` (sv)</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>RV1003</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>`mervärdskatt` (sv)</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>RV1003</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>`taxat` (en)</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>RV1009</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>`eg-rättslig` (sv)</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>RV1009</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>`eg-rättsliga` (sv)</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>RV1026</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>`glavå` (sv)</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>RV1026</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>`bargening` (en)</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>RV1038</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>`obestånds` (sv)</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>RV1038</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>`pratices` (en)</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>RV1038</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>`securites` (en)</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>RV1043</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>`förvaltningsrättliga` (sv)</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>RV1043</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>`rättsäkerheten` (sv)</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>RV1043</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>`xxxxxxxxxxx` (en)</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>RV1043</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>`xxxxxxxxxxxxx` (en)</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>RV1045</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>`åtgärdscheman` (sv)</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>RV1050</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>`eu-rätten` (sv)</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>RV1055</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>`samt` — …aminationsformer  En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,…</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>ASK22L</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>SKA</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>`formes` (en)</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>ASK22M</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>SKA</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>`reviewscrutiny` (en)</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>ASK289</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>SKA</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>`adress` (en)</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>ASK289</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>SKA</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>`compative` (en)</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>GSO2PL</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>`credits` — …7.5 credits, Psychological Perspectives on Social Work 7.5 credits credits and Welfare Measures and User Perspective 15 credits…</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>SO1027</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>`abilty` (en)</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>ATR26B</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>`hållbarbetsmål` (sv)</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>ATR2BJ</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>`leaisure` (en)</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>ATR2BJ</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>`uns` (en)</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>GTR22D</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>`samhållsvetenskap` (sv)</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>GTR22D</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>`värderigsförmåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>GTR265</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>`fömåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>GTR265</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>`afte` (en)</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>GTR26E</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>`erätter` (sv)</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>GTR29Q</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>`förhållningssät` (sv)</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>GTR29Q</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>`assignement` (en)</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>GTR29Q</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>`implmented` (en)</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>GTR2DG</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>`the` — …earch. The course is organised into two parts. In part one, the The course introduces students to quantitative research. The co…</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>GTR2DG</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>`enkätsstudie` (sv)</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>GTR2DP</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>`värderingsfömåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>TR1007</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>`recourses` (en)</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>TR1013</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>`använding` (sv)</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>TR1013</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>`lerning` (en)</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>TR1018</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>`geodemographic` (en)</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>TR1024</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>`fömåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>TR1024</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>`afte` (en)</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>TR1025</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>`studiesand` (en)</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>TR1027</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>`fömåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>TR1027</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>`afte` (en)</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>TR1028</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>`förhållningssät` (sv)</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>TR1028</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>`ansd` (en)</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>TR1029</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>`studiesand` (en)</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>TR1030</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>`tillvägagångsätt` (sv)</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>TR1031</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>`kulturellafördomar` (sv)</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>TR1034</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>`förvärvda` (sv)</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>TR1034</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>`organisaton` (en)</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>TR2004</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>`stuides` (en)</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
           <t>TR3006</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B244" t="inlineStr">
         <is>
           <t>TRU</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C244" t="inlineStr">
         <is>
           <t>Dubblerat ord</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D244" t="inlineStr">
         <is>
           <t>`the` — …- Independently identify and analyze scientific problems in the the relevant field of knowledge and conduct and report on a pro…</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E244" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>TR3006</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>`ocskå` (sv)</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>AS2002</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>`takenup` (en)</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>AS3002</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>`teh` (en)</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>AS3009</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>`literära` (sv)</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>AS3012</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>`outlineof` (en)</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>AS4003</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>`angrepssätt` (sv)</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E9"/>
+  <autoFilter ref="A1:E250"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -704,6 +7211,488 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A185" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A206" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A207" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A208" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A209" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A210" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A211" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A212" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A213" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A214" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A215" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A216" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A217" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A218" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A219" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A220" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A221" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A222" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A223" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A224" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A225" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A226" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A227" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A228" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A229" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A230" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A231" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A232" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A233" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A234" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A235" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A236" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A237" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A238" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A239" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A240" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A241" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A242" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A243" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A244" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A245" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A246" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A247" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A248" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A249" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A250" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId498"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
@@ -4294,7 +4294,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>`att` — ….m. 2013-11-13.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
+          <t>`att` — ….m. 2014-01-24.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">

--- a/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$250</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$229</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E250"/>
+  <dimension ref="A1:E229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1012,7 +1012,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GBQ36K</t>
+          <t>GBQ38V</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1022,24 +1022,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`praktical` (en)</t>
+          <t>`mediacomposer-miljö` (sv)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38V</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GBQ36K</t>
+          <t>GBQ38W</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1049,24 +1049,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`thery` (en)</t>
+          <t>`composer-miljö` (sv)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ36K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GBQ38V</t>
+          <t>GBQ38W</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1081,19 +1081,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`mediacomposer-miljö` (sv)</t>
+          <t>`höguppupplöst` (sv)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GBQ38W</t>
+          <t>GBQ3A6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1108,19 +1108,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`composer-miljö` (sv)</t>
+          <t>`användar` (sv)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GBQ38W</t>
+          <t>GBQ3A7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`höguppupplöst` (sv)</t>
+          <t>`wars-berättelserna` (sv)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GBQ38W</t>
+          <t>GBQ3A7</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`avanced` (en)</t>
+          <t>`wars-berättelsernas` (sv)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GBQ38X</t>
+          <t>GBQ3AW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`documetnary` (en)</t>
+          <t>`explainer` (en)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GBQ38X</t>
+          <t>GBQ3FG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,78 +1216,78 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`filmproject` (en)</t>
+          <t>`excercises` (en)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GBQ38X</t>
+          <t>EU1027</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`histrorical` (en)</t>
+          <t>`grundäggande` (sv)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1027</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A6</t>
+          <t>EU1033</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`användar` (sv)</t>
+          <t>`itssocial` (en)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1033</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A7</t>
+          <t>EU1034</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1297,51 +1297,51 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`wars-berättelserna` (sv)</t>
+          <t>`förhandlingprocesser` (sv)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1034</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A7</t>
+          <t>GEU2KV</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`wars-berättelsernas` (sv)</t>
+          <t>`opportunties` (en)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AW</t>
+          <t>GEU2KV</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`explainer` (en)</t>
+          <t>`willll` (en)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GBQ3FG</t>
+          <t>AFI273</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1378,51 +1378,51 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`excercises` (en)</t>
+          <t>`contignency` (en)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFI273</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>EU1027</t>
+          <t>FI1023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`grundäggande` (sv)</t>
+          <t>`philosohical` (en)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>EU1033</t>
+          <t>FI1024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1432,51 +1432,51 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`itssocial` (en)</t>
+          <t>`etichs` (en)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>EU1034</t>
+          <t>FI1039</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`förhandlingprocesser` (sv)</t>
+          <t>`have` — …urthermore, on completion of the course, the student should have have the ability to :       - be reflective in relation to probl…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GEU2KV</t>
+          <t>FI1039</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`opportunties` (en)</t>
+          <t>`asessment` (en)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GEU2KV</t>
+          <t>FI1039</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`willll` (en)</t>
+          <t>`developement` (en)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>AFI273</t>
+          <t>FI2003</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1540,19 +1540,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`contignency` (en)</t>
+          <t>`filosofi` (en)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFI273</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>FI1023</t>
+          <t>GFI3BT</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1567,19 +1567,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`philosohical` (en)</t>
+          <t>`througout` (en)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>FI1024</t>
+          <t>GFI3BU</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1594,51 +1594,51 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`etichs` (en)</t>
+          <t>`througout` (en)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>FI1039</t>
+          <t>AHI272</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`have` — …urthermore, on completion of the course, the student should have have the ability to :       - be reflective in relation to probl…</t>
+          <t>`europeiskspråkiga` (sv)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>FI1039</t>
+          <t>AHI272</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`asessment` (en)</t>
+          <t>`poitical` (en)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>FI1039</t>
+          <t>AHI29Q</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`developement` (en)</t>
+          <t>`consultaion` (en)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>FI2003</t>
+          <t>AHI29Q</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`filosofi` (en)</t>
+          <t>`situatin` (en)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GFI3BT</t>
+          <t>AS2005</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1729,51 +1729,51 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`introdcution` (en)</t>
+          <t>`takenup` (en)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2005</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GFI3BT</t>
+          <t>AS3017</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`througout` (en)</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GFI3BU</t>
+          <t>AS3020</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`througout` (en)</t>
+          <t>`outlineof` (en)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>AHI272</t>
+          <t>AS3022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1805,24 +1805,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`europeiskspråkiga` (sv)</t>
+          <t>`teh` (en)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>AHI272</t>
+          <t>GHI29Y</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1832,24 +1832,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`poitical` (en)</t>
+          <t>`innhållet` (sv)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>AHI29Q</t>
+          <t>GHI33T</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1859,24 +1859,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`consultaion` (en)</t>
+          <t>`problemförmuleringsförmåga` (sv)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>AHI29Q</t>
+          <t>GHI33V</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1886,24 +1886,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`situatin` (en)</t>
+          <t>`delkurseninnehåller` (sv)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>AS2005</t>
+          <t>GHI33V</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1913,24 +1913,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`takenup` (en)</t>
+          <t>`godkäng` (sv)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>AS3017</t>
+          <t>GHI35A</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1945,19 +1945,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`literära` (sv)</t>
+          <t>`analyseratmänniskors` (sv)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>AS3020</t>
+          <t>GHI35A</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1967,24 +1967,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`outlineof` (en)</t>
+          <t>`medförintelsen` (sv)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>AS3022</t>
+          <t>GHI35A</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1994,24 +1994,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`teh` (en)</t>
+          <t>`människorsagerande` (sv)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GHI29Y</t>
+          <t>GHI362</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2026,19 +2026,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`innhållet` (sv)</t>
+          <t>`självstänigt` (sv)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GHI33T</t>
+          <t>HI1008</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2048,24 +2048,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`problemförmuleringsförmåga` (sv)</t>
+          <t>`criterions` (en)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GHI33V</t>
+          <t>HI2011</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2080,19 +2080,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`delkurseninnehåller` (sv)</t>
+          <t>`historiedidaktikområdet` (sv)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GHI33V</t>
+          <t>HI2012</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2107,19 +2107,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`godkäng` (sv)</t>
+          <t>`sjävvalt` (sv)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GHI35A</t>
+          <t>HI2016</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`analyseratmänniskors` (sv)</t>
+          <t>`sjävvalt` (sv)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GHI35A</t>
+          <t>HI3019</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2161,78 +2161,78 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`medförintelsen` (sv)</t>
+          <t>`självständg` (sv)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3019</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GHI35A</t>
+          <t>AKG27R</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`människorsagerande` (sv)</t>
+          <t>`compulsotry` (en)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GHI362</t>
+          <t>AKG27R</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`självstänigt` (sv)</t>
+          <t>`curent` (en)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>HI1008</t>
+          <t>AKG27R</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`criterions` (en)</t>
+          <t>`theoretica` (en)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>HI2011</t>
+          <t>GKG3AT</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2269,78 +2269,78 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`historiedidaktikområdet` (sv)</t>
+          <t>`tilllämpas` (sv)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>HI2012</t>
+          <t>GKG3AT</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`sjävvalt` (sv)</t>
+          <t>`writtten` (en)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>HI2016</t>
+          <t>KG1016</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`sjävvalt` (sv)</t>
+          <t>`datalaborations` (en)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>HI3019</t>
+          <t>KG1024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`självständg` (sv)</t>
+          <t>`beräklningstung` (sv)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>AKG27R</t>
+          <t>KG1024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2377,19 +2377,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`compulsotry` (en)</t>
+          <t>`quantitativ` (en)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>AKG27R</t>
+          <t>KG1025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`curent` (en)</t>
+          <t>`evolvement` (en)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>AKG27R</t>
+          <t>KG1025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2431,19 +2431,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`theoretica` (en)</t>
+          <t>`thise` (en)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GKG3AT</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2453,24 +2453,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`tilllämpas` (sv)</t>
+          <t>`obser` (en)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GKG3AT</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2485,19 +2485,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`writtten` (en)</t>
+          <t>`perspetives` (en)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>KG1016</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`datalaborations` (en)</t>
+          <t>`standarized` (en)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>KG1020</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`assignements` (en)</t>
+          <t>`vations` (en)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>KG1024</t>
+          <t>KG2005</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`beräklningstung` (sv)</t>
+          <t>`qualititative` (en)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>KG1024</t>
+          <t>KG3010</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2593,19 +2593,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`quantitativ` (en)</t>
+          <t>`recognises` (en)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>KG1025</t>
+          <t>KG3011</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2615,24 +2615,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`evolvement` (en)</t>
+          <t>`kartöverlägg` (sv)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>KG1025</t>
+          <t>KG3011</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2642,24 +2642,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`thise` (en)</t>
+          <t>`skalnivå` (sv)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>KG3014</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2674,19 +2674,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`obser` (en)</t>
+          <t>`eaxaminer` (en)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>KG3015</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`perspetives` (en)</t>
+          <t>`eaxaminer` (en)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>KG3016</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2723,164 +2723,164 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`standarized` (en)</t>
+          <t>`gällade` (sv)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>GLP236</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`vations` (en)</t>
+          <t>`framträdandeform` (sv)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>KG2005</t>
+          <t>GLP29R</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`qualititative` (en)</t>
+          <t>`flerspårsmaterial` (sv)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29R</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>KG3010</t>
+          <t>GLP2JZ</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`recognises` (en)</t>
+          <t>`flerspårsmaterial` (sv)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2JZ</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>KG3011</t>
+          <t>GLP359</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`kartöverlägg` (sv)</t>
+          <t>`djing` (en)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>KG3011</t>
+          <t>GLP3AH</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`skalnivå` (sv)</t>
+          <t>`ande` (en)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>KG3014</t>
+          <t>GLP3AH</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2890,51 +2890,51 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`eaxaminer` (en)</t>
+          <t>`excercises` (en)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>KG3015</t>
+          <t>GLP3AR</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`eaxaminer` (en)</t>
+          <t>`tools-miljö` (sv)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>KG3016</t>
+          <t>LP1032</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2944,19 +2944,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`gällade` (sv)</t>
+          <t>`fördjupningskod` (sv)</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GLP236</t>
+          <t>LP1032</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2966,24 +2966,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`framträdandeform` (sv)</t>
+          <t>`scholary` (en)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GLP29R</t>
+          <t>LP1032</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2993,24 +2993,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`flerspårsmaterial` (sv)</t>
+          <t>`sumarise` (en)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GLP2JZ</t>
+          <t>LP1071</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3025,19 +3025,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`flerspårsmaterial` (sv)</t>
+          <t>`erätter` (sv)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2JZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GLP359</t>
+          <t>LP1071</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3052,19 +3052,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>`djing` (en)</t>
+          <t>`evaulates` (en)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GLP3AH</t>
+          <t>LP2012</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>`ande` (en)</t>
+          <t>`intiate` (en)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GLP3AH</t>
+          <t>LP2013</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3106,19 +3106,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>`excercises` (en)</t>
+          <t>`learnings` (en)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GLP3AR</t>
+          <t>LP2013</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3128,56 +3128,56 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>`tools-miljö` (sv)</t>
+          <t>`litterature` (en)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GLP3AR</t>
+          <t>GMN3EA</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>`prouction` (en)</t>
+          <t>`användar` (sv)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EA</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>LP1032</t>
+          <t>NA1024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>`fördjupningskod` (sv)</t>
+          <t>`efterfråge` (sv)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>LP1032</t>
+          <t>NA1024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3214,51 +3214,51 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>`scholary` (en)</t>
+          <t>`distancelectures` (en)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>LP1032</t>
+          <t>NA1026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>`sumarise` (en)</t>
+          <t>`studieförb` (sv)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>LP1071</t>
+          <t>NA1027</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3268,51 +3268,51 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>`erätter` (sv)</t>
+          <t>`förläsningar` (sv)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>LP1071</t>
+          <t>NA1028</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>`evaulates` (en)</t>
+          <t>`efterfråge` (sv)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1028</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>LP2012</t>
+          <t>NA1029</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>`intiate` (en)</t>
+          <t>`differentiat` (en)</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>LP2013</t>
+          <t>NA1030</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>`learnings` (en)</t>
+          <t>`excercises` (en)</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>LP2013</t>
+          <t>NA1032</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3376,78 +3376,78 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>`litterature` (en)</t>
+          <t>`descirbe` (en)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GMN3E3</t>
+          <t>NA1035</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>`rethoric` (en)</t>
+          <t>`efterfråge` (sv)</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3E3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1035</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GMN3EA</t>
+          <t>NA1036</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>`användar` (sv)</t>
+          <t>`longterm` (en)</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GMN3EX</t>
+          <t>NA1036</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3457,19 +3457,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>`desgin` (en)</t>
+          <t>`shortterm` (en)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GNA2NT</t>
+          <t>NA1039</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3484,19 +3484,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>`assignement` (en)</t>
+          <t>`assingments` (en)</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2NT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GNA3FN</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>`receiva` (en)</t>
+          <t>`kalandermånader` (sv)</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3FN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>NA1024</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3533,24 +3533,24 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>`efterfråge` (sv)</t>
+          <t>`calender` (en)</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>NA1024</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3565,19 +3565,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>`distancelectures` (en)</t>
+          <t>`oppobet` (en)</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>NA1026</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3587,24 +3587,24 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>`studieförb` (sv)</t>
+          <t>`opposnent` (en)</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>NA1027</t>
+          <t>NA2009</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3614,24 +3614,24 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>`förläsningar` (sv)</t>
+          <t>`resultas` (en)</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>NA1028</t>
+          <t>NA3001</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3646,19 +3646,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>`efterfråge` (sv)</t>
+          <t>`länderjämförelser` (sv)</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>NA1029</t>
+          <t>NA3010</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3668,24 +3668,24 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>`differentiat` (en)</t>
+          <t>`kalandermånader` (sv)</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>NA1030</t>
+          <t>NA3011</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3700,51 +3700,51 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>`excercises` (en)</t>
+          <t>`tobbit` (en)</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>NA1032</t>
+          <t>GPE3AJ</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>`descirbe` (en)</t>
+          <t>`kollegialtlärande` (sv)</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>NA1035</t>
+          <t>PE1011</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3754,24 +3754,24 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>`efterfråge` (sv)</t>
+          <t>`hög-skolepoäng` (sv)</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1011</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>NA1036</t>
+          <t>PE1020</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3781,24 +3781,24 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>`longterm` (en)</t>
+          <t>`gryndsyn` (en)</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>NA1036</t>
+          <t>PE1021</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3808,51 +3808,51 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>`shortterm` (en)</t>
+          <t>`centrum` (en)</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1021</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>NA1039</t>
+          <t>PE1023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>`assingments` (en)</t>
+          <t>`lärarlagsarbete` (sv)</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>PE1023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3862,159 +3862,159 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>`kalandermånader` (sv)</t>
+          <t>`rättsäkerhet` (sv)</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>PE1054</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>`calender` (en)</t>
+          <t>`lärstrategier` (sv)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>PE1064</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>`oppobet` (en)</t>
+          <t>`rättsäkerhetsproblematiken` (sv)</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1064</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>PE1067</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>`opposnent` (en)</t>
+          <t>`att` — ….m. 2014-01-24.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>NA2009</t>
+          <t>PE1068</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>`resultas` (en)</t>
+          <t>`känndom` (sv)</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>NA3001</t>
+          <t>PE2005</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>`länderjämförelser` (sv)</t>
+          <t>`gryndsyn` (en)</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>NA3010</t>
+          <t>PE3004</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4024,46 +4024,46 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>`kalandermånader` (sv)</t>
+          <t>`högskole-mässighet` (sv)</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>NA3011</t>
+          <t>PE3004</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>`tobbit` (en)</t>
+          <t>`lärarlagsarbete` (sv)</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GPE3AJ</t>
+          <t>PE3004</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4078,132 +4078,132 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>`kollegialtlärande` (sv)</t>
+          <t>`rättsäkerhet` (sv)</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>PE1011</t>
+          <t>GPA2FW</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>`hög-skolepoäng` (sv)</t>
+          <t>`managemet` (en)</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>PE1020</t>
+          <t>GPA2R6</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>`gryndsyn` (en)</t>
+          <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>PE1021</t>
+          <t>APG24E</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>`centrum` (en)</t>
+          <t>`inlämingsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>PE1023</t>
+          <t>APG24E</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>`lärarlagsarbete` (sv)</t>
+          <t>`credtis` (en)</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>PE1023</t>
+          <t>APG25N</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4213,51 +4213,51 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>`rättsäkerhet` (sv)</t>
+          <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>PE1054</t>
+          <t>APG276</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>`lärstrategier` (sv)</t>
+          <t>`credtis` (en)</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>PE1064</t>
+          <t>APG2AA</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4267,105 +4267,105 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>`rättsäkerhetsproblematiken` (sv)</t>
+          <t>`lärarskicklighetetens` (sv)</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>PE1067</t>
+          <t>APG2AC</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>`att` — ….m. 2014-01-24.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
+          <t>`aanalyze` (en)</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>PE1068</t>
+          <t>APG2AC</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>`känndom` (sv)</t>
+          <t>`nalyze` (en)</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>PE2005</t>
+          <t>APG2CC</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>`gryndsyn` (en)</t>
+          <t>`lärar-elevrelationer` (sv)</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>PE3004</t>
+          <t>APG2CD</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4375,24 +4375,24 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>`högskole-mässighet` (sv)</t>
+          <t>`lärarprofessionsspecifika` (sv)</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>PE3004</t>
+          <t>APG2CM</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4402,105 +4402,105 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>`lärarlagsarbete` (sv)</t>
+          <t>`undervisningensmål` (sv)</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>PE3004</t>
+          <t>GPG22K</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>`rättsäkerhet` (sv)</t>
+          <t>`conciderations` (en)</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GPA2FW</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>`managemet` (en)</t>
+          <t>`samhällorienterande` (sv)</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GPA2R6</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>`tillvägagångsätt` (sv)</t>
+          <t>`hinduism` (en)</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GPA353</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4510,19 +4510,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>`valuest` (en)</t>
+          <t>`sociaty` (en)</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA353</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>APG24E</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4532,24 +4532,24 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>`inlämingsuppgifter` (sv)</t>
+          <t>`understandingn` (en)</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>APG25N</t>
+          <t>GPG328</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4564,19 +4564,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>`tillvägagångsätt` (sv)</t>
+          <t>`andraämne` (sv)</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>APG29G</t>
+          <t>GPG329</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4586,24 +4586,24 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>`asignments` (en)</t>
+          <t>`andraämne` (sv)</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG29G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>APG2AA</t>
+          <t>GPG3AD</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4613,24 +4613,24 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>`lärarskicklighetetens` (sv)</t>
+          <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>APG2AC</t>
+          <t>GPG3CG</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4645,19 +4645,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>`aanalyze` (en)</t>
+          <t>`perspecitves` (en)</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>APG2AC</t>
+          <t>GPG3CK</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4667,24 +4667,24 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>`nalyze` (en)</t>
+          <t>`inlämninguppgift` (sv)</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>APG2AC</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4694,24 +4694,24 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>`rincipal` (en)</t>
+          <t>`samhällorienterande` (sv)</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>APG2C3</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4726,19 +4726,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>`practies` (en)</t>
+          <t>`sociaty` (en)</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>APG2CC</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4748,24 +4748,24 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>`lärar-elevrelationer` (sv)</t>
+          <t>`att` (en)</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>APG2CD</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4775,29 +4775,29 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>`lärarprofessionsspecifika` (sv)</t>
+          <t>`studenten` (en)</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>APG2CD</t>
+          <t>ARK27Q</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4807,78 +4807,78 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>`practicies` (en)</t>
+          <t>`tha` (en)</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>APG2CM</t>
+          <t>ARK29K</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>`undervisningensmål` (sv)</t>
+          <t>`cpecialisation` (en)</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29K</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>APG2CM</t>
+          <t>ARK29L</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>`pratice` (en)</t>
+          <t>`markonivå` (sv)</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29L</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>GPG22K</t>
+          <t>GRK366</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4888,24 +4888,24 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>`conciderations` (en)</t>
+          <t>`enivronments` (en)</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK366</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>GPG27X</t>
+          <t>GRK3B4</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4915,24 +4915,24 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>`lärar` (sv)</t>
+          <t>`ämesteoretiska` (sv)</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4942,132 +4942,132 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>`samhällorienterande` (sv)</t>
+          <t>`mervärdskatt` (sv)</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GRV2MK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>`hinduism` (en)</t>
+          <t>`innhåller` (sv)</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>RV1001</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>`sociaty` (en)</t>
+          <t>`glavå` (sv)</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>`understandingn` (en)</t>
+          <t>`mervärdskatt` (sv)</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>GPG328</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>`andraämne` (sv)</t>
+          <t>`taxat` (en)</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>GPG329</t>
+          <t>RV1009</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5077,105 +5077,105 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>`andraämne` (sv)</t>
+          <t>`eg-rättslig` (sv)</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>GPG3AD</t>
+          <t>RV1009</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
+          <t>`eg-rättsliga` (sv)</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>GPG3CG</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>`perspecitves` (en)</t>
+          <t>`glavå` (sv)</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GPG3CK</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>`inlämninguppgift` (sv)</t>
+          <t>`bargening` (en)</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5185,24 +5185,24 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>`samhällorienterande` (sv)</t>
+          <t>`obestånds` (sv)</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5212,24 +5212,24 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>`sociaty` (en)</t>
+          <t>`pratices` (en)</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GPG3FR</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5239,78 +5239,78 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>`progamme` (en)</t>
+          <t>`securites` (en)</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GPG3FU</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>`developement` (en)</t>
+          <t>`förvaltningsrättliga` (sv)</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>GPG3FU</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>`evalution` (en)</t>
+          <t>`rättsäkerheten` (sv)</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5320,24 +5320,24 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>`att` (en)</t>
+          <t>`xxxxxxxxxxx` (en)</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5347,105 +5347,105 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>`studenten` (en)</t>
+          <t>`xxxxxxxxxxxxx` (en)</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>RV1045</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>`tha` (en)</t>
+          <t>`åtgärdscheman` (sv)</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>ARK29K</t>
+          <t>RV1050</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>`cpecialisation` (en)</t>
+          <t>`eu-rätten` (sv)</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>ARK29L</t>
+          <t>RV1055</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>`markonivå` (sv)</t>
+          <t>`samt` — …aminationsformer  En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,…</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>GRK366</t>
+          <t>ASK22L</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5455,240 +5455,240 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>`enivronments` (en)</t>
+          <t>`formes` (en)</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK366</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>GRK3B4</t>
+          <t>ASK22M</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>`ämesteoretiska` (sv)</t>
+          <t>`reviewscrutiny` (en)</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>ASK289</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>`mervärdskatt` (sv)</t>
+          <t>`adress` (en)</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GRV2MK</t>
+          <t>ASK289</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>`innhåller` (sv)</t>
+          <t>`compative` (en)</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>RV1001</t>
+          <t>GSO2PL</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>`glavå` (sv)</t>
+          <t>`credits` — …7.5 credits, Psychological Perspectives on Social Work 7.5 credits credits and Welfare Measures and User Perspective 15 credits…</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>SO1027</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>`mervärdskatt` (sv)</t>
+          <t>`abilty` (en)</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>ATR26B</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>`taxat` (en)</t>
+          <t>`hållbarbetsmål` (sv)</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>RV1009</t>
+          <t>ATR2BJ</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>`eg-rättslig` (sv)</t>
+          <t>`leaisure` (en)</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>RV1009</t>
+          <t>ATR2BJ</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>`eg-rättsliga` (sv)</t>
+          <t>`uns` (en)</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>GTR22D</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5698,51 +5698,51 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>`glavå` (sv)</t>
+          <t>`samhållsvetenskap` (sv)</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>GTR22D</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>`bargening` (en)</t>
+          <t>`värderigsförmåga` (sv)</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>GTR265</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -5752,24 +5752,24 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>`obestånds` (sv)</t>
+          <t>`fömåga` (sv)</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>GTR265</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5779,51 +5779,51 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>`pratices` (en)</t>
+          <t>`afte` (en)</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>GTR26E</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>`securites` (en)</t>
+          <t>`erätter` (sv)</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5833,51 +5833,51 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>`förvaltningsrättliga` (sv)</t>
+          <t>`förhållningssät` (sv)</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>`rättsäkerheten` (sv)</t>
+          <t>`assignement` (en)</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5887,51 +5887,51 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>`xxxxxxxxxxx` (en)</t>
+          <t>`implmented` (en)</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>GTR2DG</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>`xxxxxxxxxxxxx` (en)</t>
+          <t>`the` — …earch. The course is organised into two parts. In part one, the The course introduces students to quantitative research. The co…</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>RV1045</t>
+          <t>GTR2DG</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5941,24 +5941,24 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>`åtgärdscheman` (sv)</t>
+          <t>`enkätsstudie` (sv)</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>RV1050</t>
+          <t>GTR2DP</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5968,78 +5968,78 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>`eu-rätten` (sv)</t>
+          <t>`värderingsfömåga` (sv)</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>RV1055</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>`samt` — …aminationsformer  En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,…</t>
+          <t>`recourses` (en)</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>ASK22L</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>`formes` (en)</t>
+          <t>`använding` (sv)</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>ASK22M</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6049,24 +6049,24 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>`reviewscrutiny` (en)</t>
+          <t>`lerning` (en)</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>ASK289</t>
+          <t>TR1018</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6076,78 +6076,78 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>`adress` (en)</t>
+          <t>`geodemographic` (en)</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>ASK289</t>
+          <t>TR1024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>`compative` (en)</t>
+          <t>`fömåga` (sv)</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>GSO2PL</t>
+          <t>TR1024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>`credits` — …7.5 credits, Psychological Perspectives on Social Work 7.5 credits credits and Welfare Measures and User Perspective 15 credits…</t>
+          <t>`afte` (en)</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>SO1027</t>
+          <t>TR1025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6157,19 +6157,19 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>`abilty` (en)</t>
+          <t>`studiesand` (en)</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>ATR26B</t>
+          <t>TR1027</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6184,19 +6184,19 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>`hållbarbetsmål` (sv)</t>
+          <t>`fömåga` (sv)</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>ATR2BJ</t>
+          <t>TR1027</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6211,19 +6211,19 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>`leaisure` (en)</t>
+          <t>`afte` (en)</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>ATR2BJ</t>
+          <t>TR1028</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6233,24 +6233,24 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>`uns` (en)</t>
+          <t>`förhållningssät` (sv)</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>GTR22D</t>
+          <t>TR1028</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6260,24 +6260,24 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>`samhållsvetenskap` (sv)</t>
+          <t>`ansd` (en)</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>GTR22D</t>
+          <t>TR1029</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6287,24 +6287,24 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>`värderigsförmåga` (sv)</t>
+          <t>`studiesand` (en)</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>GTR265</t>
+          <t>TR1030</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6319,19 +6319,19 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>`fömåga` (sv)</t>
+          <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>GTR265</t>
+          <t>TR1031</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>`afte` (en)</t>
+          <t>`kulturellafördomar` (sv)</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>GTR26E</t>
+          <t>TR1034</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6373,19 +6373,19 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>`erätter` (sv)</t>
+          <t>`förvärvda` (sv)</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>TR1034</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6395,24 +6395,24 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>`förhållningssät` (sv)</t>
+          <t>`organisaton` (en)</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>TR2004</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6427,19 +6427,19 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>`assignement` (en)</t>
+          <t>`stuides` (en)</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>TR3006</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6449,24 +6449,24 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>`implmented` (en)</t>
+          <t>`the` — …- Independently identify and analyze scientific problems in the the relevant field of knowledge and conduct and report on a pro…</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>TR3006</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6476,724 +6476,157 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>`the` — …earch. The course is organised into two parts. In part one, the The course introduces students to quantitative research. The co…</t>
+          <t>`ocskå` (sv)</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>AS2002</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>`enkätsstudie` (sv)</t>
+          <t>`takenup` (en)</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>GTR2DP</t>
+          <t>AS3002</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>`värderingsfömåga` (sv)</t>
+          <t>`teh` (en)</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>AS3009</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>`recourses` (en)</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>TR1013</t>
+          <t>AS3012</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>`använding` (sv)</t>
+          <t>`outlineof` (en)</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>TR1013</t>
+          <t>AS4003</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>`lerning` (en)</t>
+          <t>`angrepssätt` (sv)</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>TR1018</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>`geodemographic` (en)</t>
-        </is>
-      </c>
-      <c r="E230" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
-        <is>
-          <t>TR1024</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>`fömåga` (sv)</t>
-        </is>
-      </c>
-      <c r="E231" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
-        <is>
-          <t>TR1024</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>`afte` (en)</t>
-        </is>
-      </c>
-      <c r="E232" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
-        <is>
-          <t>TR1025</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>`studiesand` (en)</t>
-        </is>
-      </c>
-      <c r="E233" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
-        <is>
-          <t>TR1027</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>`fömåga` (sv)</t>
-        </is>
-      </c>
-      <c r="E234" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
-        <is>
-          <t>TR1027</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>`afte` (en)</t>
-        </is>
-      </c>
-      <c r="E235" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
-        <is>
-          <t>TR1028</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>`förhållningssät` (sv)</t>
-        </is>
-      </c>
-      <c r="E236" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
-        <is>
-          <t>TR1028</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>`ansd` (en)</t>
-        </is>
-      </c>
-      <c r="E237" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>TR1029</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>`studiesand` (en)</t>
-        </is>
-      </c>
-      <c r="E238" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>TR1030</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>`tillvägagångsätt` (sv)</t>
-        </is>
-      </c>
-      <c r="E239" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
-        <is>
-          <t>TR1031</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>`kulturellafördomar` (sv)</t>
-        </is>
-      </c>
-      <c r="E240" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>TR1034</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>`förvärvda` (sv)</t>
-        </is>
-      </c>
-      <c r="E241" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>TR1034</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>`organisaton` (en)</t>
-        </is>
-      </c>
-      <c r="E242" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="2" t="inlineStr">
-        <is>
-          <t>TR2004</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>`stuides` (en)</t>
-        </is>
-      </c>
-      <c r="E243" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
-        <is>
-          <t>TR3006</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Dubblerat ord</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>`the` — …- Independently identify and analyze scientific problems in the the relevant field of knowledge and conduct and report on a pro…</t>
-        </is>
-      </c>
-      <c r="E244" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
-        <is>
-          <t>TR3006</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>`ocskå` (sv)</t>
-        </is>
-      </c>
-      <c r="E245" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
-        <is>
-          <t>AS2002</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>`takenup` (en)</t>
-        </is>
-      </c>
-      <c r="E246" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
-        <is>
-          <t>AS3002</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>`teh` (en)</t>
-        </is>
-      </c>
-      <c r="E247" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>AS3009</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>`literära` (sv)</t>
-        </is>
-      </c>
-      <c r="E248" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
-        <is>
-          <t>AS3012</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>`outlineof` (en)</t>
-        </is>
-      </c>
-      <c r="E249" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
-        <is>
-          <t>AS4003</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>`angrepssätt` (sv)</t>
-        </is>
-      </c>
-      <c r="E250" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E250"/>
+  <autoFilter ref="A1:E229"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -7651,48 +7084,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId454"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A229" r:id="rId455"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A230" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E230" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A231" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A232" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A233" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E233" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A234" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E234" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A235" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E235" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A236" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E236" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A237" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E237" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A238" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E238" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A239" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E239" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A240" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E240" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A241" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E241" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A242" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E242" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A243" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E243" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A244" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E244" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A245" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E245" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A246" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E246" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A247" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E247" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A248" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E248" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A249" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E249" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A250" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E250" r:id="rId498"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$229</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$204</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E229"/>
+  <dimension ref="A1:E204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1012,7 +1012,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GBQ38V</t>
+          <t>GBQ38W</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`mediacomposer-miljö` (sv)</t>
+          <t>`höguppupplöst` (sv)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GBQ38W</t>
+          <t>GBQ3A6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1054,19 +1054,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`composer-miljö` (sv)</t>
+          <t>`användar` (sv)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GBQ38W</t>
+          <t>GBQ3AW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1076,24 +1076,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`höguppupplöst` (sv)</t>
+          <t>`explainer` (en)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A6</t>
+          <t>GBQ3FG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1103,29 +1103,29 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`användar` (sv)</t>
+          <t>`excercises` (en)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A7</t>
+          <t>EU1027</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1135,78 +1135,78 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`wars-berättelserna` (sv)</t>
+          <t>`grundäggande` (sv)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1027</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A7</t>
+          <t>EU1033</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`wars-berättelsernas` (sv)</t>
+          <t>`itssocial` (en)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1033</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AW</t>
+          <t>EU1034</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`explainer` (en)</t>
+          <t>`förhandlingprocesser` (sv)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1034</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GBQ3FG</t>
+          <t>GEU2KV</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`excercises` (en)</t>
+          <t>`opportunties` (en)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>EU1027</t>
+          <t>GEU2KV</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1238,29 +1238,29 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`grundäggande` (sv)</t>
+          <t>`willll` (en)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>EU1033</t>
+          <t>AFI273</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1270,51 +1270,51 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`itssocial` (en)</t>
+          <t>`contignency` (en)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFI273</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>EU1034</t>
+          <t>FI1023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`förhandlingprocesser` (sv)</t>
+          <t>`philosohical` (en)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GEU2KV</t>
+          <t>FI1024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1324,46 +1324,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`opportunties` (en)</t>
+          <t>`etichs` (en)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GEU2KV</t>
+          <t>FI1039</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`willll` (en)</t>
+          <t>`have` — …urthermore, on completion of the course, the student should have have the ability to :       - be reflective in relation to probl…</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>AFI273</t>
+          <t>FI1039</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1378,19 +1378,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`contignency` (en)</t>
+          <t>`asessment` (en)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFI273</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>FI1023</t>
+          <t>FI1039</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1405,19 +1405,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`philosohical` (en)</t>
+          <t>`developement` (en)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>FI1024</t>
+          <t>GFI3BT</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1432,19 +1432,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`etichs` (en)</t>
+          <t>`througout` (en)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>FI1039</t>
+          <t>GFI3BU</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1454,56 +1454,56 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`have` — …urthermore, on completion of the course, the student should have have the ability to :       - be reflective in relation to probl…</t>
+          <t>`througout` (en)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>FI1039</t>
+          <t>AHI272</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`asessment` (en)</t>
+          <t>`europeiskspråkiga` (sv)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>FI1039</t>
+          <t>AHI272</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`developement` (en)</t>
+          <t>`poitical` (en)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>FI2003</t>
+          <t>AHI29Q</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`filosofi` (en)</t>
+          <t>`consultaion` (en)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GFI3BT</t>
+          <t>AHI29Q</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`througout` (en)</t>
+          <t>`situatin` (en)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GFI3BU</t>
+          <t>AS2005</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1594,19 +1594,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`througout` (en)</t>
+          <t>`takenup` (en)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2005</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>AHI272</t>
+          <t>AS3017</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1621,19 +1621,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`europeiskspråkiga` (sv)</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>AHI272</t>
+          <t>AS3020</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1648,19 +1648,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`poitical` (en)</t>
+          <t>`outlineof` (en)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>AHI29Q</t>
+          <t>AS3022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`consultaion` (en)</t>
+          <t>`teh` (en)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>AHI29Q</t>
+          <t>GHI29Y</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1697,24 +1697,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`situatin` (en)</t>
+          <t>`innhållet` (sv)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>AS2005</t>
+          <t>GHI33T</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1724,24 +1724,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`takenup` (en)</t>
+          <t>`problemförmuleringsförmåga` (sv)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>AS3017</t>
+          <t>GHI33V</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`literära` (sv)</t>
+          <t>`delkurseninnehåller` (sv)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>AS3020</t>
+          <t>GHI33V</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1778,24 +1778,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`outlineof` (en)</t>
+          <t>`godkäng` (sv)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>AS3022</t>
+          <t>GHI35A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1805,24 +1805,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`teh` (en)</t>
+          <t>`analyseratmänniskors` (sv)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GHI29Y</t>
+          <t>GHI35A</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`innhållet` (sv)</t>
+          <t>`medförintelsen` (sv)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GHI33T</t>
+          <t>GHI35A</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`problemförmuleringsförmåga` (sv)</t>
+          <t>`människorsagerande` (sv)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GHI33V</t>
+          <t>GHI362</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1891,19 +1891,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`delkurseninnehåller` (sv)</t>
+          <t>`självstänigt` (sv)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GHI33V</t>
+          <t>HI1008</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1913,24 +1913,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`godkäng` (sv)</t>
+          <t>`criterions` (en)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GHI35A</t>
+          <t>HI2011</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1945,19 +1945,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`analyseratmänniskors` (sv)</t>
+          <t>`historiedidaktikområdet` (sv)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GHI35A</t>
+          <t>HI2012</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1972,19 +1972,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`medförintelsen` (sv)</t>
+          <t>`sjävvalt` (sv)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GHI35A</t>
+          <t>HI2016</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1999,19 +1999,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`människorsagerande` (sv)</t>
+          <t>`sjävvalt` (sv)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GHI362</t>
+          <t>HI3019</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`självstänigt` (sv)</t>
+          <t>`självständg` (sv)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3019</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>HI1008</t>
+          <t>AKG27R</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2053,78 +2053,78 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`criterions` (en)</t>
+          <t>`compulsotry` (en)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>HI2011</t>
+          <t>AKG27R</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`historiedidaktikområdet` (sv)</t>
+          <t>`curent` (en)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>HI2012</t>
+          <t>AKG27R</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`sjävvalt` (sv)</t>
+          <t>`theoretica` (en)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>HI2016</t>
+          <t>GKG3AT</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2134,46 +2134,46 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`sjävvalt` (sv)</t>
+          <t>`tilllämpas` (sv)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>HI3019</t>
+          <t>GKG3AT</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`självständg` (sv)</t>
+          <t>`writtten` (en)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>AKG27R</t>
+          <t>KG1024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2183,24 +2183,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`compulsotry` (en)</t>
+          <t>`beräklningstung` (sv)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>AKG27R</t>
+          <t>KG1024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2215,19 +2215,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`curent` (en)</t>
+          <t>`quantitativ` (en)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>AKG27R</t>
+          <t>KG1025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2242,19 +2242,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`theoretica` (en)</t>
+          <t>`evolvement` (en)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GKG3AT</t>
+          <t>KG1025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2264,24 +2264,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`tilllämpas` (sv)</t>
+          <t>`thise` (en)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GKG3AT</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2296,19 +2296,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`writtten` (en)</t>
+          <t>`obser` (en)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>KG1016</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2323,19 +2323,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`datalaborations` (en)</t>
+          <t>`perspetives` (en)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>KG1024</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2345,24 +2345,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`beräklningstung` (sv)</t>
+          <t>`standarized` (en)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>KG1024</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2377,19 +2377,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`quantitativ` (en)</t>
+          <t>`vations` (en)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>KG1025</t>
+          <t>KG2005</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`evolvement` (en)</t>
+          <t>`qualititative` (en)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>KG1025</t>
+          <t>KG3010</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2431,19 +2431,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`thise` (en)</t>
+          <t>`recognises` (en)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>KG3011</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2453,24 +2453,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`obser` (en)</t>
+          <t>`kartöverlägg` (sv)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>KG3011</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2480,24 +2480,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`perspetives` (en)</t>
+          <t>`skalnivå` (sv)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>KG3014</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`standarized` (en)</t>
+          <t>`eaxaminer` (en)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>KG3015</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`vations` (en)</t>
+          <t>`eaxaminer` (en)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>KG2005</t>
+          <t>KG3016</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2561,56 +2561,56 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`qualititative` (en)</t>
+          <t>`gällade` (sv)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>KG3010</t>
+          <t>GLP236</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`recognises` (en)</t>
+          <t>`framträdandeform` (sv)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>KG3011</t>
+          <t>GLP29R</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`kartöverlägg` (sv)</t>
+          <t>`flerspårsmaterial` (sv)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29R</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>KG3011</t>
+          <t>GLP2JZ</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`skalnivå` (sv)</t>
+          <t>`flerspårsmaterial` (sv)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2JZ</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>KG3014</t>
+          <t>GLP359</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`eaxaminer` (en)</t>
+          <t>`djing` (en)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>KG3015</t>
+          <t>GLP3AH</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`eaxaminer` (en)</t>
+          <t>`excercises` (en)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>KG3016</t>
+          <t>LP1032</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2728,19 +2728,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`gällade` (sv)</t>
+          <t>`fördjupningskod` (sv)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GLP236</t>
+          <t>LP1032</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2750,24 +2750,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`framträdandeform` (sv)</t>
+          <t>`scholary` (en)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GLP29R</t>
+          <t>LP1032</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2777,24 +2777,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`flerspårsmaterial` (sv)</t>
+          <t>`sumarise` (en)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GLP2JZ</t>
+          <t>LP1071</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2809,19 +2809,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`flerspårsmaterial` (sv)</t>
+          <t>`erätter` (sv)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2JZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GLP359</t>
+          <t>LP1071</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2836,19 +2836,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`djing` (en)</t>
+          <t>`evaulates` (en)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GLP3AH</t>
+          <t>LP2012</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2863,19 +2863,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`ande` (en)</t>
+          <t>`intiate` (en)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GLP3AH</t>
+          <t>LP2013</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2890,19 +2890,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`excercises` (en)</t>
+          <t>`learnings` (en)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GLP3AR</t>
+          <t>LP2013</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2912,29 +2912,29 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`tools-miljö` (sv)</t>
+          <t>`litterature` (en)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>LP1032</t>
+          <t>GMN3EA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2944,51 +2944,51 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`fördjupningskod` (sv)</t>
+          <t>`användar` (sv)</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EA</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>LP1032</t>
+          <t>NA1024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`scholary` (en)</t>
+          <t>`efterfråge` (sv)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>LP1032</t>
+          <t>NA1024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2998,24 +2998,24 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`sumarise` (en)</t>
+          <t>`distancelectures` (en)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>LP1071</t>
+          <t>NA1026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3025,78 +3025,78 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`erätter` (sv)</t>
+          <t>`studieförb` (sv)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>LP1071</t>
+          <t>NA1027</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>`evaulates` (en)</t>
+          <t>`förläsningar` (sv)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>LP2012</t>
+          <t>NA1028</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>`intiate` (en)</t>
+          <t>`efterfråge` (sv)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1028</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>LP2013</t>
+          <t>NA1029</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>`learnings` (en)</t>
+          <t>`differentiat` (en)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>LP2013</t>
+          <t>NA1030</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3133,46 +3133,46 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>`litterature` (en)</t>
+          <t>`excercises` (en)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GMN3EA</t>
+          <t>NA1032</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>`användar` (sv)</t>
+          <t>`descirbe` (en)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>NA1024</t>
+          <t>NA1035</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3192,14 +3192,14 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1035</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>NA1024</t>
+          <t>NA1036</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3214,19 +3214,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>`distancelectures` (en)</t>
+          <t>`longterm` (en)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>NA1026</t>
+          <t>NA1036</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3236,24 +3236,24 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>`studieförb` (sv)</t>
+          <t>`shortterm` (en)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>NA1027</t>
+          <t>NA1039</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3263,24 +3263,24 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>`förläsningar` (sv)</t>
+          <t>`assingments` (en)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>NA1028</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3295,19 +3295,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>`efterfråge` (sv)</t>
+          <t>`kalandermånader` (sv)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>NA1029</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3322,19 +3322,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>`differentiat` (en)</t>
+          <t>`calender` (en)</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>NA1030</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3349,19 +3349,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>`excercises` (en)</t>
+          <t>`oppobet` (en)</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>NA1032</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3376,19 +3376,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>`descirbe` (en)</t>
+          <t>`opposnent` (en)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>NA1035</t>
+          <t>NA2009</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3398,24 +3398,24 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>`efterfråge` (sv)</t>
+          <t>`resultas` (en)</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>NA1036</t>
+          <t>NA3001</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3425,24 +3425,24 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>`longterm` (en)</t>
+          <t>`länderjämförelser` (sv)</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>NA1036</t>
+          <t>NA3010</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3452,24 +3452,24 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>`shortterm` (en)</t>
+          <t>`kalandermånader` (sv)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>NA1039</t>
+          <t>NA3011</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>`assingments` (en)</t>
+          <t>`tobbit` (en)</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>GPE3AJ</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3511,24 +3511,24 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>`kalandermånader` (sv)</t>
+          <t>`kollegialtlärande` (sv)</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>PE1020</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3538,105 +3538,105 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>`calender` (en)</t>
+          <t>`gryndsyn` (en)</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>PE1023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>`oppobet` (en)</t>
+          <t>`lärarlagsarbete` (sv)</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>PE1023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>`opposnent` (en)</t>
+          <t>`rättsäkerhet` (sv)</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>NA2009</t>
+          <t>PE1054</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>`resultas` (en)</t>
+          <t>`lärstrategier` (sv)</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>NA3001</t>
+          <t>PE1064</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3646,73 +3646,73 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>`länderjämförelser` (sv)</t>
+          <t>`rättsäkerhetsproblematiken` (sv)</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1064</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>NA3010</t>
+          <t>PE1067</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>`kalandermånader` (sv)</t>
+          <t>`att` — ….m. 2014-01-24.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>NA3011</t>
+          <t>PE1068</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>`tobbit` (en)</t>
+          <t>`känndom` (sv)</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GPE3AJ</t>
+          <t>PE2005</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3722,24 +3722,24 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>`kollegialtlärande` (sv)</t>
+          <t>`gryndsyn` (en)</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>PE1011</t>
+          <t>PE3004</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3754,19 +3754,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>`hög-skolepoäng` (sv)</t>
+          <t>`lärarlagsarbete` (sv)</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>PE1020</t>
+          <t>PE3004</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3776,29 +3776,29 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>`gryndsyn` (en)</t>
+          <t>`rättsäkerhet` (sv)</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>PE1021</t>
+          <t>GPA2FW</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3808,24 +3808,24 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>`centrum` (en)</t>
+          <t>`managemet` (en)</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>PE1023</t>
+          <t>GPA2R6</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3835,24 +3835,24 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>`lärarlagsarbete` (sv)</t>
+          <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>PE1023</t>
+          <t>APG24E</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3862,51 +3862,51 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>`rättsäkerhet` (sv)</t>
+          <t>`inlämingsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>PE1054</t>
+          <t>APG24E</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>`lärstrategier` (sv)</t>
+          <t>`credtis` (en)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>PE1064</t>
+          <t>APG25N</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3916,51 +3916,51 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>`rättsäkerhetsproblematiken` (sv)</t>
+          <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>PE1067</t>
+          <t>APG276</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>`att` — ….m. 2014-01-24.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
+          <t>`credtis` (en)</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>PE1068</t>
+          <t>APG2AA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3970,24 +3970,24 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>`känndom` (sv)</t>
+          <t>`lärarskicklighetetens` (sv)</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>PE2005</t>
+          <t>APG2AC</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3997,51 +3997,51 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>`gryndsyn` (en)</t>
+          <t>`aanalyze` (en)</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>PE3004</t>
+          <t>APG2AC</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>`högskole-mässighet` (sv)</t>
+          <t>`nalyze` (en)</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>PE3004</t>
+          <t>APG2CD</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4051,24 +4051,24 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>`lärarlagsarbete` (sv)</t>
+          <t>`lärarprofessionsspecifika` (sv)</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>PE3004</t>
+          <t>APG2CM</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4078,24 +4078,24 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>`rättsäkerhet` (sv)</t>
+          <t>`undervisningensmål` (sv)</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GPA2FW</t>
+          <t>GPG22K</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4105,24 +4105,24 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>`managemet` (en)</t>
+          <t>`conciderations` (en)</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GPA2R6</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4132,19 +4132,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>`tillvägagångsätt` (sv)</t>
+          <t>`samhällorienterande` (sv)</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>APG24E</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4154,24 +4154,24 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>`inlämingsuppgifter` (sv)</t>
+          <t>`sociaty` (en)</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>APG24E</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4186,19 +4186,19 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>`credtis` (en)</t>
+          <t>`understandingn` (en)</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>APG25N</t>
+          <t>GPG328</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4213,19 +4213,19 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>`tillvägagångsätt` (sv)</t>
+          <t>`andraämne` (sv)</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>APG276</t>
+          <t>GPG329</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4235,24 +4235,24 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>`credtis` (en)</t>
+          <t>`andraämne` (sv)</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>APG2AA</t>
+          <t>GPG3AD</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4262,24 +4262,24 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>`lärarskicklighetetens` (sv)</t>
+          <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>APG2AC</t>
+          <t>GPG3CG</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4294,19 +4294,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>`aanalyze` (en)</t>
+          <t>`perspecitves` (en)</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>APG2AC</t>
+          <t>GPG3CK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4316,24 +4316,24 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>`nalyze` (en)</t>
+          <t>`inlämninguppgift` (sv)</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>APG2CC</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4348,19 +4348,19 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>`lärar-elevrelationer` (sv)</t>
+          <t>`samhällorienterande` (sv)</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>APG2CD</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4370,56 +4370,56 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>`lärarprofessionsspecifika` (sv)</t>
+          <t>`sociaty` (en)</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>APG2CM</t>
+          <t>ARK27Q</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>`undervisningensmål` (sv)</t>
+          <t>`tha` (en)</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GPG22K</t>
+          <t>ARK29K</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4429,24 +4429,24 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>`conciderations` (en)</t>
+          <t>`cpecialisation` (en)</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29K</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>ARK29L</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4456,24 +4456,24 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>`samhällorienterande` (sv)</t>
+          <t>`markonivå` (sv)</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29L</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GRK366</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4483,78 +4483,78 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>`hinduism` (en)</t>
+          <t>`enivronments` (en)</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK366</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GRK3B4</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>`sociaty` (en)</t>
+          <t>`ämesteoretiska` (sv)</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>`understandingn` (en)</t>
+          <t>`mervärdskatt` (sv)</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>GPG328</t>
+          <t>GRV2MK</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4564,24 +4564,24 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>`andraämne` (sv)</t>
+          <t>`innhåller` (sv)</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GPG329</t>
+          <t>RV1001</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4591,105 +4591,105 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>`andraämne` (sv)</t>
+          <t>`glavå` (sv)</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>GPG3AD</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
+          <t>`mervärdskatt` (sv)</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>GPG3CG</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>`perspecitves` (en)</t>
+          <t>`glavå` (sv)</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GPG3CK</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>`inlämninguppgift` (sv)</t>
+          <t>`bargening` (en)</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4699,24 +4699,24 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>`samhällorienterande` (sv)</t>
+          <t>`obestånds` (sv)</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4726,24 +4726,24 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>`sociaty` (en)</t>
+          <t>`pratices` (en)</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4753,132 +4753,132 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>`att` (en)</t>
+          <t>`securites` (en)</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>`studenten` (en)</t>
+          <t>`förvaltningsrättliga` (sv)</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>`tha` (en)</t>
+          <t>`rättsäkerheten` (sv)</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>ARK29K</t>
+          <t>RV1045</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>`cpecialisation` (en)</t>
+          <t>`åtgärdscheman` (sv)</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>ARK29L</t>
+          <t>RV1055</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>`markonivå` (sv)</t>
+          <t>`samt` — …aminationsformer  En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,…</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>GRK366</t>
+          <t>ASK22L</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4888,132 +4888,132 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>`enivronments` (en)</t>
+          <t>`formes` (en)</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK366</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>GRK3B4</t>
+          <t>ASK22M</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>`ämesteoretiska` (sv)</t>
+          <t>`reviewscrutiny` (en)</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>ASK289</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>`mervärdskatt` (sv)</t>
+          <t>`compative` (en)</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GRV2MK</t>
+          <t>GSO2PL</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>`innhåller` (sv)</t>
+          <t>`credits` — …7.5 credits, Psychological Perspectives on Social Work 7.5 credits credits and Welfare Measures and User Perspective 15 credits…</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>RV1001</t>
+          <t>SO1027</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>`glavå` (sv)</t>
+          <t>`abilty` (en)</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>ATR26B</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5023,24 +5023,24 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>`mervärdskatt` (sv)</t>
+          <t>`hållbarbetsmål` (sv)</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>ATR2BJ</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5050,24 +5050,24 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>`taxat` (en)</t>
+          <t>`leaisure` (en)</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>RV1009</t>
+          <t>GTR22D</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5077,24 +5077,24 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>`eg-rättslig` (sv)</t>
+          <t>`samhållsvetenskap` (sv)</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>RV1009</t>
+          <t>GTR22D</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5104,24 +5104,24 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>`eg-rättsliga` (sv)</t>
+          <t>`värderigsförmåga` (sv)</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>GTR265</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5131,24 +5131,24 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>`glavå` (sv)</t>
+          <t>`fömåga` (sv)</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>GTR265</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5158,24 +5158,24 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>`bargening` (en)</t>
+          <t>`afte` (en)</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>GTR26E</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5185,51 +5185,51 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>`obestånds` (sv)</t>
+          <t>`erätter` (sv)</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>`pratices` (en)</t>
+          <t>`förhållningssät` (sv)</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5239,159 +5239,159 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>`securites` (en)</t>
+          <t>`assignement` (en)</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>`förvaltningsrättliga` (sv)</t>
+          <t>`implmented` (en)</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>GTR2DG</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>`rättsäkerheten` (sv)</t>
+          <t>`the` — …earch. The course is organised into two parts. In part one, the The course introduces students to quantitative research. The co…</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>GTR2DG</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>`xxxxxxxxxxx` (en)</t>
+          <t>`enkätsstudie` (sv)</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>GTR2DP</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>`xxxxxxxxxxxxx` (en)</t>
+          <t>`värderingsfömåga` (sv)</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>RV1045</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>`åtgärdscheman` (sv)</t>
+          <t>`recourses` (en)</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>RV1050</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5401,51 +5401,51 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>`eu-rätten` (sv)</t>
+          <t>`använding` (sv)</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>RV1055</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>`samt` — …aminationsformer  En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,…</t>
+          <t>`lerning` (en)</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>ASK22L</t>
+          <t>TR1018</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5455,51 +5455,51 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>`formes` (en)</t>
+          <t>`geodemographic` (en)</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>ASK22M</t>
+          <t>TR1024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>`reviewscrutiny` (en)</t>
+          <t>`fömåga` (sv)</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>ASK289</t>
+          <t>TR1024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5509,100 +5509,100 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>`adress` (en)</t>
+          <t>`afte` (en)</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>ASK289</t>
+          <t>TR1027</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>`compative` (en)</t>
+          <t>`fömåga` (sv)</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>GSO2PL</t>
+          <t>TR1027</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>`credits` — …7.5 credits, Psychological Perspectives on Social Work 7.5 credits credits and Welfare Measures and User Perspective 15 credits…</t>
+          <t>`afte` (en)</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>SO1027</t>
+          <t>TR1028</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>`abilty` (en)</t>
+          <t>`förhållningssät` (sv)</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>ATR26B</t>
+          <t>TR1028</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5612,24 +5612,24 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>`hållbarbetsmål` (sv)</t>
+          <t>`ansd` (en)</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>ATR2BJ</t>
+          <t>TR1030</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5639,24 +5639,24 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>`leaisure` (en)</t>
+          <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>ATR2BJ</t>
+          <t>TR1031</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5666,24 +5666,24 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>`uns` (en)</t>
+          <t>`kulturellafördomar` (sv)</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>GTR22D</t>
+          <t>TR1034</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5698,19 +5698,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>`samhållsvetenskap` (sv)</t>
+          <t>`förvärvda` (sv)</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>GTR22D</t>
+          <t>TR1034</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5720,24 +5720,24 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>`värderigsförmåga` (sv)</t>
+          <t>`organisaton` (en)</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>GTR265</t>
+          <t>TR2004</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5747,24 +5747,24 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>`fömåga` (sv)</t>
+          <t>`stuides` (en)</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>GTR265</t>
+          <t>TR3006</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5774,24 +5774,24 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>`afte` (en)</t>
+          <t>`the` — …- Independently identify and analyze scientific problems in the the relevant field of knowledge and conduct and report on a pro…</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>GTR26E</t>
+          <t>TR3006</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5806,51 +5806,51 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>`erätter` (sv)</t>
+          <t>`ocskå` (sv)</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>AS2002</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>`förhållningssät` (sv)</t>
+          <t>`takenup` (en)</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>AS3002</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5860,78 +5860,78 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>`assignement` (en)</t>
+          <t>`teh` (en)</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>AS3009</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>`implmented` (en)</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>AS3012</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>`the` — …earch. The course is organised into two parts. In part one, the The course introduces students to quantitative research. The co…</t>
+          <t>`outlineof` (en)</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>AS4003</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5941,692 +5941,17 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>`enkätsstudie` (sv)</t>
+          <t>`angrepssätt` (sv)</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
-        <is>
-          <t>GTR2DP</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>`värderingsfömåga` (sv)</t>
-        </is>
-      </c>
-      <c r="E205" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
-        <is>
-          <t>TR1007</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>`recourses` (en)</t>
-        </is>
-      </c>
-      <c r="E206" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
-        <is>
-          <t>TR1013</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>`använding` (sv)</t>
-        </is>
-      </c>
-      <c r="E207" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
-        <is>
-          <t>TR1013</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>`lerning` (en)</t>
-        </is>
-      </c>
-      <c r="E208" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
-        <is>
-          <t>TR1018</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>`geodemographic` (en)</t>
-        </is>
-      </c>
-      <c r="E209" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>TR1024</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>`fömåga` (sv)</t>
-        </is>
-      </c>
-      <c r="E210" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
-        <is>
-          <t>TR1024</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>`afte` (en)</t>
-        </is>
-      </c>
-      <c r="E211" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
-        <is>
-          <t>TR1025</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>`studiesand` (en)</t>
-        </is>
-      </c>
-      <c r="E212" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1025</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
-        <is>
-          <t>TR1027</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>`fömåga` (sv)</t>
-        </is>
-      </c>
-      <c r="E213" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>TR1027</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>`afte` (en)</t>
-        </is>
-      </c>
-      <c r="E214" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
-        <is>
-          <t>TR1028</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>`förhållningssät` (sv)</t>
-        </is>
-      </c>
-      <c r="E215" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>TR1028</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>`ansd` (en)</t>
-        </is>
-      </c>
-      <c r="E216" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
-        <is>
-          <t>TR1029</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>`studiesand` (en)</t>
-        </is>
-      </c>
-      <c r="E217" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1029</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>TR1030</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>`tillvägagångsätt` (sv)</t>
-        </is>
-      </c>
-      <c r="E218" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
-        <is>
-          <t>TR1031</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>`kulturellafördomar` (sv)</t>
-        </is>
-      </c>
-      <c r="E219" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>TR1034</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>`förvärvda` (sv)</t>
-        </is>
-      </c>
-      <c r="E220" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>TR1034</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>`organisaton` (en)</t>
-        </is>
-      </c>
-      <c r="E221" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>TR2004</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>`stuides` (en)</t>
-        </is>
-      </c>
-      <c r="E222" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
-        <is>
-          <t>TR3006</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Dubblerat ord</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>`the` — …- Independently identify and analyze scientific problems in the the relevant field of knowledge and conduct and report on a pro…</t>
-        </is>
-      </c>
-      <c r="E223" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
-        <is>
-          <t>TR3006</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>`ocskå` (sv)</t>
-        </is>
-      </c>
-      <c r="E224" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>AS2002</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>`takenup` (en)</t>
-        </is>
-      </c>
-      <c r="E225" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>AS3002</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>`teh` (en)</t>
-        </is>
-      </c>
-      <c r="E226" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>AS3009</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>`literära` (sv)</t>
-        </is>
-      </c>
-      <c r="E227" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>AS3012</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>`outlineof` (en)</t>
-        </is>
-      </c>
-      <c r="E228" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
-        <is>
-          <t>AS4003</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>`angrepssätt` (sv)</t>
-        </is>
-      </c>
-      <c r="E229" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E229"/>
+  <autoFilter ref="A1:E204"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -7034,56 +6359,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A206" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A207" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A208" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E208" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A209" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E209" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A210" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E210" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A211" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E211" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A212" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E212" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A213" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E213" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A214" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E214" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A215" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E215" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A216" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E216" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A217" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E217" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A218" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E218" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A219" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E219" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A220" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E220" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A221" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E221" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A222" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E222" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A223" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E223" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A224" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E224" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A225" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E225" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A226" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E226" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A227" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E227" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A228" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E228" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A229" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E229" r:id="rId456"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$203</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E204"/>
+  <dimension ref="A1:E203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`europeiskspråkiga` (sv)</t>
+          <t>`poitical` (en)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>AHI272</t>
+          <t>AHI29Q</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,12 +1513,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`poitical` (en)</t>
+          <t>`consultaion` (en)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`consultaion` (en)</t>
+          <t>`situatin` (en)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>AHI29Q</t>
+          <t>AS2005</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1567,19 +1567,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`situatin` (en)</t>
+          <t>`takenup` (en)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2005</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>AS2005</t>
+          <t>AS3017</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1589,24 +1589,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`takenup` (en)</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>AS3017</t>
+          <t>AS3020</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`literära` (sv)</t>
+          <t>`outlineof` (en)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>AS3020</t>
+          <t>AS3022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1648,19 +1648,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`outlineof` (en)</t>
+          <t>`teh` (en)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>AS3022</t>
+          <t>GHI29Y</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1670,24 +1670,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`teh` (en)</t>
+          <t>`innhållet` (sv)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GHI29Y</t>
+          <t>GHI33T</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1702,19 +1702,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`innhållet` (sv)</t>
+          <t>`problemförmuleringsförmåga` (sv)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GHI33T</t>
+          <t>GHI33V</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`problemförmuleringsförmåga` (sv)</t>
+          <t>`delkurseninnehåller` (sv)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`delkurseninnehåller` (sv)</t>
+          <t>`godkäng` (sv)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -1768,7 +1768,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GHI33V</t>
+          <t>GHI35A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1783,12 +1783,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`godkäng` (sv)</t>
+          <t>`analyseratmänniskors` (sv)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`analyseratmänniskors` (sv)</t>
+          <t>`medförintelsen` (sv)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`medförintelsen` (sv)</t>
+          <t>`människorsagerande` (sv)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GHI35A</t>
+          <t>GHI362</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`människorsagerande` (sv)</t>
+          <t>`självstänigt` (sv)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GHI362</t>
+          <t>HI1008</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1886,24 +1886,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`självstänigt` (sv)</t>
+          <t>`criterions` (en)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>HI1008</t>
+          <t>HI2011</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1913,24 +1913,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`criterions` (en)</t>
+          <t>`historiedidaktikområdet` (sv)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>HI2011</t>
+          <t>HI2012</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1945,19 +1945,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`historiedidaktikområdet` (sv)</t>
+          <t>`sjävvalt` (sv)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>HI2012</t>
+          <t>HI2016</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1977,14 +1977,14 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>HI2016</t>
+          <t>HI3019</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1999,39 +1999,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`sjävvalt` (sv)</t>
+          <t>`självständg` (sv)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3019</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>HI3019</t>
+          <t>AKG27R</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`självständg` (sv)</t>
+          <t>`compulsotry` (en)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`compulsotry` (en)</t>
+          <t>`curent` (en)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`curent` (en)</t>
+          <t>`theoretica` (en)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2092,7 +2092,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>AKG27R</t>
+          <t>GKG3AT</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2102,17 +2102,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`theoretica` (en)</t>
+          <t>`tilllämpas` (sv)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`tilllämpas` (sv)</t>
+          <t>`writtten` (en)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GKG3AT</t>
+          <t>KG1024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2156,17 +2156,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`writtten` (en)</t>
+          <t>`beräklningstung` (sv)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
         </is>
       </c>
     </row>
@@ -2183,12 +2183,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`beräklningstung` (sv)</t>
+          <t>`quantitativ` (en)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>KG1024</t>
+          <t>KG1025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2215,12 +2215,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`quantitativ` (en)</t>
+          <t>`evolvement` (en)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`evolvement` (en)</t>
+          <t>`thise` (en)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>KG1025</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2269,12 +2269,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`thise` (en)</t>
+          <t>`obser` (en)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`obser` (en)</t>
+          <t>`perspetives` (en)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`perspetives` (en)</t>
+          <t>`standarized` (en)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`standarized` (en)</t>
+          <t>`vations` (en)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>KG2005</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2377,19 +2377,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`vations` (en)</t>
+          <t>`qualititative` (en)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>KG2005</t>
+          <t>KG3010</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`qualititative` (en)</t>
+          <t>`recognises` (en)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>KG3010</t>
+          <t>KG3011</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2426,17 +2426,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`recognises` (en)</t>
+          <t>`kartöverlägg` (sv)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`kartöverlägg` (sv)</t>
+          <t>`skalnivå` (sv)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -2470,7 +2470,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>KG3011</t>
+          <t>KG3014</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2480,24 +2480,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`skalnivå` (sv)</t>
+          <t>`eaxaminer` (en)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>KG3014</t>
+          <t>KG3015</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2517,14 +2517,14 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>KG3015</t>
+          <t>KG3016</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2534,29 +2534,29 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`eaxaminer` (en)</t>
+          <t>`gällade` (sv)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>KG3016</t>
+          <t>GLP236</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`gällade` (sv)</t>
+          <t>`framträdandeform` (sv)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GLP236</t>
+          <t>GLP29R</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2593,19 +2593,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`framträdandeform` (sv)</t>
+          <t>`flerspårsmaterial` (sv)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29R</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GLP29R</t>
+          <t>GLP2JZ</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2625,14 +2625,14 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2JZ</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GLP2JZ</t>
+          <t>GLP359</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2642,24 +2642,24 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`flerspårsmaterial` (sv)</t>
+          <t>`djing` (en)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2JZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GLP359</t>
+          <t>GLP3AH</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2674,19 +2674,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`djing` (en)</t>
+          <t>`excercises` (en)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GLP3AH</t>
+          <t>LP1032</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2696,17 +2696,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`excercises` (en)</t>
+          <t>`fördjupningskod` (sv)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
         </is>
       </c>
     </row>
@@ -2723,12 +2723,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`fördjupningskod` (sv)</t>
+          <t>`scholary` (en)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`scholary` (en)</t>
+          <t>`sumarise` (en)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -2767,7 +2767,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>LP1032</t>
+          <t>LP1071</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2777,17 +2777,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`sumarise` (en)</t>
+          <t>`erätter` (sv)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
         </is>
       </c>
     </row>
@@ -2804,12 +2804,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`erätter` (sv)</t>
+          <t>`evaulates` (en)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -2821,7 +2821,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>LP1071</t>
+          <t>LP2012</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2836,19 +2836,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`evaulates` (en)</t>
+          <t>`intiate` (en)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>LP2012</t>
+          <t>LP2013</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`intiate` (en)</t>
+          <t>`learnings` (en)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`learnings` (en)</t>
+          <t>`litterature` (en)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -2902,39 +2902,39 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>LP2013</t>
+          <t>GMN3EA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>MPR</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`litterature` (en)</t>
+          <t>`användar` (sv)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EA</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GMN3EA</t>
+          <t>NA1024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`användar` (sv)</t>
+          <t>`efterfråge` (sv)</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
         </is>
       </c>
     </row>
@@ -2966,12 +2966,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`efterfråge` (sv)</t>
+          <t>`distancelectures` (en)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>NA1024</t>
+          <t>NA1026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2993,24 +2993,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`distancelectures` (en)</t>
+          <t>`studieförb` (sv)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>NA1026</t>
+          <t>NA1027</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3025,19 +3025,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`studieförb` (sv)</t>
+          <t>`förläsningar` (sv)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>NA1027</t>
+          <t>NA1028</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3052,19 +3052,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>`förläsningar` (sv)</t>
+          <t>`efterfråge` (sv)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1028</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>NA1028</t>
+          <t>NA1029</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3074,24 +3074,24 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>`efterfråge` (sv)</t>
+          <t>`differentiat` (en)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>NA1029</t>
+          <t>NA1030</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3106,19 +3106,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>`differentiat` (en)</t>
+          <t>`excercises` (en)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>NA1030</t>
+          <t>NA1032</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3133,19 +3133,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>`excercises` (en)</t>
+          <t>`descirbe` (en)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>NA1032</t>
+          <t>NA1035</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3155,24 +3155,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>`descirbe` (en)</t>
+          <t>`efterfråge` (sv)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1035</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>NA1035</t>
+          <t>NA1036</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3182,17 +3182,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>`efterfråge` (sv)</t>
+          <t>`longterm` (en)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>`longterm` (en)</t>
+          <t>`shortterm` (en)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>NA1036</t>
+          <t>NA1039</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3241,19 +3241,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>`shortterm` (en)</t>
+          <t>`assingments` (en)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>NA1039</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3263,17 +3263,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>`assingments` (en)</t>
+          <t>`kalandermånader` (sv)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
@@ -3290,12 +3290,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>`kalandermånader` (sv)</t>
+          <t>`calender` (en)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>`calender` (en)</t>
+          <t>`oppobet` (en)</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>`oppobet` (en)</t>
+          <t>`opposnent` (en)</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>NA2009</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3376,19 +3376,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>`opposnent` (en)</t>
+          <t>`resultas` (en)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>NA2009</t>
+          <t>NA3001</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3398,24 +3398,24 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>`resultas` (en)</t>
+          <t>`länderjämförelser` (sv)</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>NA3001</t>
+          <t>NA3010</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3430,19 +3430,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>`länderjämförelser` (sv)</t>
+          <t>`kalandermånader` (sv)</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>NA3010</t>
+          <t>NA3011</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3452,51 +3452,51 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>`kalandermånader` (sv)</t>
+          <t>`tobbit` (en)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>NA3011</t>
+          <t>GPE3AJ</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>`tobbit` (en)</t>
+          <t>`kollegialtlärande` (sv)</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GPE3AJ</t>
+          <t>PE1020</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>`kollegialtlärande` (sv)</t>
+          <t>`gryndsyn` (en)</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>PE1020</t>
+          <t>PE1023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3533,17 +3533,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>`gryndsyn` (en)</t>
+          <t>`lärarlagsarbete` (sv)</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>`lärarlagsarbete` (sv)</t>
+          <t>`rättsäkerhet` (sv)</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -3577,7 +3577,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>PE1023</t>
+          <t>PE1054</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3592,19 +3592,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>`rättsäkerhet` (sv)</t>
+          <t>`lärstrategier` (sv)</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>PE1054</t>
+          <t>PE1064</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3619,19 +3619,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>`lärstrategier` (sv)</t>
+          <t>`rättsäkerhetsproblematiken` (sv)</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1064</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>PE1064</t>
+          <t>PE1067</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3641,24 +3641,24 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>`rättsäkerhetsproblematiken` (sv)</t>
+          <t>`att` — ….m. 2014-01-24.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>PE1067</t>
+          <t>PE1068</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3668,24 +3668,24 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>`att` — ….m. 2014-01-24.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
+          <t>`känndom` (sv)</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>PE1068</t>
+          <t>PE2005</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3695,24 +3695,24 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>`känndom` (sv)</t>
+          <t>`gryndsyn` (en)</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>PE2005</t>
+          <t>PE3004</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3722,17 +3722,17 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>`gryndsyn` (en)</t>
+          <t>`lärarlagsarbete` (sv)</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>`lärarlagsarbete` (sv)</t>
+          <t>`rättsäkerhet` (sv)</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -3766,34 +3766,34 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>PE3004</t>
+          <t>GPA2FW</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>`rättsäkerhet` (sv)</t>
+          <t>`managemet` (en)</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GPA2FW</t>
+          <t>GPA2R6</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3803,29 +3803,29 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>`managemet` (en)</t>
+          <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GPA2R6</t>
+          <t>APG24E</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>`tillvägagångsätt` (sv)</t>
+          <t>`inlämingsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
       </c>
     </row>
@@ -3857,12 +3857,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>`inlämingsuppgifter` (sv)</t>
+          <t>`credtis` (en)</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>APG24E</t>
+          <t>APG25N</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3884,24 +3884,24 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>`credtis` (en)</t>
+          <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>APG25N</t>
+          <t>APG276</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3911,24 +3911,24 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>`tillvägagångsätt` (sv)</t>
+          <t>`credtis` (en)</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>APG276</t>
+          <t>APG2AA</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3938,24 +3938,24 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>`credtis` (en)</t>
+          <t>`lärarskicklighetetens` (sv)</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>APG2AA</t>
+          <t>APG2AC</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>`lärarskicklighetetens` (sv)</t>
+          <t>`aanalyze` (en)</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>`aanalyze` (en)</t>
+          <t>`nalyze` (en)</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -4009,7 +4009,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>APG2AC</t>
+          <t>APG2CD</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4019,24 +4019,24 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>`nalyze` (en)</t>
+          <t>`lärarprofessionsspecifika` (sv)</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>APG2CD</t>
+          <t>APG2CM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4051,19 +4051,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>`lärarprofessionsspecifika` (sv)</t>
+          <t>`undervisningensmål` (sv)</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>APG2CM</t>
+          <t>GPG22K</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4073,24 +4073,24 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>`undervisningensmål` (sv)</t>
+          <t>`conciderations` (en)</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GPG22K</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4100,17 +4100,17 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>`conciderations` (en)</t>
+          <t>`samhällorienterande` (sv)</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
@@ -4127,12 +4127,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>`samhällorienterande` (sv)</t>
+          <t>`sociaty` (en)</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>`sociaty` (en)</t>
+          <t>`understandingn` (en)</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -4171,7 +4171,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GPG328</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4181,24 +4181,24 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>`understandingn` (en)</t>
+          <t>`andraämne` (sv)</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GPG328</t>
+          <t>GPG329</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4218,14 +4218,14 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GPG329</t>
+          <t>GPG3AD</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4235,24 +4235,24 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>`andraämne` (sv)</t>
+          <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GPG3AD</t>
+          <t>GPG3CG</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4262,24 +4262,24 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
+          <t>`perspecitves` (en)</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GPG3CG</t>
+          <t>GPG3CK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4289,24 +4289,24 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>`perspecitves` (en)</t>
+          <t>`inlämninguppgift` (sv)</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GPG3CK</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>`inlämninguppgift` (sv)</t>
+          <t>`samhällorienterande` (sv)</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4343,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>`samhällorienterande` (sv)</t>
+          <t>`sociaty` (en)</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -4360,12 +4360,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>ARK27Q</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4375,19 +4375,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>`sociaty` (en)</t>
+          <t>`tha` (en)</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>ARK29K</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4402,19 +4402,19 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>`tha` (en)</t>
+          <t>`cpecialisation` (en)</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29K</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>ARK29K</t>
+          <t>ARK29L</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4424,24 +4424,24 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>`cpecialisation` (en)</t>
+          <t>`markonivå` (sv)</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29L</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>ARK29L</t>
+          <t>GRK366</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>`markonivå` (sv)</t>
+          <t>`enivronments` (en)</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK366</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GRK366</t>
+          <t>GRK3B4</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4478,29 +4478,29 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>`enivronments` (en)</t>
+          <t>`ämesteoretiska` (sv)</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK366</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GRK3B4</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4510,19 +4510,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>`ämesteoretiska` (sv)</t>
+          <t>`mervärdskatt` (sv)</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>GRV2MK</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4537,19 +4537,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>`mervärdskatt` (sv)</t>
+          <t>`innhåller` (sv)</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>GRV2MK</t>
+          <t>RV1001</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4564,19 +4564,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>`innhåller` (sv)</t>
+          <t>`glavå` (sv)</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>RV1001</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4591,19 +4591,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>`glavå` (sv)</t>
+          <t>`mervärdskatt` (sv)</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>`mervärdskatt` (sv)</t>
+          <t>`glavå` (sv)</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
@@ -4640,12 +4640,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>`glavå` (sv)</t>
+          <t>`bargening` (en)</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -4657,7 +4657,7 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4667,17 +4667,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>`bargening` (en)</t>
+          <t>`obestånds` (sv)</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
@@ -4694,12 +4694,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>`obestånds` (sv)</t>
+          <t>`pratices` (en)</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>`pratices` (en)</t>
+          <t>`securites` (en)</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -4738,7 +4738,7 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4748,17 +4748,17 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>`securites` (en)</t>
+          <t>`förvaltningsrättliga` (sv)</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4780,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>`förvaltningsrättliga` (sv)</t>
+          <t>`rättsäkerheten` (sv)</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -4792,7 +4792,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>RV1045</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4807,19 +4807,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>`rättsäkerheten` (sv)</t>
+          <t>`åtgärdscheman` (sv)</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>RV1045</t>
+          <t>RV1055</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4829,51 +4829,51 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>`åtgärdscheman` (sv)</t>
+          <t>`samt` — …aminationsformer  En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,…</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>RV1055</t>
+          <t>ASK22L</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>`samt` — …aminationsformer  En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,…</t>
+          <t>`formes` (en)</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>ASK22L</t>
+          <t>ASK22M</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4888,19 +4888,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>`formes` (en)</t>
+          <t>`reviewscrutiny` (en)</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>ASK22M</t>
+          <t>ASK289</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4915,46 +4915,46 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>`reviewscrutiny` (en)</t>
+          <t>`compative` (en)</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>ASK289</t>
+          <t>GSO2PL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>`compative` (en)</t>
+          <t>`credits` — …7.5 credits, Psychological Perspectives on Social Work 7.5 credits credits and Welfare Measures and User Perspective 15 credits…</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GSO2PL</t>
+          <t>SO1027</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4964,51 +4964,51 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>`credits` — …7.5 credits, Psychological Perspectives on Social Work 7.5 credits credits and Welfare Measures and User Perspective 15 credits…</t>
+          <t>`abilty` (en)</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>SO1027</t>
+          <t>ATR26B</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>`abilty` (en)</t>
+          <t>`hållbarbetsmål` (sv)</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>ATR26B</t>
+          <t>ATR2BJ</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5018,24 +5018,24 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>`hållbarbetsmål` (sv)</t>
+          <t>`leaisure` (en)</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>ATR2BJ</t>
+          <t>GTR22D</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5045,17 +5045,17 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>`leaisure` (en)</t>
+          <t>`samhållsvetenskap` (sv)</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>`samhållsvetenskap` (sv)</t>
+          <t>`värderigsförmåga` (sv)</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>GTR22D</t>
+          <t>GTR265</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>`värderigsförmåga` (sv)</t>
+          <t>`fömåga` (sv)</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
         </is>
       </c>
     </row>
@@ -5126,12 +5126,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>`fömåga` (sv)</t>
+          <t>`afte` (en)</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -5143,7 +5143,7 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GTR265</t>
+          <t>GTR26E</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5153,24 +5153,24 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>`afte` (en)</t>
+          <t>`erätter` (sv)</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GTR26E</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>`erätter` (sv)</t>
+          <t>`förhållningssät` (sv)</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
@@ -5207,12 +5207,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>`förhållningssät` (sv)</t>
+          <t>`assignement` (en)</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>`assignement` (en)</t>
+          <t>`implmented` (en)</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>GTR2DG</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5261,17 +5261,17 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>`implmented` (en)</t>
+          <t>`the` — …earch. The course is organised into two parts. In part one, the The course introduces students to quantitative research. The co…</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
         </is>
       </c>
     </row>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>`the` — …earch. The course is organised into two parts. In part one, the The course introduces students to quantitative research. The co…</t>
+          <t>`enkätsstudie` (sv)</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -5305,7 +5305,7 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>GTR2DP</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5320,19 +5320,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>`enkätsstudie` (sv)</t>
+          <t>`värderingsfömåga` (sv)</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GTR2DP</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5342,24 +5342,24 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>`värderingsfömåga` (sv)</t>
+          <t>`recourses` (en)</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5369,17 +5369,17 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>`recourses` (en)</t>
+          <t>`använding` (sv)</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>`använding` (sv)</t>
+          <t>`lerning` (en)</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>TR1013</t>
+          <t>TR1018</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5428,19 +5428,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>`lerning` (en)</t>
+          <t>`geodemographic` (en)</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>TR1018</t>
+          <t>TR1024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5450,17 +5450,17 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>`geodemographic` (en)</t>
+          <t>`fömåga` (sv)</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
         </is>
       </c>
     </row>
@@ -5477,12 +5477,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>`fömåga` (sv)</t>
+          <t>`afte` (en)</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -5494,7 +5494,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>TR1024</t>
+          <t>TR1027</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5504,17 +5504,17 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>`afte` (en)</t>
+          <t>`fömåga` (sv)</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
         </is>
       </c>
     </row>
@@ -5531,12 +5531,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>`fömåga` (sv)</t>
+          <t>`afte` (en)</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>TR1027</t>
+          <t>TR1028</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5558,17 +5558,17 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>`afte` (en)</t>
+          <t>`förhållningssät` (sv)</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
         </is>
       </c>
     </row>
@@ -5585,12 +5585,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>`förhållningssät` (sv)</t>
+          <t>`ansd` (en)</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -5602,7 +5602,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>TR1028</t>
+          <t>TR1030</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5612,24 +5612,24 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>`ansd` (en)</t>
+          <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>TR1030</t>
+          <t>TR1031</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5644,19 +5644,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>`tillvägagångsätt` (sv)</t>
+          <t>`kulturellafördomar` (sv)</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>TR1031</t>
+          <t>TR1034</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>`kulturellafördomar` (sv)</t>
+          <t>`förvärvda` (sv)</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
       </c>
     </row>
@@ -5693,12 +5693,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>`förvärvda` (sv)</t>
+          <t>`organisaton` (en)</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>TR1034</t>
+          <t>TR2004</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5725,19 +5725,19 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>`organisaton` (en)</t>
+          <t>`stuides` (en)</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>TR2004</t>
+          <t>TR3006</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5747,17 +5747,17 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>`stuides` (en)</t>
+          <t>`the` — …- Independently identify and analyze scientific problems in the the relevant field of knowledge and conduct and report on a pro…</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
@@ -5774,12 +5774,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>`the` — …- Independently identify and analyze scientific problems in the the relevant field of knowledge and conduct and report on a pro…</t>
+          <t>`ocskå` (sv)</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -5791,34 +5791,34 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>TR3006</t>
+          <t>AS2002</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>`ocskå` (sv)</t>
+          <t>`takenup` (en)</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>AS2002</t>
+          <t>AS3002</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5833,19 +5833,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>`takenup` (en)</t>
+          <t>`teh` (en)</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>AS3002</t>
+          <t>AS3009</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5855,24 +5855,24 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>`teh` (en)</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>AS3009</t>
+          <t>AS3012</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5882,24 +5882,24 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>`literära` (sv)</t>
+          <t>`outlineof` (en)</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>AS3012</t>
+          <t>AS4003</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5909,49 +5909,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>`outlineof` (en)</t>
+          <t>`angrepssätt` (sv)</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>AS4003</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>`angrepssätt` (sv)</t>
-        </is>
-      </c>
-      <c r="E204" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E204"/>
+  <autoFilter ref="A1:E203"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -6357,8 +6330,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$186</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E203"/>
+  <dimension ref="A1:E186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -892,7 +892,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`användar` (sv)</t>
+          <t>`beställningsfilmsproduktion` (sv)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -904,7 +904,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GBQ2U6</t>
+          <t>GBQ2UB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -919,19 +919,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`beställningsfilmsproduktion` (sv)</t>
+          <t>`berättandestruktur` (sv)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UB</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GBQ2UB</t>
+          <t>GBQ2WH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -941,24 +941,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`berättandestruktur` (sv)</t>
+          <t>`tbt` (en)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WH</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GBQ2WH</t>
+          <t>GBQ2WK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -968,24 +968,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`tbt` (en)</t>
+          <t>`berätttarelement` (sv)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WK</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GBQ2WK</t>
+          <t>GBQ38W</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1000,19 +1000,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`berätttarelement` (sv)</t>
+          <t>`höguppupplöst` (sv)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GBQ38W</t>
+          <t>GBQ3AW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1022,24 +1022,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`höguppupplöst` (sv)</t>
+          <t>`explainer` (en)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GBQ3A6</t>
+          <t>GBQ3FG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1049,56 +1049,56 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`användar` (sv)</t>
+          <t>`excercises` (en)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3A6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GBQ3AW</t>
+          <t>EU1027</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`explainer` (en)</t>
+          <t>`grundäggande` (sv)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1027</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GBQ3FG</t>
+          <t>EU1033</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1108,19 +1108,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`excercises` (en)</t>
+          <t>`itssocial` (en)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1033</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>EU1027</t>
+          <t>EU1034</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`grundäggande` (sv)</t>
+          <t>`förhandlingprocesser` (sv)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1034</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>EU1033</t>
+          <t>GEU2KV</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1162,19 +1162,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`itssocial` (en)</t>
+          <t>`opportunties` (en)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1033</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>EU1034</t>
+          <t>GEU2KV</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1184,29 +1184,29 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`förhandlingprocesser` (sv)</t>
+          <t>`willll` (en)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GEU2KV</t>
+          <t>AFI273</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`opportunties` (en)</t>
+          <t>`contignency` (en)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFI273</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GEU2KV</t>
+          <t>FI1023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EUN</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`willll` (en)</t>
+          <t>`philosohical` (en)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>AFI273</t>
+          <t>FI1024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1270,19 +1270,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`contignency` (en)</t>
+          <t>`etichs` (en)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFI273</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>FI1023</t>
+          <t>FI1039</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1292,24 +1292,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`philosohical` (en)</t>
+          <t>`have` — …urthermore, on completion of the course, the student should have have the ability to :       - be reflective in relation to probl…</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>FI1024</t>
+          <t>FI1039</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1324,12 +1324,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`etichs` (en)</t>
+          <t>`asessment` (en)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`have` — …urthermore, on completion of the course, the student should have have the ability to :       - be reflective in relation to probl…</t>
+          <t>`developement` (en)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>FI1039</t>
+          <t>GFI3BT</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1378,19 +1378,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`asessment` (en)</t>
+          <t>`througout` (en)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>FI1039</t>
+          <t>GFI3BU</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`developement` (en)</t>
+          <t>`througout` (en)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GFI3BT</t>
+          <t>AHI272</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`througout` (en)</t>
+          <t>`poitical` (en)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GFI3BU</t>
+          <t>AHI29Q</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1459,19 +1459,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`througout` (en)</t>
+          <t>`consultaion` (en)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>AHI272</t>
+          <t>AHI29Q</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1486,19 +1486,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`poitical` (en)</t>
+          <t>`situatin` (en)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>AHI29Q</t>
+          <t>AS2005</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`consultaion` (en)</t>
+          <t>`takenup` (en)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2005</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>AHI29Q</t>
+          <t>AS3017</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1535,24 +1535,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`situatin` (en)</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>AS2005</t>
+          <t>AS3020</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1567,19 +1567,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`takenup` (en)</t>
+          <t>`outlineof` (en)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>AS3017</t>
+          <t>AS3022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1589,24 +1589,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`literära` (sv)</t>
+          <t>`teh` (en)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>AS3020</t>
+          <t>GHI29Y</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`outlineof` (en)</t>
+          <t>`innhållet` (sv)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>AS3022</t>
+          <t>GHI33T</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`teh` (en)</t>
+          <t>`problemförmuleringsförmåga` (sv)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GHI29Y</t>
+          <t>GHI33V</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`innhållet` (sv)</t>
+          <t>`delkurseninnehåller` (sv)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GHI33T</t>
+          <t>GHI33V</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1702,19 +1702,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`problemförmuleringsförmåga` (sv)</t>
+          <t>`godkäng` (sv)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GHI33V</t>
+          <t>GHI35A</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`delkurseninnehåller` (sv)</t>
+          <t>`analyseratmänniskors` (sv)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GHI33V</t>
+          <t>GHI35A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`godkäng` (sv)</t>
+          <t>`medförintelsen` (sv)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`analyseratmänniskors` (sv)</t>
+          <t>`människorsagerande` (sv)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GHI35A</t>
+          <t>GHI362</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1810,19 +1810,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`medförintelsen` (sv)</t>
+          <t>`självstänigt` (sv)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GHI35A</t>
+          <t>HI1008</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1832,24 +1832,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`människorsagerande` (sv)</t>
+          <t>`criterions` (en)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GHI362</t>
+          <t>HI2011</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`självstänigt` (sv)</t>
+          <t>`historiedidaktikområdet` (sv)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>HI1008</t>
+          <t>HI2012</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1886,24 +1886,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`criterions` (en)</t>
+          <t>`sjävvalt` (sv)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>HI2011</t>
+          <t>HI2016</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1918,19 +1918,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`historiedidaktikområdet` (sv)</t>
+          <t>`sjävvalt` (sv)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>HI2012</t>
+          <t>HI3019</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1945,66 +1945,66 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`sjävvalt` (sv)</t>
+          <t>`självständg` (sv)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3019</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>HI2016</t>
+          <t>AKG27R</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`sjävvalt` (sv)</t>
+          <t>`compulsotry` (en)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>HI3019</t>
+          <t>AKG27R</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`självständg` (sv)</t>
+          <t>`curent` (en)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`compulsotry` (en)</t>
+          <t>`theoretica` (en)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2038,7 +2038,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>AKG27R</t>
+          <t>GKG3AT</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2048,24 +2048,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`curent` (en)</t>
+          <t>`tilllämpas` (sv)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>AKG27R</t>
+          <t>GKG3AT</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2080,19 +2080,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`theoretica` (en)</t>
+          <t>`writtten` (en)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GKG3AT</t>
+          <t>KG1024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2107,19 +2107,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`tilllämpas` (sv)</t>
+          <t>`beräklningstung` (sv)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GKG3AT</t>
+          <t>KG1024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`writtten` (en)</t>
+          <t>`quantitativ` (en)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>KG1024</t>
+          <t>KG1025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2156,24 +2156,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`beräklningstung` (sv)</t>
+          <t>`evolvement` (en)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>KG1024</t>
+          <t>KG1025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2188,19 +2188,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`quantitativ` (en)</t>
+          <t>`thise` (en)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>KG1025</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2215,19 +2215,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`evolvement` (en)</t>
+          <t>`obser` (en)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>KG1025</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`thise` (en)</t>
+          <t>`perspetives` (en)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`obser` (en)</t>
+          <t>`standarized` (en)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`perspetives` (en)</t>
+          <t>`vations` (en)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>KG2005</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2323,19 +2323,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`standarized` (en)</t>
+          <t>`qualititative` (en)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>KG2001</t>
+          <t>KG3010</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`vations` (en)</t>
+          <t>`recognises` (en)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>KG2005</t>
+          <t>KG3011</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2372,24 +2372,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`qualititative` (en)</t>
+          <t>`kartöverlägg` (sv)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>KG3010</t>
+          <t>KG3014</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`recognises` (en)</t>
+          <t>`eaxaminer` (en)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>KG3011</t>
+          <t>KG3015</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2426,24 +2426,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`kartöverlägg` (sv)</t>
+          <t>`eaxaminer` (en)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>KG3011</t>
+          <t>KG3016</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2458,51 +2458,51 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`skalnivå` (sv)</t>
+          <t>`gällade` (sv)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>KG3014</t>
+          <t>GLP236</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`eaxaminer` (en)</t>
+          <t>`framträdandeform` (sv)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>KG3015</t>
+          <t>GLP359</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2512,46 +2512,46 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`eaxaminer` (en)</t>
+          <t>`djing` (en)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>KG3016</t>
+          <t>GLP3AH</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>KGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`gällade` (sv)</t>
+          <t>`excercises` (en)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GLP236</t>
+          <t>LP1032</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`framträdandeform` (sv)</t>
+          <t>`scholary` (en)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GLP29R</t>
+          <t>LP1032</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2588,24 +2588,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`flerspårsmaterial` (sv)</t>
+          <t>`sumarise` (en)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP29R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GLP2JZ</t>
+          <t>LP1071</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2620,19 +2620,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`flerspårsmaterial` (sv)</t>
+          <t>`erätter` (sv)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2JZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GLP359</t>
+          <t>LP1071</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2647,19 +2647,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`djing` (en)</t>
+          <t>`evaulates` (en)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GLP3AH</t>
+          <t>LP2012</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2674,19 +2674,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`excercises` (en)</t>
+          <t>`intiate` (en)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>LP1032</t>
+          <t>LP2013</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2696,24 +2696,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`fördjupningskod` (sv)</t>
+          <t>`learnings` (en)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>LP1032</t>
+          <t>LP2013</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`scholary` (en)</t>
+          <t>`litterature` (en)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>LP1032</t>
+          <t>NA1024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2755,24 +2755,24 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`sumarise` (en)</t>
+          <t>`distancelectures` (en)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>LP1071</t>
+          <t>NA1027</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2782,24 +2782,24 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`erätter` (sv)</t>
+          <t>`förläsningar` (sv)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>LP1071</t>
+          <t>NA1029</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2809,24 +2809,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`evaulates` (en)</t>
+          <t>`differentiat` (en)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>LP2012</t>
+          <t>NA1030</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2836,24 +2836,24 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`intiate` (en)</t>
+          <t>`excercises` (en)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>LP2013</t>
+          <t>NA1032</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2863,24 +2863,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`learnings` (en)</t>
+          <t>`descirbe` (en)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>LP2013</t>
+          <t>NA1036</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LPU</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2890,46 +2890,46 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`litterature` (en)</t>
+          <t>`longterm` (en)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GMN3EA</t>
+          <t>NA1036</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MPR</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`användar` (sv)</t>
+          <t>`shortterm` (en)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3EA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>NA1024</t>
+          <t>NA1039</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2939,24 +2939,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`efterfråge` (sv)</t>
+          <t>`assingments` (en)</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>NA1024</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2966,24 +2966,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`distancelectures` (en)</t>
+          <t>`kalandermånader` (sv)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>NA1026</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2993,24 +2993,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`studieförb` (sv)</t>
+          <t>`calender` (en)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>NA1027</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3020,24 +3020,24 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`förläsningar` (sv)</t>
+          <t>`oppobet` (en)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>NA1028</t>
+          <t>NA2008</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3047,24 +3047,24 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>`efterfråge` (sv)</t>
+          <t>`opposnent` (en)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>NA1029</t>
+          <t>NA2009</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>`differentiat` (en)</t>
+          <t>`resultas` (en)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>NA1030</t>
+          <t>NA3001</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3101,24 +3101,24 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>`excercises` (en)</t>
+          <t>`länderjämförelser` (sv)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>NA1032</t>
+          <t>NA3010</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3128,24 +3128,24 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>`descirbe` (en)</t>
+          <t>`kalandermånader` (sv)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>NA1035</t>
+          <t>NA3011</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3155,56 +3155,56 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>`efterfråge` (sv)</t>
+          <t>`tobbit` (en)</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>NA1036</t>
+          <t>GPE3AJ</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>`longterm` (en)</t>
+          <t>`kollegialtlärande` (sv)</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>NA1036</t>
+          <t>PE1020</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3214,105 +3214,105 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>`shortterm` (en)</t>
+          <t>`gryndsyn` (en)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>NA1039</t>
+          <t>PE1023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>`assingments` (en)</t>
+          <t>`rättsäkerhet` (sv)</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>PE1067</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>`kalandermånader` (sv)</t>
+          <t>`att` — ….m. 2014-01-24.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>PE1068</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>`calender` (en)</t>
+          <t>`känndom` (sv)</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>PE2005</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3322,51 +3322,51 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>`oppobet` (en)</t>
+          <t>`gryndsyn` (en)</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>NA2008</t>
+          <t>PE3004</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>`opposnent` (en)</t>
+          <t>`rättsäkerhet` (sv)</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>NA2009</t>
+          <t>GPA2FW</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>`resultas` (en)</t>
+          <t>`managemet` (en)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>NA3001</t>
+          <t>GPA2R6</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>`länderjämförelser` (sv)</t>
+          <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>NA3010</t>
+          <t>APG24E</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>`kalandermånader` (sv)</t>
+          <t>`inlämingsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>NA3011</t>
+          <t>APG24E</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>`tobbit` (en)</t>
+          <t>`credtis` (en)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GPE3AJ</t>
+          <t>APG25N</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>`kollegialtlärande` (sv)</t>
+          <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>PE1020</t>
+          <t>APG276</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3511,24 +3511,24 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>`gryndsyn` (en)</t>
+          <t>`credtis` (en)</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>PE1023</t>
+          <t>APG2AA</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3538,78 +3538,78 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>`lärarlagsarbete` (sv)</t>
+          <t>`lärarskicklighetetens` (sv)</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>PE1023</t>
+          <t>APG2AC</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>`rättsäkerhet` (sv)</t>
+          <t>`aanalyze` (en)</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>PE1054</t>
+          <t>APG2AC</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>`lärstrategier` (sv)</t>
+          <t>`nalyze` (en)</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>PE1064</t>
+          <t>APG2CM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3619,51 +3619,51 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>`rättsäkerhetsproblematiken` (sv)</t>
+          <t>`undervisningensmål` (sv)</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>PE1067</t>
+          <t>GPG22K</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>`att` — ….m. 2014-01-24.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
+          <t>`conciderations` (en)</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>PE1068</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3673,24 +3673,24 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>`känndom` (sv)</t>
+          <t>`samhällorienterande` (sv)</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>PE2005</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3700,51 +3700,51 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>`gryndsyn` (en)</t>
+          <t>`sociaty` (en)</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>PE3004</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>`lärarlagsarbete` (sv)</t>
+          <t>`understandingn` (en)</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>PE3004</t>
+          <t>GPG328</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3754,73 +3754,73 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>`rättsäkerhet` (sv)</t>
+          <t>`andraämne` (sv)</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GPA2FW</t>
+          <t>GPG329</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>`managemet` (en)</t>
+          <t>`andraämne` (sv)</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GPA2R6</t>
+          <t>GPG3AD</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>`tillvägagångsätt` (sv)</t>
+          <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>APG24E</t>
+          <t>GPG3CG</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3830,24 +3830,24 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>`inlämingsuppgifter` (sv)</t>
+          <t>`perspecitves` (en)</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>APG24E</t>
+          <t>GPG3CK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3857,24 +3857,24 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>`credtis` (en)</t>
+          <t>`inlämninguppgift` (sv)</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>APG25N</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3889,19 +3889,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>`tillvägagångsätt` (sv)</t>
+          <t>`samhällorienterande` (sv)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>APG276</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3916,51 +3916,51 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>`credtis` (en)</t>
+          <t>`sociaty` (en)</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>APG2AA</t>
+          <t>ARK27Q</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>`lärarskicklighetetens` (sv)</t>
+          <t>`tha` (en)</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>APG2AC</t>
+          <t>ARK29K</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3970,78 +3970,78 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>`aanalyze` (en)</t>
+          <t>`cpecialisation` (en)</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29K</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>APG2AC</t>
+          <t>ARK29L</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>`nalyze` (en)</t>
+          <t>`markonivå` (sv)</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29L</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>APG2CD</t>
+          <t>GRK366</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>`lärarprofessionsspecifika` (sv)</t>
+          <t>`enivronments` (en)</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK366</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>APG2CM</t>
+          <t>GRK3B4</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4051,51 +4051,51 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>`undervisningensmål` (sv)</t>
+          <t>`ämesteoretiska` (sv)</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GPG22K</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>`conciderations` (en)</t>
+          <t>`mervärdskatt` (sv)</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GRV2MK</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4105,78 +4105,78 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>`samhällorienterande` (sv)</t>
+          <t>`innhåller` (sv)</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>RV1001</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>`sociaty` (en)</t>
+          <t>`glavå` (sv)</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>`understandingn` (en)</t>
+          <t>`mervärdskatt` (sv)</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GPG328</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4186,78 +4186,78 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>`andraämne` (sv)</t>
+          <t>`glavå` (sv)</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GPG329</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>`andraämne` (sv)</t>
+          <t>`bargening` (en)</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GPG3AD</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
+          <t>`pratices` (en)</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GPG3CG</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4267,24 +4267,24 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>`perspecitves` (en)</t>
+          <t>`securites` (en)</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GPG3CK</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4294,24 +4294,24 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>`inlämninguppgift` (sv)</t>
+          <t>`förvaltningsrättliga` (sv)</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4321,78 +4321,78 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>`samhällorienterande` (sv)</t>
+          <t>`rättsäkerheten` (sv)</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>RV1045</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>`sociaty` (en)</t>
+          <t>`åtgärdscheman` (sv)</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>RV1055</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>`tha` (en)</t>
+          <t>`samt` — …aminationsformer  En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,…</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>ARK29K</t>
+          <t>ASK22L</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4402,51 +4402,51 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>`cpecialisation` (en)</t>
+          <t>`formes` (en)</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>ARK29L</t>
+          <t>ASK22M</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>`markonivå` (sv)</t>
+          <t>`reviewscrutiny` (en)</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GRK366</t>
+          <t>ASK289</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4456,78 +4456,78 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>`enivronments` (en)</t>
+          <t>`compative` (en)</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK366</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GRK3B4</t>
+          <t>GSO2PL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>`ämesteoretiska` (sv)</t>
+          <t>`credits` — …7.5 credits, Psychological Perspectives on Social Work 7.5 credits credits and Welfare Measures and User Perspective 15 credits…</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>SO1027</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>`mervärdskatt` (sv)</t>
+          <t>`abilty` (en)</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GRV2MK</t>
+          <t>ATR26B</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4537,51 +4537,51 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>`innhåller` (sv)</t>
+          <t>`hållbarbetsmål` (sv)</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>RV1001</t>
+          <t>ATR2BJ</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>`glavå` (sv)</t>
+          <t>`leaisure` (en)</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>GTR22D</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>`mervärdskatt` (sv)</t>
+          <t>`samhållsvetenskap` (sv)</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>GTR22D</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4618,267 +4618,267 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>`glavå` (sv)</t>
+          <t>`värderigsförmåga` (sv)</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>GTR265</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>`bargening` (en)</t>
+          <t>`fömåga` (sv)</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>GTR265</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>`obestånds` (sv)</t>
+          <t>`afte` (en)</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>GTR26E</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>`pratices` (en)</t>
+          <t>`erätter` (sv)</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>`securites` (en)</t>
+          <t>`förhållningssät` (sv)</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>`förvaltningsrättliga` (sv)</t>
+          <t>`assignement` (en)</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>`rättsäkerheten` (sv)</t>
+          <t>`implmented` (en)</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>RV1045</t>
+          <t>GTR2DG</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>`åtgärdscheman` (sv)</t>
+          <t>`the` — …earch. The course is organised into two parts. In part one, the The course introduces students to quantitative research. The co…</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>RV1055</t>
+          <t>GTR2DG</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>`samt` — …aminationsformer  En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,…</t>
+          <t>`enkätsstudie` (sv)</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>ASK22L</t>
+          <t>GTR2DP</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>`formes` (en)</t>
+          <t>`värderingsfömåga` (sv)</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>ASK22M</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4888,78 +4888,78 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>`reviewscrutiny` (en)</t>
+          <t>`recourses` (en)</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>ASK289</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>`compative` (en)</t>
+          <t>`använding` (sv)</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GSO2PL</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>`credits` — …7.5 credits, Psychological Perspectives on Social Work 7.5 credits credits and Welfare Measures and User Perspective 15 credits…</t>
+          <t>`lerning` (en)</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>SO1027</t>
+          <t>TR1018</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4969,19 +4969,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>`abilty` (en)</t>
+          <t>`geodemographic` (en)</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>ATR26B</t>
+          <t>TR1024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4996,19 +4996,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>`hållbarbetsmål` (sv)</t>
+          <t>`fömåga` (sv)</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>ATR2BJ</t>
+          <t>TR1024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5023,19 +5023,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>`leaisure` (en)</t>
+          <t>`afte` (en)</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>GTR22D</t>
+          <t>TR1027</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5050,19 +5050,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>`samhållsvetenskap` (sv)</t>
+          <t>`fömåga` (sv)</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>GTR22D</t>
+          <t>TR1027</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5072,24 +5072,24 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>`värderigsförmåga` (sv)</t>
+          <t>`afte` (en)</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>GTR265</t>
+          <t>TR1028</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5104,19 +5104,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>`fömåga` (sv)</t>
+          <t>`förhållningssät` (sv)</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>GTR265</t>
+          <t>TR1028</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5131,19 +5131,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>`afte` (en)</t>
+          <t>`ansd` (en)</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GTR26E</t>
+          <t>TR1030</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5158,19 +5158,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>`erätter` (sv)</t>
+          <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>TR1031</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5185,19 +5185,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>`förhållningssät` (sv)</t>
+          <t>`kulturellafördomar` (sv)</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>TR1034</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5207,24 +5207,24 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>`assignement` (en)</t>
+          <t>`förvärvda` (sv)</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>TR1034</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5239,19 +5239,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>`implmented` (en)</t>
+          <t>`organisaton` (en)</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>TR2004</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5261,24 +5261,24 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>`the` — …earch. The course is organised into two parts. In part one, the The course introduces students to quantitative research. The co…</t>
+          <t>`stuides` (en)</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>TR3006</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5288,24 +5288,24 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>`enkätsstudie` (sv)</t>
+          <t>`the` — …- Independently identify and analyze scientific problems in the the relevant field of knowledge and conduct and report on a pro…</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>GTR2DP</t>
+          <t>TR3006</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5320,24 +5320,24 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>`värderingsfömåga` (sv)</t>
+          <t>`ocskå` (sv)</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>AS2002</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5347,78 +5347,78 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>`recourses` (en)</t>
+          <t>`takenup` (en)</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>TR1013</t>
+          <t>AS3002</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>`använding` (sv)</t>
+          <t>`teh` (en)</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>TR1013</t>
+          <t>AS3009</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>`lerning` (en)</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>TR1018</t>
+          <t>AS3012</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5428,24 +5428,24 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>`geodemographic` (en)</t>
+          <t>`outlineof` (en)</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>TR1024</t>
+          <t>AS4003</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>UVX</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5455,476 +5455,17 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>`fömåga` (sv)</t>
+          <t>`angrepssätt` (sv)</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
-        <is>
-          <t>TR1024</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>`afte` (en)</t>
-        </is>
-      </c>
-      <c r="E187" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
-        <is>
-          <t>TR1027</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>`fömåga` (sv)</t>
-        </is>
-      </c>
-      <c r="E188" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
-        <is>
-          <t>TR1027</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>`afte` (en)</t>
-        </is>
-      </c>
-      <c r="E189" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>TR1028</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>`förhållningssät` (sv)</t>
-        </is>
-      </c>
-      <c r="E190" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
-        <is>
-          <t>TR1028</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>`ansd` (en)</t>
-        </is>
-      </c>
-      <c r="E191" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>TR1030</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>`tillvägagångsätt` (sv)</t>
-        </is>
-      </c>
-      <c r="E192" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>TR1031</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>`kulturellafördomar` (sv)</t>
-        </is>
-      </c>
-      <c r="E193" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>TR1034</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>`förvärvda` (sv)</t>
-        </is>
-      </c>
-      <c r="E194" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>TR1034</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>`organisaton` (en)</t>
-        </is>
-      </c>
-      <c r="E195" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>TR2004</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>`stuides` (en)</t>
-        </is>
-      </c>
-      <c r="E196" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
-        <is>
-          <t>TR3006</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Dubblerat ord</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>`the` — …- Independently identify and analyze scientific problems in the the relevant field of knowledge and conduct and report on a pro…</t>
-        </is>
-      </c>
-      <c r="E197" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>TR3006</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>`ocskå` (sv)</t>
-        </is>
-      </c>
-      <c r="E198" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>AS2002</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>`takenup` (en)</t>
-        </is>
-      </c>
-      <c r="E199" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>AS3002</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>`teh` (en)</t>
-        </is>
-      </c>
-      <c r="E200" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>AS3009</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>`literära` (sv)</t>
-        </is>
-      </c>
-      <c r="E201" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>AS3012</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>`outlineof` (en)</t>
-        </is>
-      </c>
-      <c r="E202" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>AS4003</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>UVX</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>`angrepssätt` (sv)</t>
-        </is>
-      </c>
-      <c r="E203" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E203"/>
+  <autoFilter ref="A1:E186"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -6296,40 +5837,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId368"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId369"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$192</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,221 +472,5162 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ABQ2B4</t>
+          <t>AB1019</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`en` — …- formulera och muntligt framföra konstruktiv kritik på en en text av vetenskaplig karaktär    - vetenskapligt värdera oc…</t>
+          <t>`arbetsträtt` (sv)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1019</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>FI1039</t>
+          <t>AB1019</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`have` — …urthermore, on completion of the course, the student should have have the ability to :       - be reflective in relation to probl…</t>
+          <t>`förläsningar` (sv)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1019</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>PE1067</t>
+          <t>AB1019</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`att` — ….m. 2014-01-24.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
+          <t>`municpality` (en)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1019</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GPG3AD</t>
+          <t>AB1022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
+          <t>`därmellen` (sv)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1022</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>RV1055</t>
+          <t>AB1029</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`samt` — …aminationsformer  En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,…</t>
+          <t>`abilith` (en)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1029</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GSO2PL</t>
+          <t>AB3001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`credits` — …7.5 credits, Psychological Perspectives on Social Work 7.5 credits credits and Welfare Measures and User Perspective 15 credits…</t>
+          <t>`kommunförb` (sv)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB3001</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>ABQ2AM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`the` — …earch. The course is organised into two parts. In part one, the The course introduces students to quantitative research. The co…</t>
+          <t>`inludes` (en)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>ABQ2AM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>`managment` (en)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ABQ2B4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>`en` — …- formulera och muntligt framföra konstruktiv kritik på en en text av vetenskaplig karaktär    - vetenskapligt värdera oc…</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>BQ1079</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>`devolop` (en)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ1079</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>BQ1079</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>`strucuring` (en)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ1079</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>BQ2018</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>`lärarare` (sv)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>BQ2057</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>`postproduction` (en)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2057</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>GBQ29D</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>`undergradaute` (en)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29D</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>GBQ29E</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>`undergradaute` (en)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29E</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>GBQ2U6</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>`beställningsfilmsproduktion` (sv)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>GBQ2UB</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>`berättandestruktur` (sv)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UB</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>GBQ2WH</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>`tbt` (en)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WH</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>GBQ2WK</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>`berätttarelement` (sv)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>GBQ38W</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>`höguppupplöst` (sv)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>GBQ3AW</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>`explainer` (en)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>GBQ3FG</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>`excercises` (en)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>EU1027</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EUN</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>`grundäggande` (sv)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>EU1033</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>EUN</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>`itssocial` (en)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1033</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>EU1034</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>EUN</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>`förhandlingprocesser` (sv)</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1034</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>GEU2KV</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>EUN</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>`opportunties` (en)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>GEU2KV</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>EUN</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>`willll` (en)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>AFI273</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>`contignency` (en)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFI273</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>FI1023</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>`philosohical` (en)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>FI1024</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>`etichs` (en)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>FI1039</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>`have` — …urthermore, on completion of the course, the student should have have the ability to :       - be reflective in relation to probl…</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>FI1039</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>`asessment` (en)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>FI1039</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>`developement` (en)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>GFI3BT</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>`througout` (en)</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>GFI3BU</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>`througout` (en)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>AHI272</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>`poitical` (en)</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>AHI29Q</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>`consultaion` (en)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>AHI29Q</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>`situatin` (en)</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>AS2005</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>`takenup` (en)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>AS3017</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>`literära` (sv)</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>AS3020</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>`outlineof` (en)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>AS3022</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>`teh` (en)</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>GHI29Y</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>`innhållet` (sv)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>GHI33T</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>`problemförmuleringsförmåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>GHI33V</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>`delkurseninnehåller` (sv)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>GHI33V</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>`godkäng` (sv)</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>GHI35A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>`analyseratmänniskors` (sv)</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>GHI35A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>`medförintelsen` (sv)</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>GHI35A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>`människorsagerande` (sv)</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>GHI362</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>`självstänigt` (sv)</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>HI1008</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>`criterions` (en)</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>HI2011</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>`historiedidaktikområdet` (sv)</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>HI2012</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>`sjävvalt` (sv)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>HI2016</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>`sjävvalt` (sv)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>HI3019</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>`självständg` (sv)</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3019</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>AKG27R</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>`compulsotry` (en)</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>AKG27R</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>`curent` (en)</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>AKG27R</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>`theoretica` (en)</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>GKG3AT</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>`tilllämpas` (sv)</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>GKG3AT</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>`writtten` (en)</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>KG1024</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>`beräklningstung` (sv)</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>KG1024</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>`quantitativ` (en)</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>KG1025</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>`evolvement` (en)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>KG1025</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>`thise` (en)</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>KG2001</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>`obser` (en)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>KG2001</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>`perspetives` (en)</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>KG2001</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>`standarized` (en)</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>KG2001</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>`vations` (en)</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>KG2005</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>`qualititative` (en)</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>KG3010</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>`recognises` (en)</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>KG3011</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>`kartöverlägg` (sv)</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>KG3014</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>`eaxaminer` (en)</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>KG3015</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>`eaxaminer` (en)</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>KG3016</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>`gällade` (sv)</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>GLP236</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>`framträdandeform` (sv)</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>GLP359</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>`djing` (en)</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>GLP3AH</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>`excercises` (en)</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>LP1032</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>`scholary` (en)</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>LP1032</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>`sumarise` (en)</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>LP1071</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>`erätter` (sv)</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>LP1071</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>`evaulates` (en)</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>LP2012</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>`intiate` (en)</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>LP2013</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>`learnings` (en)</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>LP2013</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>`litterature` (en)</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>GMN3F2</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>MPR</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>`incuding` (en)</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>NA1024</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>`distancelectures` (en)</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>NA1027</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>`förläsningar` (sv)</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>NA1029</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>`differentiat` (en)</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>NA1030</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>`excercises` (en)</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>NA1032</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>`descirbe` (en)</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>NA1036</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>`longterm` (en)</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>NA1036</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>`shortterm` (en)</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>NA1039</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>`assingments` (en)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>NA2008</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>`kalandermånader` (sv)</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>NA2008</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>`calender` (en)</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>NA2008</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>`oppobet` (en)</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>NA2008</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>`opposnent` (en)</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>NA2009</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>`resultas` (en)</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>NA3001</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>`länderjämförelser` (sv)</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>NA3010</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>`kalandermånader` (sv)</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>NA3011</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>`tobbit` (en)</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>GPE3AJ</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>`kollegialtlärande` (sv)</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>PE1020</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>`gryndsyn` (en)</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>PE1023</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>`rättsäkerhet` (sv)</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>PE1067</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>`att` — ….m. 2014-01-24.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>PE1068</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>`känndom` (sv)</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>PE2005</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>`gryndsyn` (en)</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>PE3004</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>`rättsäkerhet` (sv)</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>GPA2FW</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>`managemet` (en)</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>GPA2R6</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>`tillvägagångsätt` (sv)</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>APG24E</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>`inlämingsuppgifter` (sv)</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>APG24E</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>`credtis` (en)</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>APG25N</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>`tillvägagångsätt` (sv)</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>APG276</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>`credtis` (en)</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>APG2AA</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>`lärarskicklighetetens` (sv)</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>APG2AC</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>`aanalyze` (en)</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>APG2AC</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>`nalyze` (en)</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>APG2BK</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>`addmitted` (en)</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>APG2C6</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>`credtis` (en)</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>APG2C6</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>`whithin` (en)</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>APG2CM</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>`undervisningensmål` (sv)</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>APG2CM</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>`educare` (en)</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>GPG22K</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>`conciderations` (en)</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>GPG2SC</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>`samhällorienterande` (sv)</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>GPG2SC</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>`sociaty` (en)</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>GPG2SC</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>`understandingn` (en)</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>GPG328</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>`andraämne` (sv)</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>GPG329</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>`andraämne` (sv)</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>GPG3AD</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CG</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>`perspecitves` (en)</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CK</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>`inlämninguppgift` (sv)</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CL</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>`samhällorienterande` (sv)</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CL</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>`sociaty` (en)</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>GPG3FT</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>`addmitted` (en)</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>ARK27Q</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>`tha` (en)</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>ARK29K</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>`cpecialisation` (en)</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29K</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>ARK29L</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>`markonivå` (sv)</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29L</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>GRK366</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>`enivronments` (en)</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK366</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>GRK3B4</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>`ämesteoretiska` (sv)</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>GRV266</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>`mervärdskatt` (sv)</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>GRV2MK</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>`innhåller` (sv)</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>RV1001</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>`glavå` (sv)</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>RV1003</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>`mervärdskatt` (sv)</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>RV1026</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>`glavå` (sv)</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>RV1026</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>`bargening` (en)</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>RV1038</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>`pratices` (en)</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>RV1038</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>`securites` (en)</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>RV1043</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>`förvaltningsrättliga` (sv)</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>RV1043</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>`rättsäkerheten` (sv)</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>RV1045</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>`åtgärdscheman` (sv)</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>RV1055</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>`samt` — …aminationsformer  En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,…</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>ASK22L</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>SKA</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>`formes` (en)</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>ASK22M</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>SKA</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>`reviewscrutiny` (en)</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>ASK289</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>SKA</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>`compative` (en)</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>GSO2PL</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>`credits` — …7.5 credits, Psychological Perspectives on Social Work 7.5 credits credits and Welfare Measures and User Perspective 15 credits…</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>SO1027</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>`abilty` (en)</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>ATR26B</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>`hållbarbetsmål` (sv)</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>ATR2BJ</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>`leaisure` (en)</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>GTR22D</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>`samhållsvetenskap` (sv)</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>GTR22D</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>`värderigsförmåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>GTR265</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>`fömåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>GTR265</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>`afte` (en)</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>GTR26E</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>`erätter` (sv)</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>GTR29Q</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>`förhållningssät` (sv)</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>GTR29Q</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>`assignement` (en)</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>GTR29Q</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>`implmented` (en)</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>GTR2DG</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>`the` — …earch. The course is organised into two parts. In part one, the The course introduces students to quantitative research. The co…</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>GTR2DG</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>`enkätsstudie` (sv)</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>GTR2DP</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>`värderingsfömåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>TR1007</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>`recourses` (en)</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>TR1013</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>`använding` (sv)</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>TR1013</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>`lerning` (en)</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>TR1018</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>`geodemographic` (en)</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>TR1024</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>`fömåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>TR1024</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>`afte` (en)</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>TR1027</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>`fömåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>TR1027</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>`afte` (en)</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>TR1028</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>`förhållningssät` (sv)</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>TR1028</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>`ansd` (en)</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>TR1030</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>`tillvägagångsätt` (sv)</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>TR1031</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>`kulturellafördomar` (sv)</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>TR1034</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>`förvärvda` (sv)</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>TR1034</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>`organisaton` (en)</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>TR2004</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>`stuides` (en)</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
           <t>TR3006</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B186" t="inlineStr">
         <is>
           <t>TRU</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C186" t="inlineStr">
         <is>
           <t>Dubblerat ord</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D186" t="inlineStr">
         <is>
           <t>`the` — …- Independently identify and analyze scientific problems in the the relevant field of knowledge and conduct and report on a pro…</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>TR3006</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>`ocskå` (sv)</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>AS2002</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>`takenup` (en)</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>AS3002</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>`teh` (en)</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>AS3009</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>`literära` (sv)</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>AS3012</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>`outlineof` (en)</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>AS4003</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>`angrepssätt` (sv)</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E9"/>
+  <autoFilter ref="A1:E192"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -704,6 +5645,372 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A185" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$205</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,221 +472,5513 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ABQ2B4</t>
+          <t>AB1019</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`en` — …- formulera och muntligt framföra konstruktiv kritik på en en text av vetenskaplig karaktär    - vetenskapligt värdera oc…</t>
+          <t>`arbetsträtt` (sv)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1019</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>FI1039</t>
+          <t>AB1019</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`have` — …urthermore, on completion of the course, the student should have have the ability to :       - be reflective in relation to probl…</t>
+          <t>`förläsningar` (sv)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1019</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>PE1067</t>
+          <t>AB1019</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`att` — ….m. 2014-01-24.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
+          <t>`municpality` (en)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1019</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GPG3AD</t>
+          <t>AB1022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
+          <t>`därmellen` (sv)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1022</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>RV1055</t>
+          <t>AB1029</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`samt` — …aminationsformer  En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,…</t>
+          <t>`abilith` (en)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1029</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GSO2PL</t>
+          <t>AB3001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`credits` — …7.5 credits, Psychological Perspectives on Social Work 7.5 credits credits and Welfare Measures and User Perspective 15 credits…</t>
+          <t>`kommunförb` (sv)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB3001</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>ABQ2AM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`the` — …earch. The course is organised into two parts. In part one, the The course introduces students to quantitative research. The co…</t>
+          <t>`inludes` (en)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>ABQ2AM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>`managment` (en)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ABQ2B4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>`en` — …- formulera och muntligt framföra konstruktiv kritik på en en text av vetenskaplig karaktär    - vetenskapligt värdera oc…</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>BQ1079</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>`devolop` (en)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ1079</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>BQ1079</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>`strucuring` (en)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ1079</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>BQ2018</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>`lärarare` (sv)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>BQ2057</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>`postproduction` (en)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2057</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>GBQ29D</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>`undergradaute` (en)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29D</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>GBQ29E</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>`undergradaute` (en)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29E</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>GBQ2U6</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>`beställningsfilmsproduktion` (sv)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>GBQ2UB</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>`berättandestruktur` (sv)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UB</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>GBQ2WH</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>`tbt` (en)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WH</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>GBQ2WK</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>`berätttarelement` (sv)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>GBQ38W</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>`höguppupplöst` (sv)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>GBQ3AW</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>`explainer` (en)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>GBQ3FG</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>`excercises` (en)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>EU1027</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EUN</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>`grundäggande` (sv)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>EU1033</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>EUN</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>`itssocial` (en)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1033</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>EU1034</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>EUN</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>`förhandlingprocesser` (sv)</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1034</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>GEU2KV</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>EUN</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>`opportunties` (en)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>GEU2KV</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>EUN</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>`willll` (en)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>AFI273</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>`contignency` (en)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFI273</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>FI1023</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>`philosohical` (en)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>FI1024</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>`etichs` (en)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>FI1039</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>`have` — …urthermore, on completion of the course, the student should have have the ability to :       - be reflective in relation to probl…</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>FI1039</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>`asessment` (en)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>FI1039</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>`developement` (en)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>GFI3BT</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>`througout` (en)</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>GFI3BU</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>`througout` (en)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>AHI272</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>`poitical` (en)</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>AHI29Q</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>`consultaion` (en)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>AHI29Q</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>`situatin` (en)</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>AS2005</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>`takenup` (en)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>AS3017</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>`literära` (sv)</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>AS3020</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>`outlineof` (en)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>AS3022</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>`teh` (en)</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>GHI29Y</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>`innhållet` (sv)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>GHI33T</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>`problemförmuleringsförmåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>GHI33V</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>`delkurseninnehåller` (sv)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>GHI33V</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>`godkäng` (sv)</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>GHI35A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>`analyseratmänniskors` (sv)</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>GHI35A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>`medförintelsen` (sv)</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>GHI35A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>`människorsagerande` (sv)</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>GHI362</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>`självstänigt` (sv)</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>HI1008</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>`criterions` (en)</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>HI2011</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>`historiedidaktikområdet` (sv)</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>HI2012</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>`sjävvalt` (sv)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>HI2016</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>`sjävvalt` (sv)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>HI3019</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>`självständg` (sv)</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3019</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>AKG27R</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>`compulsotry` (en)</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>AKG27R</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>`curent` (en)</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>AKG27R</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>`theoretica` (en)</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>GKG3AT</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>`tilllämpas` (sv)</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>GKG3AT</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>`writtten` (en)</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>KG1024</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>`beräklningstung` (sv)</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>KG1024</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>`quantitativ` (en)</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>KG1025</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>`evolvement` (en)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>KG1025</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>`thise` (en)</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>KG2001</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>`obser` (en)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>KG2001</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>`perspetives` (en)</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>KG2001</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>`standarized` (en)</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>KG2001</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>`vations` (en)</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>KG2005</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>`qualititative` (en)</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>KG3010</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>`recognises` (en)</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>KG3011</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>`kartöverlägg` (sv)</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>KG3014</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>`eaxaminer` (en)</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>KG3015</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>`eaxaminer` (en)</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>KG3016</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>`gällade` (sv)</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>GLP236</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>`framträdandeform` (sv)</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>GLP359</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>`djing` (en)</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>GLP3AH</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>`excercises` (en)</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>LP1032</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>`scholary` (en)</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>LP1032</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>`sumarise` (en)</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>LP1071</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>`erätter` (sv)</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>LP1071</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>`evaulates` (en)</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>LP2012</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>`intiate` (en)</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>LP2013</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>`learnings` (en)</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>LP2013</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>`litterature` (en)</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>GMN3F2</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>MPR</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>`incuding` (en)</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>NA1024</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>`distancelectures` (en)</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>NA1027</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>`förläsningar` (sv)</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>NA1029</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>`differentiat` (en)</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>NA1030</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>`excercises` (en)</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>NA1032</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>`descirbe` (en)</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>NA1036</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>`longterm` (en)</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>NA1036</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>`shortterm` (en)</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>NA1039</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>`assingments` (en)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>NA2008</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>`kalandermånader` (sv)</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>NA2008</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>`calender` (en)</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>NA2008</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>`oppobet` (en)</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>NA2008</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>`opposnent` (en)</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>NA2009</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>`resultas` (en)</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>NA3001</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>`länderjämförelser` (sv)</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>NA3010</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>`kalandermånader` (sv)</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>NA3011</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>`tobbit` (en)</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>GPE3AJ</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>`kollegialtlärande` (sv)</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>PE1020</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>`gryndsyn` (en)</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>PE1023</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>`rättsäkerhet` (sv)</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>PE1067</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>`att` — ….m. 2014-01-24.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>PE1068</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>`känndom` (sv)</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>PE2005</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>`gryndsyn` (en)</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>PE3004</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>`rättsäkerhet` (sv)</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>GPA2FW</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>`managemet` (en)</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>GPA2R6</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>`tillvägagångsätt` (sv)</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>APG24E</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>`inlämingsuppgifter` (sv)</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>APG24E</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>`credtis` (en)</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>APG25N</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>`tillvägagångsätt` (sv)</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>APG276</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>`credtis` (en)</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>APG2AA</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>`lärarskicklighetetens` (sv)</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>APG2AC</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>`aanalyze` (en)</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>APG2AC</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>`nalyze` (en)</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>APG2BK</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>`addmitted` (en)</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>APG2C6</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>`credtis` (en)</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>APG2C6</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>`whithin` (en)</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>APG2CM</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>`undervisningensmål` (sv)</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>APG2CM</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>`educare` (en)</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>GPG22K</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>`conciderations` (en)</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>GPG2SC</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>`samhällorienterande` (sv)</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>GPG2SC</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>`sociaty` (en)</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>GPG2SC</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>`understandingn` (en)</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>GPG328</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>`andraämne` (sv)</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>GPG329</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>`andraämne` (sv)</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>GPG3AD</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CG</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>`perspecitves` (en)</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CK</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>`inlämninguppgift` (sv)</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CL</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>`samhällorienterande` (sv)</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CL</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>`sociaty` (en)</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>GPG3FT</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>`addmitted` (en)</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>ARK27Q</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>`tha` (en)</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>ARK29K</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>`cpecialisation` (en)</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29K</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>ARK29L</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>`markonivå` (sv)</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29L</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>GRK366</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>`enivronments` (en)</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK366</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>GRK3B4</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>`ämesteoretiska` (sv)</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>GRV266</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>`mervärdskatt` (sv)</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>GRV2MK</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>`innhåller` (sv)</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>RV1001</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>`glavå` (sv)</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>RV1003</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>`mervärdskatt` (sv)</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>RV1026</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>`glavå` (sv)</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>RV1026</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>`bargening` (en)</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>RV1038</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>`pratices` (en)</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>RV1038</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>`securites` (en)</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>RV1043</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>`förvaltningsrättliga` (sv)</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>RV1043</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>`rättsäkerheten` (sv)</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>RV1045</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>`åtgärdscheman` (sv)</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>RV1055</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>`samt` — …aminationsformer  En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,…</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>ASK22L</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>SKA</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>`formes` (en)</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>ASK22M</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>SKA</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>`reviewscrutiny` (en)</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>ASK289</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>SKA</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>`compative` (en)</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>GSO2PL</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>`credits` — …7.5 credits, Psychological Perspectives on Social Work 7.5 credits credits and Welfare Measures and User Perspective 15 credits…</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>SO1027</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>`abilty` (en)</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>ATR26B</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>`hållbarbetsmål` (sv)</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>ATR2BJ</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>`leaisure` (en)</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>GTR22D</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>`samhållsvetenskap` (sv)</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>GTR22D</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>`värderigsförmåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>GTR265</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>`fömåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>GTR265</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>`afte` (en)</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>GTR26E</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>`erätter` (sv)</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>GTR29Q</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>`förhållningssät` (sv)</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>GTR29Q</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>`assignement` (en)</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>GTR29Q</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>`implmented` (en)</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>GTR2DG</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>`the` — …earch. The course is organised into two parts. In part one, the The course introduces students to quantitative research. The co…</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>GTR2DG</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>`enkätsstudie` (sv)</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>GTR2DP</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>`värderingsfömåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>TR1007</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>`recourses` (en)</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>TR1013</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>`använding` (sv)</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>TR1013</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>`lerning` (en)</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>TR1018</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>`geodemographic` (en)</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>TR1024</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>`fömåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>TR1024</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>`afte` (en)</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>TR1027</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>`fömåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>TR1027</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>`afte` (en)</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>TR1028</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>`förhållningssät` (sv)</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>TR1028</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>`ansd` (en)</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>TR1030</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>`tillvägagångsätt` (sv)</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>TR1031</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>`kulturellafördomar` (sv)</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>TR1034</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>`förvärvda` (sv)</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>TR1034</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>`organisaton` (en)</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>TR2004</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>`stuides` (en)</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
           <t>TR3006</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B186" t="inlineStr">
         <is>
           <t>TRU</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C186" t="inlineStr">
         <is>
           <t>Dubblerat ord</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D186" t="inlineStr">
         <is>
           <t>`the` — …- Independently identify and analyze scientific problems in the the relevant field of knowledge and conduct and report on a pro…</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>TR3006</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>`ocskå` (sv)</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>AS2002</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>`takenup` (en)</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>AS3002</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>`teh` (en)</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>AS3009</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>`literära` (sv)</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>AS3012</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>`outlineof` (en)</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>AS4003</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>`angrepssätt` (sv)</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>KAPSG</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>`jörgensen` (sv)</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>KFPPG</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>`göran` (sv)</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFPPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>KFTKG</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>`åsa` (sv)</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>KMLJG</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>`påbyggbar` (sv)</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>KMPTG</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>`thorbjörn` (sv)</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMPTG</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>LVALA</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>`fändrik` (sv)</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>LVALA</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>`grundlärar` (sv)</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>LVALA</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>`umeå` (sv)</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>LVALA</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>`ämneslärar` (sv)</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>SENGR</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>`utgångpunkt` (sv)</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>SENGR</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>`väldfärdsanalys` (sv)</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>SPARG</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>`enström` (sv)</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>`möjliggörandet` (sv)</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E9"/>
+  <autoFilter ref="A1:E205"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -704,6 +5996,398 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A185" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$192</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E205"/>
+  <dimension ref="A1:E192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5626,359 +5626,8 @@
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>KAPSG</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>`jörgensen` (sv)</t>
-        </is>
-      </c>
-      <c r="E193" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>KFPPG</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>`göran` (sv)</t>
-        </is>
-      </c>
-      <c r="E194" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFPPG</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>KFTKG</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>`åsa` (sv)</t>
-        </is>
-      </c>
-      <c r="E195" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>KMLJG</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>`påbyggbar` (sv)</t>
-        </is>
-      </c>
-      <c r="E196" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
-        <is>
-          <t>KMPTG</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>`thorbjörn` (sv)</t>
-        </is>
-      </c>
-      <c r="E197" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMPTG</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>LVALA</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>`fändrik` (sv)</t>
-        </is>
-      </c>
-      <c r="E198" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>LVALA</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>`grundlärar` (sv)</t>
-        </is>
-      </c>
-      <c r="E199" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>LVALA</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>`umeå` (sv)</t>
-        </is>
-      </c>
-      <c r="E200" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>LVALA</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>`ämneslärar` (sv)</t>
-        </is>
-      </c>
-      <c r="E201" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>SENGR</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>`utgångpunkt` (sv)</t>
-        </is>
-      </c>
-      <c r="E202" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>SENGR</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>`väldfärdsanalys` (sv)</t>
-        </is>
-      </c>
-      <c r="E203" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>SPARG</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>`enström` (sv)</t>
-        </is>
-      </c>
-      <c r="E204" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>`möjliggörandet` (sv)</t>
-        </is>
-      </c>
-      <c r="E205" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E205"/>
+  <autoFilter ref="A1:E192"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -6362,32 +6011,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId381"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$192</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E205"/>
+  <dimension ref="A1:E192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>`att` — ….m. 2014-01-24.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
+          <t>`att` — ….m. 2014-01-24.  \## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5626,359 +5626,8 @@
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>KAPSG</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>`jörgensen` (sv)</t>
-        </is>
-      </c>
-      <c r="E193" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>KFPPG</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>`göran` (sv)</t>
-        </is>
-      </c>
-      <c r="E194" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFPPG</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>KFTKG</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>`åsa` (sv)</t>
-        </is>
-      </c>
-      <c r="E195" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>KMLJG</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>`påbyggbar` (sv)</t>
-        </is>
-      </c>
-      <c r="E196" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
-        <is>
-          <t>KMPTG</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>`thorbjörn` (sv)</t>
-        </is>
-      </c>
-      <c r="E197" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMPTG</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>LVALA</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>`fändrik` (sv)</t>
-        </is>
-      </c>
-      <c r="E198" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>LVALA</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>`grundlärar` (sv)</t>
-        </is>
-      </c>
-      <c r="E199" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>LVALA</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>`umeå` (sv)</t>
-        </is>
-      </c>
-      <c r="E200" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>LVALA</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>`ämneslärar` (sv)</t>
-        </is>
-      </c>
-      <c r="E201" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>SENGR</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>`utgångpunkt` (sv)</t>
-        </is>
-      </c>
-      <c r="E202" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>SENGR</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>`väldfärdsanalys` (sv)</t>
-        </is>
-      </c>
-      <c r="E203" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>SPARG</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>`enström` (sv)</t>
-        </is>
-      </c>
-      <c r="E204" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>`möjliggörandet` (sv)</t>
-        </is>
-      </c>
-      <c r="E205" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E205"/>
+  <autoFilter ref="A1:E192"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -6362,32 +6011,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId381"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$193</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E192"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3388,12 +3388,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GPA2FW</t>
+          <t>FPA2226</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3403,19 +3403,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>`managemet` (en)</t>
+          <t>`cognitiveoriented` (en)</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2226</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GPA2R6</t>
+          <t>GPA2FW</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3425,29 +3425,29 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>`tillvägagångsätt` (sv)</t>
+          <t>`managemet` (en)</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>APG24E</t>
+          <t>GPA2R6</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3457,12 +3457,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>`inlämingsuppgifter` (sv)</t>
+          <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>`credtis` (en)</t>
+          <t>`inlämingsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>APG25N</t>
+          <t>APG24E</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>`tillvägagångsätt` (sv)</t>
+          <t>`credtis` (en)</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>APG276</t>
+          <t>APG25N</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3533,24 +3533,24 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>`credtis` (en)</t>
+          <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>APG2AA</t>
+          <t>APG276</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3560,24 +3560,24 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>`lärarskicklighetetens` (sv)</t>
+          <t>`credtis` (en)</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>APG2AC</t>
+          <t>APG2AA</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3587,17 +3587,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>`aanalyze` (en)</t>
+          <t>`lärarskicklighetetens` (sv)</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>`nalyze` (en)</t>
+          <t>`aanalyze` (en)</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -3631,7 +3631,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>APG2BK</t>
+          <t>APG2AC</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3646,19 +3646,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>`addmitted` (en)</t>
+          <t>`nalyze` (en)</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>APG2C6</t>
+          <t>APG2BK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>`credtis` (en)</t>
+          <t>`addmitted` (en)</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>`whithin` (en)</t>
+          <t>`credtis` (en)</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>APG2CM</t>
+          <t>APG2C6</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3722,17 +3722,17 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>`undervisningensmål` (sv)</t>
+          <t>`whithin` (en)</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C6</t>
         </is>
       </c>
     </row>
@@ -3749,12 +3749,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>`educare` (en)</t>
+          <t>`undervisningensmål` (sv)</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GPG22K</t>
+          <t>APG2CM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3781,19 +3781,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>`conciderations` (en)</t>
+          <t>`educare` (en)</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GPG22K</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3803,17 +3803,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>`samhällorienterande` (sv)</t>
+          <t>`conciderations` (en)</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
         </is>
       </c>
     </row>
@@ -3830,12 +3830,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>`sociaty` (en)</t>
+          <t>`samhällorienterande` (sv)</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>`understandingn` (en)</t>
+          <t>`sociaty` (en)</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GPG328</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3884,24 +3884,24 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>`andraämne` (sv)</t>
+          <t>`understandingn` (en)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GPG329</t>
+          <t>GPG328</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3921,14 +3921,14 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GPG3AD</t>
+          <t>GPG329</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3938,24 +3938,24 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
+          <t>`andraämne` (sv)</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GPG3CG</t>
+          <t>GPG3AD</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3965,24 +3965,24 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>`perspecitves` (en)</t>
+          <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GPG3CK</t>
+          <t>GPG3CG</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3992,24 +3992,24 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>`inlämninguppgift` (sv)</t>
+          <t>`perspecitves` (en)</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>GPG3CK</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>`samhällorienterande` (sv)</t>
+          <t>`inlämninguppgift` (sv)</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
         </is>
       </c>
     </row>
@@ -4046,12 +4046,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>`sociaty` (en)</t>
+          <t>`samhällorienterande` (sv)</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -4063,7 +4063,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GPG3FT</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4078,24 +4078,24 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>`addmitted` (en)</t>
+          <t>`sociaty` (en)</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>ARK27Q</t>
+          <t>GPG3FT</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4105,19 +4105,19 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>`tha` (en)</t>
+          <t>`addmitted` (en)</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>ARK29K</t>
+          <t>ARK27Q</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4132,19 +4132,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>`cpecialisation` (en)</t>
+          <t>`tha` (en)</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>ARK29L</t>
+          <t>ARK29K</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4154,24 +4154,24 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>`markonivå` (sv)</t>
+          <t>`cpecialisation` (en)</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29K</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GRK366</t>
+          <t>ARK29L</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4181,24 +4181,24 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>`enivronments` (en)</t>
+          <t>`markonivå` (sv)</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK366</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29L</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GRK3B4</t>
+          <t>GRK366</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4208,29 +4208,29 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>`ämesteoretiska` (sv)</t>
+          <t>`enivronments` (en)</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK366</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>GRK3B4</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4240,19 +4240,19 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>`mervärdskatt` (sv)</t>
+          <t>`ämesteoretiska` (sv)</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GRV2MK</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4267,19 +4267,19 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>`innhåller` (sv)</t>
+          <t>`mervärdskatt` (sv)</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>RV1001</t>
+          <t>GRV2MK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4294,19 +4294,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>`glavå` (sv)</t>
+          <t>`innhåller` (sv)</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>RV1003</t>
+          <t>RV1001</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4321,19 +4321,19 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>`mervärdskatt` (sv)</t>
+          <t>`glavå` (sv)</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>RV1026</t>
+          <t>RV1003</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4348,12 +4348,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>`glavå` (sv)</t>
+          <t>`mervärdskatt` (sv)</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>`bargening` (en)</t>
+          <t>`glavå` (sv)</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -4387,7 +4387,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>RV1026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>`pratices` (en)</t>
+          <t>`bargening` (en)</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>`securites` (en)</t>
+          <t>`pratices` (en)</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -4441,7 +4441,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>RV1043</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4451,17 +4451,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>`förvaltningsrättliga` (sv)</t>
+          <t>`securites` (en)</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
@@ -4483,7 +4483,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>`rättsäkerheten` (sv)</t>
+          <t>`förvaltningsrättliga` (sv)</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>RV1045</t>
+          <t>RV1043</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4510,19 +4510,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>`åtgärdscheman` (sv)</t>
+          <t>`rättsäkerheten` (sv)</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>RV1055</t>
+          <t>RV1045</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4532,51 +4532,51 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>`samt` — …aminationsformer  En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,…</t>
+          <t>`åtgärdscheman` (sv)</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>ASK22L</t>
+          <t>RV1055</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>`formes` (en)</t>
+          <t>`samt` — …aminationsformer  En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,…</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>ASK22M</t>
+          <t>ASK22L</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4591,19 +4591,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>`reviewscrutiny` (en)</t>
+          <t>`formes` (en)</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>ASK289</t>
+          <t>ASK22M</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4618,46 +4618,46 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>`compative` (en)</t>
+          <t>`reviewscrutiny` (en)</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>GSO2PL</t>
+          <t>ASK289</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>`credits` — …7.5 credits, Psychological Perspectives on Social Work 7.5 credits credits and Welfare Measures and User Perspective 15 credits…</t>
+          <t>`compative` (en)</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>SO1027</t>
+          <t>GSO2PL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4667,51 +4667,51 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>`abilty` (en)</t>
+          <t>`credits` — …7.5 credits, Psychological Perspectives on Social Work 7.5 credits credits and Welfare Measures and User Perspective 15 credits…</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>ATR26B</t>
+          <t>SO1027</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>`hållbarbetsmål` (sv)</t>
+          <t>`abilty` (en)</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>ATR2BJ</t>
+          <t>ATR26B</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4721,24 +4721,24 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>`leaisure` (en)</t>
+          <t>`hållbarbetsmål` (sv)</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>GTR22D</t>
+          <t>ATR2BJ</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4748,17 +4748,17 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>`samhållsvetenskap` (sv)</t>
+          <t>`leaisure` (en)</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4780,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>`värderigsförmåga` (sv)</t>
+          <t>`samhållsvetenskap` (sv)</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -4792,7 +4792,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>GTR265</t>
+          <t>GTR22D</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>`fömåga` (sv)</t>
+          <t>`värderigsförmåga` (sv)</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
         </is>
       </c>
     </row>
@@ -4829,12 +4829,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>`afte` (en)</t>
+          <t>`fömåga` (sv)</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>GTR26E</t>
+          <t>GTR265</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4856,24 +4856,24 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>`erätter` (sv)</t>
+          <t>`afte` (en)</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>GTR29Q</t>
+          <t>GTR26E</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>`förhållningssät` (sv)</t>
+          <t>`erätter` (sv)</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
         </is>
       </c>
     </row>
@@ -4910,12 +4910,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>`assignement` (en)</t>
+          <t>`förhållningssät` (sv)</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>`implmented` (en)</t>
+          <t>`assignement` (en)</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -4954,7 +4954,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>GTR29Q</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4964,17 +4964,17 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>`the` — …earch. The course is organised into two parts. In part one, the The course introduces students to quantitative research. The co…</t>
+          <t>`implmented` (en)</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
         </is>
       </c>
     </row>
@@ -4991,12 +4991,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>`enkätsstudie` (sv)</t>
+          <t>`the` — …earch. The course is organised into two parts. In part one, the The course introduces students to quantitative research. The co…</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -5008,7 +5008,7 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>GTR2DP</t>
+          <t>GTR2DG</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5023,19 +5023,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>`värderingsfömåga` (sv)</t>
+          <t>`enkätsstudie` (sv)</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>GTR2DP</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5045,24 +5045,24 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>`recourses` (en)</t>
+          <t>`värderingsfömåga` (sv)</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>TR1013</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5072,17 +5072,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>`använding` (sv)</t>
+          <t>`recourses` (en)</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>`lerning` (en)</t>
+          <t>`använding` (sv)</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -5116,7 +5116,7 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>TR1018</t>
+          <t>TR1013</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5131,19 +5131,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>`geodemographic` (en)</t>
+          <t>`lerning` (en)</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>TR1024</t>
+          <t>TR1018</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5153,17 +5153,17 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>`fömåga` (sv)</t>
+          <t>`geodemographic` (en)</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
         </is>
       </c>
     </row>
@@ -5180,12 +5180,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>`afte` (en)</t>
+          <t>`fömåga` (sv)</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -5197,7 +5197,7 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>TR1027</t>
+          <t>TR1024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5207,17 +5207,17 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>`fömåga` (sv)</t>
+          <t>`afte` (en)</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
         </is>
       </c>
     </row>
@@ -5234,12 +5234,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>`afte` (en)</t>
+          <t>`fömåga` (sv)</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>TR1028</t>
+          <t>TR1027</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5261,17 +5261,17 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>`förhållningssät` (sv)</t>
+          <t>`afte` (en)</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
         </is>
       </c>
     </row>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>`ansd` (en)</t>
+          <t>`förhållningssät` (sv)</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -5305,7 +5305,7 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>TR1030</t>
+          <t>TR1028</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5315,24 +5315,24 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>`tillvägagångsätt` (sv)</t>
+          <t>`ansd` (en)</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>TR1031</t>
+          <t>TR1030</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5347,19 +5347,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>`kulturellafördomar` (sv)</t>
+          <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>TR1034</t>
+          <t>TR1031</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>`förvärvda` (sv)</t>
+          <t>`kulturellafördomar` (sv)</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>`organisaton` (en)</t>
+          <t>`förvärvda` (sv)</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>TR2004</t>
+          <t>TR1034</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5428,19 +5428,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>`stuides` (en)</t>
+          <t>`organisaton` (en)</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>TR3006</t>
+          <t>TR2004</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5450,17 +5450,17 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>`the` — …- Independently identify and analyze scientific problems in the the relevant field of knowledge and conduct and report on a pro…</t>
+          <t>`stuides` (en)</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
         </is>
       </c>
     </row>
@@ -5477,12 +5477,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>`ocskå` (sv)</t>
+          <t>`the` — …- Independently identify and analyze scientific problems in the the relevant field of knowledge and conduct and report on a pro…</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -5494,34 +5494,34 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>AS2002</t>
+          <t>TR3006</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>UVX</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>`takenup` (en)</t>
+          <t>`ocskå` (sv)</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>AS3002</t>
+          <t>AS2002</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5536,19 +5536,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>`teh` (en)</t>
+          <t>`takenup` (en)</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>AS3009</t>
+          <t>AS3002</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5558,24 +5558,24 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>`literära` (sv)</t>
+          <t>`teh` (en)</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>AS3012</t>
+          <t>AS3009</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5585,49 +5585,76 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>`outlineof` (en)</t>
+          <t>`literära` (sv)</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
+          <t>AS3012</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>`outlineof` (en)</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
           <t>AS4003</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B193" t="inlineStr">
         <is>
           <t>UVX</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
         <is>
           <t>`angrepssätt` (sv)</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E192"/>
+  <autoFilter ref="A1:E193"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -6011,6 +6038,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId381"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -685,359 +685,8 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>KAPSG</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>`jörgensen` (sv)</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>KFPPG</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>`göran` (sv)</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFPPG</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>KFTKG</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>`åsa` (sv)</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>KMLJG</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>`påbyggbar` (sv)</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>KMPTG</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>`thorbjörn` (sv)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMPTG</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>LVALA</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>`fändrik` (sv)</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>LVALA</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>`grundlärar` (sv)</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>LVALA</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>`umeå` (sv)</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>LVALA</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>`ämneslärar` (sv)</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>SENGR</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>`utgångpunkt` (sv)</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>SENGR</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>`väldfärdsanalys` (sv)</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>SPARG</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>`enström` (sv)</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>`möjliggörandet` (sv)</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E22"/>
+  <autoFilter ref="A1:E9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -1055,32 +704,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$193</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,221 +472,5189 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ABQ2B4</t>
+          <t>AB1019</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`en` — …- formulera och muntligt framföra konstruktiv kritik på en en text av vetenskaplig karaktär    - vetenskapligt värdera oc…</t>
+          <t>`arbetsträtt` (sv)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1019</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>FI1039</t>
+          <t>AB1019</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`have` — …urthermore, on completion of the course, the student should have have the ability to :       - be reflective in relation to probl…</t>
+          <t>`förläsningar` (sv)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1019</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>PE1067</t>
+          <t>AB1019</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PEA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`att` — ….m. 2014-01-24.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
+          <t>`municpality` (en)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1019</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GPG3AD</t>
+          <t>AB1022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
+          <t>`därmellen` (sv)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1022</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>RV1055</t>
+          <t>AB1029</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`samt` — …aminationsformer  En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,…</t>
+          <t>`abilith` (en)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1029</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GSO2PL</t>
+          <t>AB3001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`credits` — …7.5 credits, Psychological Perspectives on Social Work 7.5 credits credits and Welfare Measures and User Perspective 15 credits…</t>
+          <t>`kommunförb` (sv)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB3001</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GTR2DG</t>
+          <t>ABQ2AM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`the` — …earch. The course is organised into two parts. In part one, the The course introduces students to quantitative research. The co…</t>
+          <t>`inludes` (en)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>ABQ2AM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>`managment` (en)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ABQ2B4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>`en` — …- formulera och muntligt framföra konstruktiv kritik på en en text av vetenskaplig karaktär    - vetenskapligt värdera oc…</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>BQ1079</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>`devolop` (en)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ1079</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>BQ1079</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>`strucuring` (en)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ1079</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>BQ2018</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>`lärarare` (sv)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>BQ2057</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>`postproduction` (en)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2057</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>GBQ29D</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>`undergradaute` (en)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29D</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>GBQ29E</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>`undergradaute` (en)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29E</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>GBQ2U6</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>`beställningsfilmsproduktion` (sv)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>GBQ2UB</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>`berättandestruktur` (sv)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UB</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>GBQ2WH</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>`tbt` (en)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WH</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>GBQ2WK</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>`berätttarelement` (sv)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>GBQ38W</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>`höguppupplöst` (sv)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>GBQ3AW</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>`explainer` (en)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>GBQ3FG</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BPO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>`excercises` (en)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>EU1027</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EUN</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>`grundäggande` (sv)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>EU1033</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>EUN</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>`itssocial` (en)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1033</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>EU1034</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>EUN</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>`förhandlingprocesser` (sv)</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1034</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>GEU2KV</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>EUN</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>`opportunties` (en)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>GEU2KV</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>EUN</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>`willll` (en)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>AFI273</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>`contignency` (en)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFI273</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>FI1023</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>`philosohical` (en)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>FI1024</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>`etichs` (en)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>FI1039</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>`have` — …urthermore, on completion of the course, the student should have have the ability to :       - be reflective in relation to probl…</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>FI1039</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>`asessment` (en)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>FI1039</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>`developement` (en)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>GFI3BT</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>`througout` (en)</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>GFI3BU</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FIA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>`througout` (en)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>AHI272</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>`poitical` (en)</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>AHI29Q</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>`consultaion` (en)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>AHI29Q</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>`situatin` (en)</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>AS2005</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>`takenup` (en)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>AS3017</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>`literära` (sv)</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>AS3020</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>`outlineof` (en)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>AS3022</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>`teh` (en)</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>GHI29Y</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>`innhållet` (sv)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>GHI33T</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>`problemförmuleringsförmåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>GHI33V</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>`delkurseninnehåller` (sv)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>GHI33V</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>`godkäng` (sv)</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>GHI35A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>`analyseratmänniskors` (sv)</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>GHI35A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>`medförintelsen` (sv)</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>GHI35A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>`människorsagerande` (sv)</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>GHI362</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>`självstänigt` (sv)</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>HI1008</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>`criterions` (en)</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>HI2011</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>`historiedidaktikområdet` (sv)</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>HI2012</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>`sjävvalt` (sv)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>HI2016</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>`sjävvalt` (sv)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>HI3019</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>HIA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>`självständg` (sv)</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3019</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>AKG27R</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>`compulsotry` (en)</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>AKG27R</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>`curent` (en)</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>AKG27R</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>`theoretica` (en)</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>GKG3AT</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>`tilllämpas` (sv)</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>GKG3AT</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>`writtten` (en)</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>KG1024</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>`beräklningstung` (sv)</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>KG1024</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>`quantitativ` (en)</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>KG1025</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>`evolvement` (en)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>KG1025</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>`thise` (en)</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>KG2001</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>`obser` (en)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>KG2001</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>`perspetives` (en)</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>KG2001</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>`standarized` (en)</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>KG2001</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>`vations` (en)</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>KG2005</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>`qualititative` (en)</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>KG3010</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>`recognises` (en)</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>KG3011</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>`kartöverlägg` (sv)</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>KG3014</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>`eaxaminer` (en)</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>KG3015</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>`eaxaminer` (en)</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>KG3016</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>KGA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>`gällade` (sv)</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>GLP236</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>`framträdandeform` (sv)</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>GLP359</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>`djing` (en)</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>GLP3AH</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>`excercises` (en)</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>LP1032</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>`scholary` (en)</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>LP1032</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>`sumarise` (en)</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>LP1071</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>`erätter` (sv)</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>LP1071</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>`evaulates` (en)</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>LP2012</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>`intiate` (en)</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>LP2013</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>`learnings` (en)</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>LP2013</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>LPU</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>`litterature` (en)</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>GMN3F2</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>MPR</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>`incuding` (en)</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>NA1024</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>`distancelectures` (en)</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>NA1027</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>`förläsningar` (sv)</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>NA1029</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>`differentiat` (en)</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>NA1030</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>`excercises` (en)</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>NA1032</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>`descirbe` (en)</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>NA1036</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>`longterm` (en)</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>NA1036</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>`shortterm` (en)</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>NA1039</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>`assingments` (en)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>NA2008</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>`kalandermånader` (sv)</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>NA2008</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>`calender` (en)</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>NA2008</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>`oppobet` (en)</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>NA2008</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>`opposnent` (en)</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>NA2009</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>`resultas` (en)</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>NA3001</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>`länderjämförelser` (sv)</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>NA3010</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>`kalandermånader` (sv)</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>NA3011</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>NAA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>`tobbit` (en)</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>GPE3AJ</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>`kollegialtlärande` (sv)</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>PE1020</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>`gryndsyn` (en)</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>PE1023</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>`rättsäkerhet` (sv)</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>PE1067</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>`att` — ….m. 2014-01-24.  \## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>PE1068</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>`känndom` (sv)</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>PE2005</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>`gryndsyn` (en)</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>PE3004</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>`rättsäkerhet` (sv)</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>FPA2226</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>PEDAGARB</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>`cognitiveoriented` (en)</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2226</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>GPA2FW</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>`managemet` (en)</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>GPA2R6</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PEE</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>`tillvägagångsätt` (sv)</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>APG24E</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>`inlämingsuppgifter` (sv)</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>APG24E</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>`credtis` (en)</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>APG25N</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>`tillvägagångsätt` (sv)</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>APG276</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>`credtis` (en)</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>APG2AA</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>`lärarskicklighetetens` (sv)</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>APG2AC</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>`aanalyze` (en)</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>APG2AC</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>`nalyze` (en)</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>APG2BK</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>`addmitted` (en)</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>APG2C6</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>`credtis` (en)</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>APG2C6</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>`whithin` (en)</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>APG2CM</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>`undervisningensmål` (sv)</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>APG2CM</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>`educare` (en)</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>GPG22K</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>`conciderations` (en)</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>GPG2SC</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>`samhällorienterande` (sv)</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>GPG2SC</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>`sociaty` (en)</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>GPG2SC</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>`understandingn` (en)</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>GPG328</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>`andraämne` (sv)</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>GPG329</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>`andraämne` (sv)</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>GPG3AD</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CG</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>`perspecitves` (en)</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CK</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>`inlämninguppgift` (sv)</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CL</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>`samhällorienterande` (sv)</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CL</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>`sociaty` (en)</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>GPG3FT</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>`addmitted` (en)</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>ARK27Q</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>`tha` (en)</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK27Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>ARK29K</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>`cpecialisation` (en)</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29K</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>ARK29L</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>`markonivå` (sv)</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK29L</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>GRK366</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>`enivronments` (en)</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK366</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>GRK3B4</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>`ämesteoretiska` (sv)</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>GRV266</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>`mervärdskatt` (sv)</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>GRV2MK</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>`innhåller` (sv)</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>RV1001</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>`glavå` (sv)</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1001</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>RV1003</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>`mervärdskatt` (sv)</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1003</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>RV1026</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>`glavå` (sv)</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>RV1026</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>`bargening` (en)</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1026</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>RV1038</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>`pratices` (en)</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>RV1038</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>`securites` (en)</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>RV1043</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>`förvaltningsrättliga` (sv)</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>RV1043</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>`rättsäkerheten` (sv)</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>RV1045</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>`åtgärdscheman` (sv)</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>RV1055</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>`samt` — …aminationsformer  En kortare dugga per rättsområde (4x1 hp) samt samt en skriftlig inlämningsuppgift med avslutande seminarie (3,…</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>ASK22L</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>SKA</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>`formes` (en)</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22L</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>ASK22M</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>SKA</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>`reviewscrutiny` (en)</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK22M</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>ASK289</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>SKA</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>`compative` (en)</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASK289</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>GSO2PL</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>`credits` — …7.5 credits, Psychological Perspectives on Social Work 7.5 credits credits and Welfare Measures and User Perspective 15 credits…</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>SO1027</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>`abilty` (en)</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>ATR26B</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>`hållbarbetsmål` (sv)</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR26B</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>ATR2BJ</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>`leaisure` (en)</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATR2BJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>GTR22D</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>`samhållsvetenskap` (sv)</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>GTR22D</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>`värderigsförmåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR22D</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>GTR265</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>`fömåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>GTR265</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>`afte` (en)</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR265</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>GTR26E</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>`erätter` (sv)</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR26E</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>GTR29Q</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>`förhållningssät` (sv)</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>GTR29Q</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>`assignement` (en)</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>GTR29Q</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>`implmented` (en)</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>GTR2DG</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>`the` — …earch. The course is organised into two parts. In part one, the The course introduces students to quantitative research. The co…</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>GTR2DG</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>`enkätsstudie` (sv)</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DG</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>GTR2DP</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>`värderingsfömåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2DP</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>TR1007</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>`recourses` (en)</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>TR1013</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>`använding` (sv)</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>TR1013</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>`lerning` (en)</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1013</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>TR1018</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>`geodemographic` (en)</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>TR1024</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>`fömåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>TR1024</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>`afte` (en)</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>TR1027</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>`fömåga` (sv)</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>TR1027</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>`afte` (en)</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>TR1028</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>`förhållningssät` (sv)</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>TR1028</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>`ansd` (en)</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>TR1030</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>`tillvägagångsätt` (sv)</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>TR1031</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>`kulturellafördomar` (sv)</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1031</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>TR1034</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>`förvärvda` (sv)</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>TR1034</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>`organisaton` (en)</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1034</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>TR2004</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>`stuides` (en)</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
           <t>TR3006</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B187" t="inlineStr">
         <is>
           <t>TRU</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C187" t="inlineStr">
         <is>
           <t>Dubblerat ord</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D187" t="inlineStr">
         <is>
           <t>`the` — …- Independently identify and analyze scientific problems in the the relevant field of knowledge and conduct and report on a pro…</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
         </is>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>TR3006</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>`ocskå` (sv)</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>AS2002</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>`takenup` (en)</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>AS3002</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>`teh` (en)</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3002</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>AS3009</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>`literära` (sv)</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>AS3012</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>`outlineof` (en)</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>AS4003</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>UVX</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>`angrepssätt` (sv)</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS4003</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E9"/>
+  <autoFilter ref="A1:E193"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -704,6 +5672,374 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E173" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A181" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A185" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A187" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E190" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E191" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
@@ -3295,7 +3295,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>`att` — ….m. 2014-01-24.  \## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
+          <t>`att` — ….m. 2014-01-24.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">

--- a/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$206</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5653,8 +5653,359 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>KAPSG</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>`jörgensen` (sv)</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>KFPPG</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>`göran` (sv)</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFPPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>KFTKG</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>`åsa` (sv)</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>KMLJG</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>`påbyggbar` (sv)</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>KMPTG</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>`thorbjörn` (sv)</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMPTG</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>LVALA</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>`fändrik` (sv)</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>LVALA</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>`grundlärar` (sv)</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>LVALA</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>`umeå` (sv)</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>LVALA</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>`ämneslärar` (sv)</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>SENGR</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>`utgångpunkt` (sv)</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>SENGR</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>`väldfärdsanalys` (sv)</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>SPARG</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>`enström` (sv)</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>`möjliggörandet` (sv)</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E193"/>
+  <autoFilter ref="A1:E206"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -6040,6 +6391,32 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A206" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$193</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E206"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>`att` — ….m. 2014-01-24.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
+          <t>`att` — ….m. 2014-01-24.  \## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5653,359 +5653,8 @@
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>KAPSG</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>`jörgensen` (sv)</t>
-        </is>
-      </c>
-      <c r="E194" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>KFPPG</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>`göran` (sv)</t>
-        </is>
-      </c>
-      <c r="E195" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFPPG</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>KFTKG</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>`åsa` (sv)</t>
-        </is>
-      </c>
-      <c r="E196" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
-        <is>
-          <t>KMLJG</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>`påbyggbar` (sv)</t>
-        </is>
-      </c>
-      <c r="E197" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>KMPTG</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>`thorbjörn` (sv)</t>
-        </is>
-      </c>
-      <c r="E198" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMPTG</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>LVALA</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>`fändrik` (sv)</t>
-        </is>
-      </c>
-      <c r="E199" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>LVALA</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>`grundlärar` (sv)</t>
-        </is>
-      </c>
-      <c r="E200" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>LVALA</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>`umeå` (sv)</t>
-        </is>
-      </c>
-      <c r="E201" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>LVALA</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>`ämneslärar` (sv)</t>
-        </is>
-      </c>
-      <c r="E202" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>SENGR</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>`utgångpunkt` (sv)</t>
-        </is>
-      </c>
-      <c r="E203" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>SENGR</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>`väldfärdsanalys` (sv)</t>
-        </is>
-      </c>
-      <c r="E204" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
-        <is>
-          <t>SPARG</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>`enström` (sv)</t>
-        </is>
-      </c>
-      <c r="E205" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>`möjliggörandet` (sv)</t>
-        </is>
-      </c>
-      <c r="E206" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E206"/>
+  <autoFilter ref="A1:E193"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -6391,32 +6040,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A206" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$207</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>`att` — ….m. 2014-01-24.  \## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
+          <t>`att` — ….m. 2014-01-24.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5653,8 +5653,386 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>HAFSA</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>`västafrika` (sv)</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>KAPSG</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>`jörgensen` (sv)</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>KFPPG</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>`göran` (sv)</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFPPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>KFTKG</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>`åsa` (sv)</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>KMLJG</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>`påbyggbar` (sv)</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>KMPTG</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>`thorbjörn` (sv)</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMPTG</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>LVALA</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>`fändrik` (sv)</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>LVALA</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>`grundlärar` (sv)</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>LVALA</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>`umeå` (sv)</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>LVALA</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>`ämneslärar` (sv)</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>SENGR</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>`utgångpunkt` (sv)</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>SENGR</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>`väldfärdsanalys` (sv)</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>SPARG</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>`enström` (sv)</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>`möjliggörandet` (sv)</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E193"/>
+  <autoFilter ref="A1:E207"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -6040,6 +6418,34 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E192" r:id="rId382"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId383"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E193" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E194" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E195" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E196" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E197" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A198" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E198" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E199" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E200" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E201" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E202" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E203" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E204" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E205" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A206" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E206" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A207" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E207" r:id="rId412"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$207</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$G$207</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E207"/>
+  <dimension ref="A1:G207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>2013-02-21</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>`arbetsträtt` (sv)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1019</t>
         </is>
@@ -509,15 +527,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>2013-02-21</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>`förläsningar` (sv)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1019</t>
         </is>
@@ -536,15 +560,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+          <t>2013-02-21</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>`municpality` (en)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1019</t>
         </is>
@@ -563,15 +593,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>2013-06-13</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>`därmellen` (sv)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1022</t>
         </is>
@@ -590,15 +626,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+          <t>2015-09-15</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>`abilith` (en)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1029</t>
         </is>
@@ -617,15 +659,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+          <t>2009-11-26</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>`kommunförb` (sv)</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB3001</t>
         </is>
@@ -644,15 +692,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>`inludes` (en)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
         </is>
@@ -671,15 +725,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>`managment` (en)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
         </is>
@@ -698,15 +758,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Dubblerat ord</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>`en` — …- formulera och muntligt framföra konstruktiv kritik på en en text av vetenskaplig karaktär    - vetenskapligt värdera oc…</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2B4</t>
         </is>
@@ -725,15 +791,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+          <t>2014-03-18</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>`devolop` (en)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ1079</t>
         </is>
@@ -752,15 +824,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+          <t>2014-03-18</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>`strucuring` (en)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ1079</t>
         </is>
@@ -779,15 +857,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>2011-10-13</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2018-12-10</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>`lärarare` (sv)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2018</t>
         </is>
@@ -806,15 +894,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+          <t>2017-03-22</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>`postproduction` (en)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BQ2057</t>
         </is>
@@ -833,15 +927,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+          <t>2019-05-03</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>`undergradaute` (en)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29D</t>
         </is>
@@ -860,15 +960,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+          <t>2019-05-03</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>`undergradaute` (en)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ29E</t>
         </is>
@@ -887,15 +993,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+          <t>2022-02-04</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>`beställningsfilmsproduktion` (sv)</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2U6</t>
         </is>
@@ -914,15 +1026,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+          <t>2022-02-07</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>`berättandestruktur` (sv)</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UB</t>
         </is>
@@ -941,15 +1059,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+          <t>2022-05-25</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>`tbt` (en)</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WH</t>
         </is>
@@ -968,15 +1092,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+          <t>2022-05-25</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>`berätttarelement` (sv)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WK</t>
         </is>
@@ -995,15 +1125,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>`höguppupplöst` (sv)</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ38W</t>
         </is>
@@ -1022,15 +1158,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>`explainer` (en)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3AW</t>
         </is>
@@ -1049,15 +1191,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>`excercises` (en)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ3FG</t>
         </is>
@@ -1076,15 +1224,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+          <t>2013-11-14</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>`grundäggande` (sv)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1027</t>
         </is>
@@ -1103,15 +1257,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+          <t>2015-02-26</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>`itssocial` (en)</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1033</t>
         </is>
@@ -1130,15 +1290,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+          <t>2015-06-11</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>`förhandlingprocesser` (sv)</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1034</t>
         </is>
@@ -1157,15 +1323,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+          <t>2020-11-26</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>`opportunties` (en)</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
         </is>
@@ -1184,15 +1356,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+          <t>2020-11-26</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>`willll` (en)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEU2KV</t>
         </is>
@@ -1211,15 +1389,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>`contignency` (en)</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFI273</t>
         </is>
@@ -1238,15 +1426,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2006-10-19</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>`philosohical` (en)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1023</t>
         </is>
@@ -1265,15 +1463,25 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2006-10-19</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>2020-07-06</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>`etichs` (en)</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1024</t>
         </is>
@@ -1292,15 +1500,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>2011-05-30</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>Dubblerat ord</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>`have` — …urthermore, on completion of the course, the student should have have the ability to :       - be reflective in relation to probl…</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
@@ -1319,15 +1537,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2011-05-30</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>`asessment` (en)</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
@@ -1346,15 +1574,25 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2011-05-30</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>2020-07-03</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>`developement` (en)</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1039</t>
         </is>
@@ -1373,15 +1611,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>`througout` (en)</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
         </is>
@@ -1400,15 +1644,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>`througout` (en)</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
         </is>
@@ -1427,15 +1677,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>`poitical` (en)</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI272</t>
         </is>
@@ -1454,15 +1710,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>`consultaion` (en)</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
         </is>
@@ -1481,15 +1743,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>`situatin` (en)</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AHI29Q</t>
         </is>
@@ -1508,15 +1776,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+          <t>2018-02-13</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>`takenup` (en)</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS2005</t>
         </is>
@@ -1535,15 +1809,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+          <t>2017-09-26</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>`literära` (sv)</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3017</t>
         </is>
@@ -1562,15 +1842,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+          <t>2017-09-26</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>`outlineof` (en)</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3020</t>
         </is>
@@ -1589,15 +1875,25 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2018-02-13</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>2023-03-06</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>`teh` (en)</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AS3022</t>
         </is>
@@ -1616,15 +1912,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+          <t>2019-06-17</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>`innhållet` (sv)</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
         </is>
@@ -1643,15 +1945,25 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>2023-03-08</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>2023-05-25</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>`problemförmuleringsförmåga` (sv)</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
         </is>
@@ -1670,15 +1982,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+          <t>2023-03-15</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>`delkurseninnehåller` (sv)</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
         </is>
@@ -1697,15 +2015,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+          <t>2023-03-15</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>`godkäng` (sv)</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
         </is>
@@ -1724,15 +2048,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>`analyseratmänniskors` (sv)</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
         </is>
@@ -1751,15 +2081,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>`medförintelsen` (sv)</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
         </is>
@@ -1778,15 +2114,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>`människorsagerande` (sv)</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
         </is>
@@ -1805,15 +2147,25 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>`självstänigt` (sv)</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
         </is>
@@ -1832,15 +2184,25 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2011-11-25</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>2014-08-01</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>`criterions` (en)</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1008</t>
         </is>
@@ -1859,15 +2221,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+          <t>2015-02-05</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>`historiedidaktikområdet` (sv)</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2011</t>
         </is>
@@ -1886,15 +2254,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+          <t>2015-02-05</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>`sjävvalt` (sv)</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2012</t>
         </is>
@@ -1913,15 +2287,25 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>2016-05-18</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>2018-09-13</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>`sjävvalt` (sv)</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI2016</t>
         </is>
@@ -1940,15 +2324,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
+          <t>2015-09-17</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>`självständg` (sv)</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI3019</t>
         </is>
@@ -1967,15 +2357,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
+          <t>2022-02-16</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>`compulsotry` (en)</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
         </is>
@@ -1994,15 +2390,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+          <t>2022-02-16</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>`curent` (en)</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
         </is>
@@ -2021,15 +2423,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+          <t>2022-02-16</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>`theoretica` (en)</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKG27R</t>
         </is>
@@ -2048,15 +2456,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>`tilllämpas` (sv)</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
         </is>
@@ -2075,15 +2489,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>`writtten` (en)</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKG3AT</t>
         </is>
@@ -2102,15 +2522,25 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>2010-02-23</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>2012-10-01</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>`beräklningstung` (sv)</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
         </is>
@@ -2129,15 +2559,25 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2010-02-23</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>2012-10-01</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>`quantitativ` (en)</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1024</t>
         </is>
@@ -2156,15 +2596,25 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2010-04-20</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>2012-10-18</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>`evolvement` (en)</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
         </is>
@@ -2183,15 +2633,25 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2010-04-20</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>2012-10-18</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t>`thise` (en)</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1025</t>
         </is>
@@ -2210,15 +2670,25 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2007-05-30</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>2011-12-22</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t>`obser` (en)</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
@@ -2237,15 +2707,25 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2007-05-30</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>2011-12-22</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t>`perspetives` (en)</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
@@ -2264,15 +2744,25 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2007-05-30</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>2011-12-22</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>`standarized` (en)</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
@@ -2291,15 +2781,25 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2007-05-30</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t>2011-12-22</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t>`vations` (en)</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
@@ -2318,15 +2818,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
+          <t>2014-01-30</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>`qualititative` (en)</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
         </is>
@@ -2345,15 +2851,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+          <t>2009-03-30</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>`recognises` (en)</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3010</t>
         </is>
@@ -2372,15 +2884,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
+          <t>2009-09-02</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>`kartöverlägg` (sv)</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3011</t>
         </is>
@@ -2399,15 +2917,25 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2010-04-20</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t>2012-04-12</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t>`eaxaminer` (en)</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3014</t>
         </is>
@@ -2426,15 +2954,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
+          <t>2013-02-25</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>`eaxaminer` (en)</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3015</t>
         </is>
@@ -2453,15 +2987,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+          <t>2013-12-12</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>`gällade` (sv)</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
         </is>
@@ -2480,15 +3020,21 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+          <t>2018-05-21</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>`framträdandeform` (sv)</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP236</t>
         </is>
@@ -2507,15 +3053,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>`djing` (en)</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP359</t>
         </is>
@@ -2534,15 +3086,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>`excercises` (en)</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP3AH</t>
         </is>
@@ -2561,15 +3119,25 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2011-05-03</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t>2018-06-15</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t>`scholary` (en)</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
         </is>
@@ -2588,15 +3156,25 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2011-05-03</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>2018-06-15</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t>`sumarise` (en)</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1032</t>
         </is>
@@ -2615,15 +3193,25 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>2015-12-10</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t>`erätter` (sv)</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
         </is>
@@ -2642,15 +3230,25 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2015-12-10</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>`evaulates` (en)</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP1071</t>
         </is>
@@ -2669,15 +3267,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>`intiate` (en)</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2012</t>
         </is>
@@ -2696,15 +3300,21 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>`learnings` (en)</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
         </is>
@@ -2723,15 +3333,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>`litterature` (en)</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2013</t>
         </is>
@@ -2750,15 +3366,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>`incuding` (en)</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMN3F2</t>
         </is>
@@ -2777,15 +3399,21 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
+          <t>2009-10-19</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>`distancelectures` (en)</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1024</t>
         </is>
@@ -2804,15 +3432,25 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>2009-10-19</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t>2013-03-07</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t>`förläsningar` (sv)</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
         </is>
@@ -2831,15 +3469,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
+          <t>2013-02-01</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>`differentiat` (en)</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1029</t>
         </is>
@@ -2858,15 +3502,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
+          <t>2013-02-01</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>`excercises` (en)</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1030</t>
         </is>
@@ -2885,15 +3535,25 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2013-02-21</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t>2015-06-17</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t>`descirbe` (en)</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1032</t>
         </is>
@@ -2912,15 +3572,25 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2013-02-01</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t>2020-01-19</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t>`longterm` (en)</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
         </is>
@@ -2939,15 +3609,25 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2013-02-01</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t>2020-01-19</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t>`shortterm` (en)</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1036</t>
         </is>
@@ -2966,15 +3646,21 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
+          <t>2014-03-13</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>`assingments` (en)</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1039</t>
         </is>
@@ -2993,15 +3679,21 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
+          <t>2013-02-01</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>`kalandermånader` (sv)</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
@@ -3020,15 +3712,21 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
+          <t>2013-02-01</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>`calender` (en)</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
@@ -3047,15 +3745,21 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
+          <t>2013-02-01</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>`oppobet` (en)</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
@@ -3074,15 +3778,21 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
+          <t>2013-02-01</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>`opposnent` (en)</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2008</t>
         </is>
@@ -3101,15 +3811,21 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
+          <t>2013-02-21</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>`resultas` (en)</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2009</t>
         </is>
@@ -3128,15 +3844,21 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
+          <t>2006-12-06</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>`länderjämförelser` (sv)</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
         </is>
@@ -3155,15 +3877,21 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
+          <t>2013-02-01</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>`kalandermånader` (sv)</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3010</t>
         </is>
@@ -3182,15 +3910,21 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
+          <t>2013-02-01</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>`tobbit` (en)</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3011</t>
         </is>
@@ -3209,15 +3943,21 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>`kollegialtlärande` (sv)</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPE3AJ</t>
         </is>
@@ -3236,15 +3976,25 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2007-01-10</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t>2014-01-24</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t>`gryndsyn` (en)</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1020</t>
         </is>
@@ -3263,15 +4013,21 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
+          <t>2007-03-22</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>`rättsäkerhet` (sv)</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
         </is>
@@ -3290,15 +4046,25 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
+          <t>2013-11-06</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2014-01-24</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
           <t>Dubblerat ord</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>`att` — ….m. 2014-01-24.  ## Lärandemål  Kursens övergripande mål är att att den studerande förstår hur man kan styra sina informationsf…</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1067</t>
         </is>
@@ -3317,15 +4083,21 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
+          <t>2013-11-06</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
         <is>
           <t>`känndom` (sv)</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1068</t>
         </is>
@@ -3344,15 +4116,25 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2007-01-10</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
+          <t>2013-03-06</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
           <t>`gryndsyn` (en)</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2005</t>
         </is>
@@ -3371,15 +4153,25 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>2007-03-22</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t>2011-11-11</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
           <t>`rättsäkerhet` (sv)</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
         </is>
@@ -3398,15 +4190,21 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
+          <t>2019-10-23</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>`cognitiveoriented` (en)</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2226</t>
         </is>
@@ -3425,15 +4223,21 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
+          <t>2020-03-09</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>`managemet` (en)</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
         </is>
@@ -3452,15 +4256,21 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
@@ -3479,15 +4289,25 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>2020-02-24</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
           <t>`inlämingsuppgifter` (sv)</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
@@ -3506,15 +4326,25 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2020-02-24</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
           <t>`credtis` (en)</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
@@ -3533,15 +4363,21 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
+          <t>2020-04-23</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>`tillvägagångsätt` (sv)</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
         </is>
@@ -3560,15 +4396,21 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>`credtis` (en)</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
@@ -3587,15 +4429,21 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>`lärarskicklighetetens` (sv)</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AA</t>
         </is>
@@ -3614,15 +4462,21 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
+          <t>2024-02-06</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>`aanalyze` (en)</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
         </is>
@@ -3641,15 +4495,21 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
+          <t>2024-02-06</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>`nalyze` (en)</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AC</t>
         </is>
@@ -3668,15 +4528,21 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>`addmitted` (en)</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
         </is>
@@ -3695,15 +4561,21 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>`credtis` (en)</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C6</t>
         </is>
@@ -3722,15 +4594,21 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>`whithin` (en)</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C6</t>
         </is>
@@ -3749,15 +4627,21 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>`undervisningensmål` (sv)</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
         </is>
@@ -3776,15 +4660,21 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>`educare` (en)</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
         </is>
@@ -3803,15 +4693,25 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>2018-03-08</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
+          <t>2020-09-30</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
           <t>`conciderations` (en)</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22K</t>
         </is>
@@ -3830,15 +4730,21 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
+          <t>2021-12-03</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>`samhällorienterande` (sv)</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
@@ -3857,15 +4763,21 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
+          <t>2021-12-03</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
         <is>
           <t>`sociaty` (en)</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
@@ -3884,15 +4796,21 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
+          <t>2021-12-03</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
         <is>
           <t>`understandingn` (en)</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
@@ -3911,15 +4829,21 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
+          <t>2023-01-24</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>`andraämne` (sv)</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
         </is>
@@ -3938,15 +4862,21 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
+          <t>2023-01-24</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
         <is>
           <t>`andraämne` (sv)</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
         </is>
@@ -3965,15 +4895,21 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
+          <t>2024-02-06</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
           <t>Dubblerat ord</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>`as` — …ment on the way to the subject teaching profession, as well as as support for being able to make conscious didactic choices d…</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AD</t>
         </is>
@@ -3992,15 +4928,21 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
         <is>
           <t>`perspecitves` (en)</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
         </is>
@@ -4019,15 +4961,21 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
         <is>
           <t>`inlämninguppgift` (sv)</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
         </is>
@@ -4046,15 +4994,21 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>`samhällorienterande` (sv)</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
@@ -4073,15 +5027,21 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>`sociaty` (en)</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
@@ -4100,15 +5060,21 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>